--- a/baseline_scores.xlsx
+++ b/baseline_scores.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="first_iteration" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="hybrid_rerank" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="first_iteration" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hybrid_rerank" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="section_aware_chunking" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quey_rewriter" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hyde_expander_fusion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2561,4 +2564,3237 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>user_input</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>retrieved_contexts</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>context_recall</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>llm_context_precision_with_reference</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>faithfulness</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>semantic_similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What is the maximum cap on accumulated liquidated damages?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'context 2:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'context 3:\n## 16. LIMITATION ON LIABILITY\n\nIn no event shall SE, SDI or their affiliates, employees, officers, and directors be liable for any punitive, consequential, incidental, special, or indirect damages, in any action arising from or related to this Agreement, whether based in contract, tort (including negligence), intended conduct or otherwise, including without limitation, damages relating to the loss of profits, business, income, savings, use, goodwill or revenue.  Notwithstanding anything contained herein, SE’s and/or  SDI’s maximum liability shall be limited to the payments to be made to Supplier on undisputed invoices.']</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The maximum cap on accumulated liquidated damages is 10% of the Price of the related Purchase Order.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10% of the Price of the related Purchase Order.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6050673860868422</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Which country's laws govern the Agreement?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'context 2:\n## 22. COMPLIANCE WITH LAWS\n\nThe Supplier shall comply with all applicable laws in its performance of the Agreement, including without limitation, those set forth in Art. 22 and 23 of these T&amp;C.', 'context 3:\n## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.']</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The Agreement is governed by the laws of India.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The laws of India.</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6998807776087896</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>How many days does the Supplier have to challenge a debit note?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'context 2:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'context 3:\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C']</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The Supplier has fifteen (15) days from the issuing of the debit note to challenge it.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>15 days from the issuing of the debit note.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8085939276622207</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Where will any arbitration proceeding take place?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'context 2:\n## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.', 'context 3:\n## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.']</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Any arbitration proceeding will take place at New Delhi.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New Delhi.</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4608276126732579</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>If a vendor hands over goods late, how much can be docked for each week the shipment is overdue?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'context 2:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'context 3:\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>For each week of delay, 1% of the Price of the Products or Works which have not yet been delivered can be docked as liquidated damages. The accumulated liquidated damages shall not exceed 10% of the Price of the related Purchase Order.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1% of the Price of the undelivered Products/Works (or unprovided Services) per week of delay, capped overall at 10%.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6379818464372515</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Who foots the bill for obtaining the paperwork needed to ship products across borders legally?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'context 2:\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', "context 3:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The Supplier is responsible for obtaining the paperwork needed to ship products across borders legally and shall bear the associated costs.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The Supplier, at its own expense, must obtain all necessary export and re-export permits or licenses.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7299131526145219</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>How soon does the seller get paid once the integrator has itself received money from the buyer?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'context 2:\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', "context 3:\n## 17. SET-OFF\n\nSDI (in consultation with SE) may withhold amounts due under this Agreement on account of:  (a) claims arising out of or related to Supplier's breach or reasonably anticipated breach of this Agreement, (b) any amounts owed by Supplier to SE and/or SDI under this Agreement or otherwise; (c) non-conforming or deficient Services not yet corrected; (d) a reasonable doubt that Supplier can complete the Services for the unpaid portion of the Agreement price; or (e) any amounts owed by Supplier to SE and/or SDI or to an Affiliate under any other contracts, claims, demands, lawsuits or other matters.  If amounts owed by Supplier to SE and/or SDI exceed the unpaid balance of this Agreement, Supplier agrees to pay those amounts within forty-five calendar days after receipt of SDI’s notice identifying the amounts due."]</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The seller's payment will be processed within five (5) business days after the integrator (SDI) receives payment from the buyer (SE), provided that all contractually required documentation has been submitted to SDI, the seller submits its invoice in correct form containing all mandatory details, and SDI has no obligation to pay the seller unless and until the integrator is paid by the buyer for the invoiced service and product.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Within 5 business days after SDI receives payment from SE (subject to correct invoicing and documentation).</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7097784954298831</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>If a buyer wants to walk away from an order even though the supplier did nothing wrong, how much advance warning must it give?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'context 2:\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.', 'context 3:\n## 26. CONFIDENTIALITY\n\nThe Supplier shall keep all Confidential Information secret and shall not use any of it for any purpose other than the performance of the Agreement, except that, for the purpose of performance of the Agreement, the Supplier is allowed to disclose any Confidential Information, on a need-to-know basis, to his employees, subcontractors, or suppliers who undertake in writing not to disclose or otherwise misuse the Confidential Information. Upon the request by SDI, the Supplier shall execute a separate non-disclosure agreement in the form reasonably satisfactory to the SDI, undertaking not to disclose or misuse the Confidential Information.  If any Purchase Order is completed or otherwise terminated, the Supplier shall return or destroy (at the SDI’s request), at its own costs, all documents or other media which contain any Confidential Information.  The obligation set out in this Article or in any non-disclosure agreement shall survive the termination or completion of any Purchase Order or the Agreement.']</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>15 days' prior notice (termination at convenience / without cause).</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02383386720931489</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Which ISO/IEC standards are named as the alignment benchmark for the Supplier's data-security safeguards?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'context 2:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'context 3:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The ISO/IEC standards named as the alignment benchmark for the Supplier's data-security safeguards are ISO/IEC 27001 and IEC 62443.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001 or IEC 62443.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6995300392001614</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Under which Act will disputes be settled by arbitration?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'context 2:\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'context 3:\n## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.']</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Disputes will be settled by arbitration under the Arbitration and Conciliation Act, 1996.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The Arbitration and Conciliation Act, 1996 (referred to as 'IAC').</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6194351527120757</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>List the Quality Assessment Standards the Products must comply with under the warranty.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'context 2:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'context 3:\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).']</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The Products must comply with the following Quality Assessment Standards under the warranty:
+- ISO9000
+- ISO26000
+- ISO14001
+- ISO 50001
+or any other internationally recognized standards applicable to the manufacture and delivery of the Products.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ISO9000, ISO26000, ISO14001 and ISO 50001 (or other internationally recognized applicable standards).</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7154463360754051</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>What is the proprietary web-based tool through which Suppliers must submit invoices?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'context 2:\n## 1. DEFINITIONS\n\n- 1.9. “ **Payment Documentation** ” means all documents which are either a) specified in the Purchase Order which must be sent and approved by SDI as the condition for the payment of the Price; or b) if the relevant Purchase Order fails to specify the Payment Documentation: (i) a commercial invoice correctly stating the Price, (ii) (if applicable) a photocopy / original copy of the Final Acceptance Certificate bearing the SE’s (or its representative’s) signature; and (iii) if any third party Intellectual Property Right is involved in the manufacture, use, or delivery of the Products, Works or Services, all necessary documents or certificates which prove that the SE has the right to use, sell, or otherwise dispose the Products, the Works, or the Services; \n\n- 1.10.“ **Price** ” means the price for the Products, the Works or Services which SDI is obliged to pay to the Supplier under a relevant Purchase Order; \n\n\n\n- 1.11.“ **Privacy Laws** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.12.“ **Product** ” means any product which the SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.13.“ **Purchase Order** ” means any document which the SDI and the Supplier enter into which contemplates a transaction under which the Supplier is to deliver certain Products or Works to, or provide certain Services to, the SE; \n\n- 1.14.“ **SE** ” means the relevant Schneider Electric India entity on whose behalf SDI will place the Purchase Order on the Supplier, which shall include any of the following Schneider Electric India entities mentioned below: \n\n   - 1.14.1.Schneider Electric India Private Limited; \n\n   - 1.14.2.Schneider Electric Private Limited; \n\n   - 1.14.3.Schneider Electric IT Business India Private Limited \n\n   - 1.14.4.Schneider Electric President Systems Limited \n\n   - 1.14.5.Schneider Electric Infrastructure Limited \n\n   - 1.14.6.Schneider Electric Systems India Private Limited (formerly known as Invensys India Private Limited) \n\n   - 1.14.7.Eurotherm India Private Limited \n\n   - 1.14.8.Energy Grid Automation Transformers &amp; Switchgear India Private Limited; and \n\n   - 1.14.9.Schneider Electric Solar India Private Limited.', 'context 3:\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>The proprietary web-based tool through which Suppliers must submit invoices is Work Nexus®.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Work Nexus(R), SDI's proprietary web-based tool.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6188086270072779</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A non-MSME supplier delivers goods two weeks late. Explain both the payment timeline that applies and the penalty for the delay.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'context 2:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'context 3:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.']</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>The payment timeline for a non-MSME supplier is as follows: Supplier's payments will be processed within five (5) business days after SDI receives payment from SE. SE's payment terms to SDI for non-MSME vendors are Net seventy (70) days from the receipt of the invoice by SE. Therefore, the payment to the supplier will occur within 70 days from the receipt of the invoice by SE, plus an additional five business days for SDI to process the payment to the supplier.
+As for the penalty for the two-week delay in delivery, the supplier will be subject to liquidated damages. For each week of delay, the supplier is penalized 1% of the Price of the undelivered Products or unprovided Services. Since the supplier is two weeks late, the supplier incurs a penalty of 2% of the Price of the undelivered Products or unprovided Services. The accumulated liquidated damages shall not exceed 10% of the Price of the related Purchase Order. This penalty is in addition to the supplier's obligation to fulfill its remaining obligations under the Agreement.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Payment: SE pays SDI on Net 70-day terms for non-MSME vendors (from SE's receipt of invoice), and the Supplier is paid within 5 business days after SDI receives payment from SE. Penalty: liquidated damages of 1% of Price per week of delay, so ~2% for two weeks, subject to the overall 10% cap.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8443405595717418</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>What are the notice periods for terminating a Purchase Order for convenience versus for an unrectified breach?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'context 2:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'context 3:\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>For terminating a Purchase Order for convenience under Article 13, SDI must provide 15 days' prior notice to the Supplier.
+For terminating a Purchase Order for an unrectified breach under Article 14, SDI may issue notice with immediate effect and is not required to provide a specific notice period.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Termination at convenience requires 15 days' prior notice. Termination for default for a rectifiable breach allows termination if the Supplier fails to rectify within 30 days of SDI's notice.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8654262528863044</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>When does title pass to SE, and when does risk pass to SE, and why are they different points in time?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', 'context 2:\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'context 3:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>- The title passes to SE when the Products and Works are delivered to the Delivery Point, or when the Services are completed, or when a Purchase Order is terminated and the Supplier receives the termination notice.
+- The risk passes to SE only after the Supplier receives the Final Acceptance Certificate.
+- They are different points in time because title and risk are different legal concepts: Title refers to ownership and legal rights being transferred, while risk refers to who bears the consequences if anything goes wrong (e.g., damage, loss). The distinction allows SE to take legal ownership before fully accepting the deliverables and being satisfied with their quality.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Title/ownership vests with SE when the Products/Works are delivered to the Delivery Point or the Services are completed. Risk, however, remains with the Supplier until the Supplier receives the Final Acceptance Certificate. So title can transfer before risk does.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8717064732070583</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>For a product found defective during the warranty period, what are the Supplier's options and the associated interest rate and time limit?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'context 2:\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'context 3:\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.']</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>During the warranty period, if a product is found defective, the Supplier has two options:
+1) The Supplier may immediately collect the defective items at its own cost and repay the price to SDI (or their designated customer) along with interest at 2% above the prevailing prime lending rate, calculated from the date SDI paid the price. The Supplier is also required to compensate for any losses arising from the purchase, use, or resale of the defective items.
+2) Alternatively, the Supplier may repair, rectify, or replace the defective items at its own cost within a specified period. If no period is specified in the Compliance Notice, the time limit is 15 working days from the date of the Compliance Notice.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>At SDI's election the Supplier must either (a) collect the defective items and repay the Price with interest at 2% above the prevailing prime lending rate (plus compensate losses), or (b) repair/rectify/replace within the period specified, defaulting to 15 working days. The warranty period is, by default, 12 months.</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9038582522309823</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>What event triggers a 'Compliance Notice', and what must the Supplier do once it receives one? Use the document's own definitions.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'context 2:\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.', 'context 3:\n## 1. DEFINITIONS\n\nFor the purpose of, these General Terms and Conditions of Purchase (“T&amp;C”), the following terms shall have the meaning hereby assigned to them unless the context would obviously require otherwise:\n- 1.1. “ **Agreement”** means these T&amp;C and the Purchase Order, collectively;\n- 1.2. “ **Alteration Notice** ” shall have the meaning set out in Art. 15 of these T&amp;C;\n- 1.3. “ **Compliance Notice** ” shall have the meaning set out in Art. 8.4 of these T&amp;C; SDI will provide such a notice to Supplier via e-mail upon being requested to do so by SE.']</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A 'Compliance Notice' is triggered when SDI finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs ("Defective Item"), and SDI (if requested by SE) sends the notice to the Supplier. 
+Upon receipt of the Compliance Notice, the Supplier must, at SE’s election, either: 
+a) immediately collect the Defective Items at its own cost, repay the Price for the Defective Items with interest, and compensate for any losses, or 
+b) repair, rectify, or replace the Defective Items at its own cost within the specified period.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>The definition of 'Compliance Notice' points to Art. 8.4. It is triggered when SE finds (itself or via a customer) that any Product/Work/Service is a 'Defective Item' during the Warranty Period. On receipt, the Supplier must, at SDI's election, either repay the Price plus 2% above prime lending rate (and compensate losses), or repair/replace within 15 working days.</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8333333332916666</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9174934700600528</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>If a Purchase Order does not state a warranty period for a Service, when does the warranty begin and how long does it last?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'context 2:\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'context 3:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>If a Purchase Order does not state a warranty period for a Service, the warranty period begins:  
+- **Either** on the date when the Service is completed **or** on the date when the SE issues a Final Acceptance Certificate for the relevant Service (whichever occurs later).  
+The warranty period lasts **twelve (12) months** from this start date. Additionally, if the Service is repaired or replaced after the Final Acceptance Certificate is granted, the warranty period for the repaired or replaced Service lasts **twelve (12) months from the date of such repair or replacement**.  
+(As defined in Art. 1.20 "Warranty Period" of the context.)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>It lasts 12 months, running from the date SE issues the Final Acceptance Certificate for the Services or from when the Services are completed, whichever is later. (This requires combining the 'Warranty Period' default with the 'Final Acceptance Certificate' concept.)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6949319624077415</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A supplier has separately negotiated and executed a services agreement. A conflict then arises between that agreement, the Purchase Order, and these T&amp;C. Which prevails, and how do you know?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'context 2:\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'context 3:\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>The services agreement prevails over these T&amp;C to the extent of any discrepancy or conflict. This is stated in Art. 2.1 of the T&amp;C, which clarifies that if the Parties specifically negotiate and execute a services agreement, the terms and conditions of that services agreement shall prevail over these T&amp;C.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Normally the T&amp;C prevail over an inconsistent Purchase Order. However, where the parties specifically negotiate and execute a services agreement, that services agreement prevails over the T&amp;C to the extent of any conflict. (The Order of Precedence on p.1 plus Art. 2.1 establish this.)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7741082652950427</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>At what exact point are Products considered 'delivered' so that the payment process can begin? Pull together every condition the document attaches.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', 'context 2:\n## 1. DEFINITIONS\n\n- 1.5. “ **Defective Item** ” shall have the meaning set out in Art. 8.4 of these T&amp;C;\n- 1.6. “ **Delivery Point** ” means the location which the Purchase Order stipulates for the delivery of the Products or the Works or the Services or, if the Purchase Order fails to specify such location, a location of which the SE or SDI may notify to the Supplier within a reasonable period before the scheduled delivery date;\n- 1.7. “ **Final Acceptance Certificate** ” means the document which the SE, or its duly authorized representative, issues to the Supplier confirming that the Products, the Works or the Services comply with requirements under the Agreement, after having a reasonable opportunity to examine them according to Art. 9.3 of these T&amp;C;\n- 1.8. “ **Intellectual Property Right** ” means any intellectual property right, regardless of whether registered or not, including any: (i) patent, (ii) copyright (including moral right and author’s right); (iii) database right; (iv) know-how or trade secret, whether or not developed or reduced to practice; (v) industrial design; (vi) trademark, service mark, logo, domain name and keyword, and the goodwill associated with them; (vii) right of publicity; and (viii) any other proprietary right relating to intangible property anywhere in the world;', 'context 3:\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.']</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>According to the document, the Products or Works are considered delivered and the Services are considered performed only when the following conditions are met:
+1. All Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pickup or for use.
+2. SE and SDI have received a notification from the Supplier regarding the delivery and completion.
+3. All documents set out in Article 24 of these Terms and Conditions have been received by SE and SDI.
+4. If any Product, Work, or Service requires replacement or repair according to Article 8.4 of these Terms and Conditions, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Products/Works are not considered delivered until: (a) all are placed at the Delivery Point ready for pickup/use; (b) SE and SDI receive the Supplier's delivery/completion notification; (c) all required documents are received; and (d) where repair/replacement applied, the relevant Final Acceptance Certificate is issued. Only once delivery is complete and a compliant invoice is submitted does the payment timeline run.</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.8402700376285699</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>What late-payment interest rate must SDI pay the Supplier if SDI pays after the due date?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.', 'context 2:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', "context 3:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>The document does not specify any late-payment interest payable by SDI to the Supplier. (It specifies interest on defective-item repayments and on GST/credit reversals, but not a penalty for SDI's late payment.) The correct response is that this is not stated.</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.051666416740992</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>What is the minimum order value or monetary threshold required to raise a Purchase Order under these terms?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'context 2:\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', 'context 3:\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The document does not state any minimum order value or monetary threshold for a Purchase Order. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.01824678317384411</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>How many days of paid leave are the Supplier's on-site personnel entitled to?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', "context 2:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", "context 3:\n## 17. SET-OFF\n\nSDI (in consultation with SE) may withhold amounts due under this Agreement on account of:  (a) claims arising out of or related to Supplier's breach or reasonably anticipated breach of this Agreement, (b) any amounts owed by Supplier to SE and/or SDI under this Agreement or otherwise; (c) non-conforming or deficient Services not yet corrected; (d) a reasonable doubt that Supplier can complete the Services for the unpaid portion of the Agreement price; or (e) any amounts owed by Supplier to SE and/or SDI or to an Affiliate under any other contracts, claims, demands, lawsuits or other matters.  If amounts owed by Supplier to SE and/or SDI exceed the unpaid balance of this Agreement, Supplier agrees to pay those amounts within forty-five calendar days after receipt of SDI’s notice identifying the amounts due."]</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Not addressed. This is a purchase T&amp;C, not an employment contract; it expressly states the Supplier's personnel are independent and not employees of SE/SDI, but says nothing about their leave entitlements. The correct response is that this is not covered.</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.07823683174726326</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>In which currency must invoices be denominated?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'context 2:\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'context 3:\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.']</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The document does not specify a currency for invoices. It details required invoice fields, taxes and GST handling, but no currency is stated. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.01623632649160952</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>List every distinct deadline or response window the Supplier must observe across the whole contract.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'context 2:\n## 20. ASSIGNMENT AND SUBCONTRACTING\n\nSDI shall have the right to assign its rights or obligations under the Agreement in part or in whole to any third party (including its affiliate) by notice to, but without consent of, the Supplier. However, the Supplier shall not assign or subcontract any obligation under the Agreement to any third party without the prior written consent of SDI. Without prejudice to the foregoing, SDI’s consent to the assignment or sub-contracting shall not release the Supplier from the obligations under the Agreement which have been assigned or subcontracted. Supplier assumes full responsibility to SE and SDI for the improper acts and omissions of its subcontractors or others employed or retained by Supplier in connection with the Agreement.', 'context 3:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1. The Supplier must respond to an Alteration Notice from SDI within five (5) working days from the date of the Alteration Notice.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Examples spanning the document: 15 days to challenge a debit note (Art. 4); 5 working days to respond to an Alteration Notice (Art. 15.1); 7 days to act after a Reminder Notice if none specified (Art. 6.3); 30 days to rectify a rectifiable breach (Art. 14.1(b)); 15 working days to repair/replace a Defective Item if none specified (Art. 8.4); 3 working days to supply export-control info after PO receipt (Art. 23); 24 hours to notify a Security Incident (Art. 31.3); 45 calendar days to pay set-off amounts (Art. 17). A complete answer requires sweeping the entire document.</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4020997522600651</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Summarize every scenario in which SE or SDI may withhold, deduct, or recover money from the Supplier.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 17. SET-OFF\n\nSDI (in consultation with SE) may withhold amounts due under this Agreement on account of:  (a) claims arising out of or related to Supplier's breach or reasonably anticipated breach of this Agreement, (b) any amounts owed by Supplier to SE and/or SDI under this Agreement or otherwise; (c) non-conforming or deficient Services not yet corrected; (d) a reasonable doubt that Supplier can complete the Services for the unpaid portion of the Agreement price; or (e) any amounts owed by Supplier to SE and/or SDI or to an Affiliate under any other contracts, claims, demands, lawsuits or other matters.  If amounts owed by Supplier to SE and/or SDI exceed the unpaid balance of this Agreement, Supplier agrees to pay those amounts within forty-five calendar days after receipt of SDI’s notice identifying the amounts due.", 'context 2:\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.', 'context 3:\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SE or SDI may withhold, deduct, or recover money from the Supplier in the following scenarios:
+1. **Set-Off (Section 17):**
+   - Due to claims arising from the Supplier's breach or reasonably anticipated breach of the Agreement.
+   - For any amounts owed by the Supplier to SE and/or SDI under this Agreement or otherwise.
+   - Due to non-conforming or deficient Services that have not yet been corrected.
+   - If there is a reasonable doubt that the Supplier can complete the Services for the unpaid portion of the Agreement.
+   - For any amounts owed by the Supplier to SE and/or SDI or to an Affiliate under other contracts, claims, demands, or lawsuits.
+2. **Intellectual Property Rights (Section 12.1):**
+   - If a third party brings or threatens to bring an action or claim against SE or SDI for infringement of an Intellectual Property Right, SE or SDI may withhold any money due or to be due to the Supplier.
+3. **Packing and Shipping (Section 21):**
+   - SE and SDI may deduct any amount owed by the Supplier from any payment due or to be due to the Supplier. This applies if the Supplier incurs increased costs due to insufficient packing, improper preparation of shipping documents, or delays in document submission that lead to additional expenses (e.g., storage, demurrage, tariff charges).</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Across the document these include: GST/input-tax-credit non-compliance withholding and recovery (Art. 5); debit notes for volume/quality/price disputes (Art. 4); set-off of amounts owed (Art. 17); liquidated damages for late delivery (Art. 6); repayment plus interest for Defective Items (Art. 8.4); deductions for losses from improper packing/shipping (Art. 21); and withholding money on third-party IP-infringement claims (Art. 12.1). A complete answer requires aggregating many sections.</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5767984514379076</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Overall, what are the main categories of obligation this contract places on the Supplier?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 20. ASSIGNMENT AND SUBCONTRACTING\n\nSDI shall have the right to assign its rights or obligations under the Agreement in part or in whole to any third party (including its affiliate) by notice to, but without consent of, the Supplier. However, the Supplier shall not assign or subcontract any obligation under the Agreement to any third party without the prior written consent of SDI. Without prejudice to the foregoing, SDI’s consent to the assignment or sub-contracting shall not release the Supplier from the obligations under the Agreement which have been assigned or subcontracted. Supplier assumes full responsibility to SE and SDI for the improper acts and omissions of its subcontractors or others employed or retained by Supplier in connection with the Agreement.', 'context 2:\n## 26. CONFIDENTIALITY\n\nThe Supplier shall keep all Confidential Information secret and shall not use any of it for any purpose other than the performance of the Agreement, except that, for the purpose of performance of the Agreement, the Supplier is allowed to disclose any Confidential Information, on a need-to-know basis, to his employees, subcontractors, or suppliers who undertake in writing not to disclose or otherwise misuse the Confidential Information. Upon the request by SDI, the Supplier shall execute a separate non-disclosure agreement in the form reasonably satisfactory to the SDI, undertaking not to disclose or misuse the Confidential Information.  If any Purchase Order is completed or otherwise terminated, the Supplier shall return or destroy (at the SDI’s request), at its own costs, all documents or other media which contain any Confidential Information.  The obligation set out in this Article or in any non-disclosure agreement shall survive the termination or completion of any Purchase Order or the Agreement.', 'context 3:\n## 2. INTERPRETATION\n\n- 2.2. The provisions of these T&amp;C shall be interpreted according to the following rules: a) The article headings and marginal notes are for convenience of reference only and are not part of the Agreement, and shall not be taken into consideration in their construction and interpretation; \n\n   - b) Words importing persons shall include partnerships, firms, joint ventures, trusts, associations, companies and corporations and any organization or institution having legal capacity; \n\n   - c) Words importing the singular also include the plural and vice versa where the context requires. Words importing one gender also include other genders; \n\n   - d) With respect to the obligations that are binding on the Supplier under the Agreement, the Supplier shall also ensure that its subcontractors and suppliers comply with them to the extent applicable; and \n\ne) The words “including” or “includes” shall be deemed to be qualified by a reference to “without limitation”.']</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the main categories of obligation placed on the Supplier by the contract are:
+1. **Non-Assignment/Subcontracting Obligation**:
+   - The Supplier must obtain prior written consent from SDI before assigning or subcontracting any obligations under the Agreement.
+2. **Confidentiality Obligation**:
+   - The Supplier must maintain the confidentiality of SDI's Confidential Information.
+   - The Supplier can only disclose Confidential Information to employees, subcontractors, or suppliers on a need-to-know basis, provided they are bound by written undertakings not to misuse or disclose it.
+   - Upon SDI's request, the Supplier must execute a non-disclosure agreement.
+   - The Supplier must return or destroy all documents or media containing Confidential Information upon completion or termination of the Purchase Order, at its own cost.
+   - These confidentiality obligations survive the termination or completion of any Purchase Order or the Agreement.
+3. **Responsibility for Subcontractors**:
+   - The Supplier is responsible for the improper acts or omissions of its subcontractors or others used in connection with the Agreement.
+4. **Compliance with Agreement Terms**:
+   - The Supplier must ensure its subcontractors and suppliers comply with the obligations applicable to the Supplier under the Agreement.
+These obligations are outlined in the sections on Assignment and Subcontracting, Confidentiality, and Interpretation of the Agreement.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>High-level themes spanning the contract: deliver on time and to spec (Arts. 6, 8, 9); provide warranties and remedy defects (Art. 8); carry insurance (Art. 11); indemnify SE/SDI (Art. 10); respect and assign IP rights (Art. 12); maintain confidentiality (Arts. 1.4, 26); comply with tax/GST, export-control and other laws (Arts. 5, 22, 23); protect data and meet cyber-security minimums (Arts. 24, 31); supply documentation (Art. 25); and follow the Business Partner Code of Conduct (Art. 30). This is a whole-document synthesis.</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6081059833234015</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>List all the ways a Purchase Order can be terminated under this contract and the condition for each.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'context 2:\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'context 3:\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1. **Termination at Convenience (Article 13)**  
+   - **Condition**: SDI, in consultation with SE, can terminate a Purchase Order in whole or in part without cause by giving 15 days' prior notice to the Supplier.  
+   - **Details**:  
+     - The Supplier must immediately cease performance, including manufacturing, providing services, and placing orders with subcontractors or suppliers.  
+     - The Supplier must protect and hand over any completed Products or Works, along with required documentation.  
+     - The Supplier must make best efforts to terminate existing orders with subcontractors or suppliers or assign such orders to SDI if requested.  
+     - The Supplier is entitled to payment only for completed Products, Works, or Services that meet the Agreement's requirements at the time of termination. No other compensation or damages are allowable.
+2. **Termination for Default (Article 14)**  
+   - **Condition**: SDI, in consultation with SE, can terminate a Purchase Order in whole or in part due to the Supplier's default. Termination is effective immediately and without compensation.  
+   - **Details**:  
+     - Termination applies if the Supplier:  
+       - a) breaches any material provision of the Agreement;  
+       - b) breaches any provision of the Agreement and fails to rectify it within 30 days of notice (if rectifiable);  
+       - c) fails to deliver the Products or Works, or to complete the Services as specified;  
+       - d) refuses to proceed with the performance of the Purchase Order; or  
+       - e) becomes insolvent, bankrupt, or takes action that puts SE or SDI at risk of losing substantial benefit under the Purchase Order.  
+     - SDI will pay (and only pay) for the Products, Works, or Services that SE has received and elects to keep.  
+     - The Supplier must repay SDI for any Products or Works paid for but not delivered or returned.  
+     - Termination under this Article does not affect obligations of the Supplier for delivered and paid-for Products or Services.
+3. **Automatic Termination upon Delivery or Termination Notice (Article 7.1)**  
+   - **Condition**: If a Purchase Order is terminated for any reason before delivery of the Products or Works or completion of the Services, the title to those deliverables vests with SE when the Supplier receives the termination notice under Articles 13 or 14.  
+   - **Details**:  
+     - This termination does not affect the Supplier's obligations under the Agreement.  
+     - Risk remains with the Supplier until the Final Acceptance Certificate is issued.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Termination at convenience: by SDI without cause on 15 days' notice (Art. 13). Termination for default: immediately, on a material breach, an unrectified breach (30 days), failure to deliver after a Reminder Notice, refusal to perform, or insolvency/bankruptcy (Art. 14). Via change order: if the parties cannot agree on a rejected/extra-cost Alteration Notice, SDI may terminate under Art. 13 (Art. 15.3). Delivery failure: termination after an unmet Reminder Notice period (Art. 6.3). Requires gathering distant sections.</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7376574338890848</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>user_input</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>retrieved_contexts</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>context_recall</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>llm_context_precision_with_reference</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>faithfulness</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>semantic_similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What is the maximum cap on accumulated liquidated damages?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'context 2:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'context 3:\n## 16. LIMITATION ON LIABILITY\n\nIn no event shall SE, SDI or their affiliates, employees, officers, and directors be liable for any punitive, consequential, incidental, special, or indirect damages, in any action arising from or related to this Agreement, whether based in contract, tort (including negligence), intended conduct or otherwise, including without limitation, damages relating to the loss of profits, business, income, savings, use, goodwill or revenue.  Notwithstanding anything contained herein, SE’s and/or  SDI’s maximum liability shall be limited to the payments to be made to Supplier on undisputed invoices.']</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The accumulated liquidated damages shall not exceed 10% of the Price of the related Purchase Order.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10% of the Price of the related Purchase Order.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.597864497137063</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Which country's laws govern the Agreement?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'context 2:\n## 22. COMPLIANCE WITH LAWS\n\nThe Supplier shall comply with all applicable laws in its performance of the Agreement, including without limitation, those set forth in Art. 22 and 23 of these T&amp;C.', 'context 3:\n## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.']</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The laws of India apply to this agreement.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The laws of India.</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7423790907307452</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>How many days does the Supplier have to challenge a debit note?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'context 2:\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'context 3:\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The supplier has fifteen (15) days from the issuing of the debit note to challenge it.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>15 days from the issuing of the debit note.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8085939276622207</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Where will any arbitration proceeding take place?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'context 2:\n## 1. DEFINITIONS\n\n- 1.5. “ **Defective Item** ” shall have the meaning set out in Art. 8.4 of these T&amp;C;\n- 1.6. “ **Delivery Point** ” means the location which the Purchase Order stipulates for the delivery of the Products or the Works or the Services or, if the Purchase Order fails to specify such location, a location of which the SE or SDI may notify to the Supplier within a reasonable period before the scheduled delivery date;\n- 1.7. “ **Final Acceptance Certificate** ” means the document which the SE, or its duly authorized representative, issues to the Supplier confirming that the Products, the Works or the Services comply with requirements under the Agreement, after having a reasonable opportunity to examine them according to Art. 9.3 of these T&amp;C;\n- 1.8. “ **Intellectual Property Right** ” means any intellectual property right, regardless of whether registered or not, including any: (i) patent, (ii) copyright (including moral right and author’s right); (iii) database right; (iv) know-how or trade secret, whether or not developed or reduced to practice; (v) industrial design; (vi) trademark, service mark, logo, domain name and keyword, and the goodwill associated with them; (vii) right of publicity; and (viii) any other proprietary right relating to intangible property anywhere in the world;', 'context 3:\n## 28. COMMUNICATIONS\n\nAll communications between the Supplier and SDI shall be in English and in the form of e-mails, faxes, or letters and shall be sent to the address or e-mail accounts, or contact numbers (as the case may be) as shown on the Purchase Order, unless one Party otherwise notifies the other Party in writing.']</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Arbitration hearings will be held in New Delhi.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New Delhi.</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4028469817888714</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>If a vendor hands over goods late, how much can be docked for each week the shipment is overdue?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'context 2:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'context 3:\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The penalty for late delivery of goods by a vendor is 1% of the Price of the Products or Works which have not yet been delivered, for each week of delay. The accumulated liquidated damages shall not exceed 10% of the Price of the related Purchase Order.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1% of the Price of the undelivered Products/Works (or unprovided Services) per week of delay, capped overall at 10%.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6140735096435772</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Who foots the bill for obtaining the paperwork needed to ship products across borders legally?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'context 2:\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', "context 3:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The Supplier is responsible for obtaining all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The Supplier, at its own expense, must obtain all necessary export and re-export permits or licenses.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8520479618926511</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>How soon does the seller get paid once the integrator has itself received money from the buyer?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", "context 2:\n## 17. SET-OFF\n\nSDI (in consultation with SE) may withhold amounts due under this Agreement on account of:  (a) claims arising out of or related to Supplier's breach or reasonably anticipated breach of this Agreement, (b) any amounts owed by Supplier to SE and/or SDI under this Agreement or otherwise; (c) non-conforming or deficient Services not yet corrected; (d) a reasonable doubt that Supplier can complete the Services for the unpaid portion of the Agreement price; or (e) any amounts owed by Supplier to SE and/or SDI or to an Affiliate under any other contracts, claims, demands, lawsuits or other matters.  If amounts owed by Supplier to SE and/or SDI exceed the unpaid balance of this Agreement, Supplier agrees to pay those amounts within forty-five calendar days after receipt of SDI’s notice identifying the amounts due.", 'context 3:\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The seller (Supplier) receives payment within five (5) business days after the integrator (SDI) receives payment from the buyer (SE).</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Within 5 business days after SDI receives payment from SE (subject to correct invoicing and documentation).</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8113747298804375</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>If a buyer wants to walk away from an order even though the supplier did nothing wrong, how much advance warning must it give?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'context 2:\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'context 3:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The notice period required for a buyer (SDI) to cancel an order without penalty when the supplier is not at fault is 15 days' prior notice to the supplier.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>15 days' prior notice (termination at convenience / without cause).</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.49702268858798</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Which ISO/IEC standards are named as the alignment benchmark for the Supplier's data-security safeguards?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'context 2:\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.1. To the extent required by law, applicable industrial standards, or the  Purchase Order, the Supplier shall carry out (and ensure its subcontractors and suppliers carry out), at no cost to the  SE or  SDI, all testing and inspection of the Products, the Works and the Services before it notifies   SE and SDI of the delivery or completion according Art. 6.4(b) of these T&amp;C. The Supplier shall notify the SE and SDI of such testing or inspection; and SE shall have the right (but not obligation) to witness such testing and inspection. The Supplier shall provide the SE with full access to such testing or inspection and all related results.', 'context 3:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The ISO standards used to measure a supplier's data security measures include ISO/IEC 27001 and IEC 62443.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001 or IEC 62443.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.731560838030298</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Under which Act will disputes be settled by arbitration?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'context 2:\n## 22. COMPLIANCE WITH LAWS\n\nThe Supplier shall comply with all applicable laws in its performance of the Agreement, including without limitation, those set forth in Art. 22 and 23 of these T&amp;C.', 'context 3:\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.']</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>The Arbitration and Conciliation Act, 1996 (IAC) governs arbitration to resolve disputes.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The Arbitration and Conciliation Act, 1996 (referred to as 'IAC').</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8180403080836856</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>List the Quality Assessment Standards the Products must comply with under the warranty.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'context 2:\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.', 'context 3:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>To be covered by a warranty, the products must meet ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the products or works.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ISO9000, ISO26000, ISO14001 and ISO 50001 (or other internationally recognized applicable standards).</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8333333332916666</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6603511581961912</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>What is the proprietary web-based tool through which Suppliers must submit invoices?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'context 2:\n## 28. COMMUNICATIONS\n\nAll communications between the Supplier and SDI shall be in English and in the form of e-mails, faxes, or letters and shall be sent to the address or e-mail accounts, or contact numbers (as the case may be) as shown on the Purchase Order, unless one Party otherwise notifies the other Party in writing.', 'context 3:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Suppliers use SDI’s proprietary web-based tool, Work Nexus®, to submit invoices.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Work Nexus(R), SDI's proprietary web-based tool.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7110430641716996</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A non-MSME supplier delivers goods two weeks late. Explain both the payment timeline that applies and the penalty for the delay.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'context 2:\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'context 3:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.']</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>If a regular supplier delivers goods late, SDI (in consultation with SE) may serve a Reminder Notice requesting immediate delivery or completion within a specified period. For each week of delay, the supplier is subject to liquidated damages of 1% of the Price of the undelivered Products or Works or unprovided Services, with a maximum cap of 10% of the Price of the related Purchase Order. The supplier remains obligated to fulfill all obligations under the Agreement, and any additional costs or expenses incurred due to the delay will be borne by the supplier. The supplier must also ensure proper packing and timely preparation of shipping documents to avoid further costs, which the supplier is liable to indemnify if not met. SDI and SE reserve the right to terminate the Purchase Order if the supplier fails to deliver or provide services within the specified period or seven (7) days from the Reminder Notice, if no period is specified.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Payment: SE pays SDI on Net 70-day terms for non-MSME vendors (from SE's receipt of invoice), and the Supplier is paid within 5 business days after SDI receives payment from SE. Penalty: liquidated damages of 1% of Price per week of delay, so ~2% for two weeks, subject to the overall 10% cap.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7205421933159237</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>What are the notice periods for terminating a Purchase Order for convenience versus for an unrectified breach?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'context 2:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'context 3:\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>- For termination at convenience (as per Article 13.1), the notice period is **15 days**.
+- For termination due to a breach (as per Article 14.1), there is **no specific notice period** stated; however, if the breach is rectifiable, the Supplier is given **30 days** from the notice to rectify the breach before termination can occur.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Termination at convenience requires 15 days' prior notice. Termination for default for a rectifiable breach allows termination if the Supplier fails to rectify within 30 days of SDI's notice.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7242792602120089</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>When does title pass to SE, and when does risk pass to SE, and why are they different points in time?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', 'context 2:\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'context 3:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.']</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>The title transfers to SE when: 
+- the Products and Works are delivered to the Delivery Point or the Services are completed, or 
+- if a Purchase Order is terminated before delivery or completion, when the Supplier receives the termination notice according to Art. 13 and 14 of the T&amp;C.
+The risk remains with the Supplier until the Supplier receives the Final Acceptance Certificate.
+They occur at different times because the title transfer is based on delivery or completion (or termination), whereas the risk transfer is contingent on receiving the Final Acceptance Certificate. This distinction ensures that ownership can vest with SE upon delivery, while the Supplier remains responsible for any potential issues until formal acceptance.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Title/ownership vests with SE when the Products/Works are delivered to the Delivery Point or the Services are completed. Risk, however, remains with the Supplier until the Supplier receives the Final Acceptance Certificate. So title can transfer before risk does.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9240288514226052</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>For a product found defective during the warranty period, what are the Supplier's options and the associated interest rate and time limit?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'context 2:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'context 3:\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).']</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>During the warranty period, if a defective product is identified, the supplier has the following options:
+1. **Option (a)**: The supplier must immediately collect the defective items at its own cost and repay SDI (or their designated customer) the price for the defective items. The interest rate applied is 2% above the prevailing prime lending rate, calculated from the date when SDI paid the price. Additionally, the supplier must compensate SE and SDI for any losses arising from the purchase, use, or resale of the defective items.
+2. **Option (b)**: The supplier may repair, rectify, or replace the defective items at its own cost. This must be done within the period specified in the Compliance Notice issued by SDI (in consultation with SE). If no period is specified, the time limit is 15 working days from the date of the Compliance Notice.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>At SDI's election the Supplier must either (a) collect the defective items and repay the Price with interest at 2% above the prevailing prime lending rate (plus compensate losses), or (b) repair/rectify/replace within the period specified, defaulting to 15 working days. The warranty period is, by default, 12 months.</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9014458758650199</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>What event triggers a 'Compliance Notice', and what must the Supplier do once it receives one? Use the document's own definitions.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.', 'context 2:\n## 1. DEFINITIONS\n\nFor the purpose of, these General Terms and Conditions of Purchase (“T&amp;C”), the following terms shall have the meaning hereby assigned to them unless the context would obviously require otherwise:\n- 1.1. “ **Agreement”** means these T&amp;C and the Purchase Order, collectively;\n- 1.2. “ **Alteration Notice** ” shall have the meaning set out in Art. 15 of these T&amp;C;\n- 1.3. “ **Compliance Notice** ” shall have the meaning set out in Art. 8.4 of these T&amp;C; SDI will provide such a notice to Supplier via e-mail upon being requested to do so by SE.', 'context 3:\n## 22. COMPLIANCE WITH LAWS\n\nThe Supplier shall comply with all applicable laws in its performance of the Agreement, including without limitation, those set forth in Art. 22 and 23 of these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>When a supplier receives a Compliance Notice, according to the document's rules, the supplier shall, at SE's election, retrieve, replace, or rectify the defects as set out in Art. 8.4 of these T&amp;C. The term "Compliance Notice" is defined as having the meaning set out in Art. 8.4 of these T&amp;C, and SDI will provide such a notice to the Supplier via e-mail upon being requested to do so by SE.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>The definition of 'Compliance Notice' points to Art. 8.4. It is triggered when SE finds (itself or via a customer) that any Product/Work/Service is a 'Defective Item' during the Warranty Period. On receipt, the Supplier must, at SDI's election, either repay the Price plus 2% above prime lending rate (and compensate losses), or repair/replace within 15 working days.</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8585754179244236</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>If a Purchase Order does not state a warranty period for a Service, when does the warranty begin and how long does it last?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'context 2:\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'context 3:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>The default warranty period for services, if not specified in a purchase order, is twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>It lasts 12 months, running from the date SE issues the Final Acceptance Certificate for the Services or from when the Services are completed, whichever is later. (This requires combining the 'Warranty Period' default with the 'Final Acceptance Certificate' concept.)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8200839060750049</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A supplier has separately negotiated and executed a services agreement. A conflict then arises between that agreement, the Purchase Order, and these T&amp;C. Which prevails, and how do you know?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'context 2:\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', 'context 3:\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>If there is any inconsistency between any provision in the Purchase Order and any provision in the Terms and Conditions (T&amp;C), the T&amp;C prevail. However, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over the T&amp;C to the extent of any discrepancy or conflict.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Normally the T&amp;C prevail over an inconsistent Purchase Order. However, where the parties specifically negotiate and execute a services agreement, that services agreement prevails over the T&amp;C to the extent of any conflict. (The Order of Precedence on p.1 plus Art. 2.1 establish this.)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9161630686222071</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>At what exact point are Products considered 'delivered' so that the payment process can begin? Pull together every condition the document attaches.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'context 2:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', 'context 3:\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.']</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Products are considered delivered when the following conditions are met:
+- All Products and Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick-up or use.
+- SE and SDI have received a notification from the Supplier regarding the delivery and completion.
+- All required documents, as outlined in Article 24 of the T&amp;C, have been received by SE and SDI.
+- If any Product, Work, or Service requires replacement or repair according to Article 8.4 of the T&amp;C, the delivery of the Product or Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.
+For payment to start, the following conditions must be met:
+- All contractually required documentation has been submitted to SDI.
+- The Supplier submits its invoice in the correct form containing all mandatory details as defined in the T&amp;C and SDI’s Billing Instructions.
+- SDI receives payment from SE for the invoiced Service and Product.
+Once these conditions are satisfied, payments to the Supplier will be processed within five (5) business days after SDI receives payment from SE.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Products/Works are not considered delivered until: (a) all are placed at the Delivery Point ready for pickup/use; (b) SE and SDI receive the Supplier's delivery/completion notification; (c) all required documents are received; and (d) where repair/replacement applied, the relevant Final Acceptance Certificate is issued. Only once delivery is complete and a compliant invoice is submitted does the payment timeline run.</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9166147603074257</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>What late-payment interest rate must SDI pay the Supplier if SDI pays after the due date?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'context 2:\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.', 'context 3:\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>The document does not specify any late-payment interest payable by SDI to the Supplier. (It specifies interest on defective-item repayments and on GST/credit reversals, but not a penalty for SDI's late payment.) The correct response is that this is not stated.</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.051666416740992</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>What is the minimum order value or monetary threshold required to raise a Purchase Order under these terms?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'context 2:\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'context 3:\n## 1. DEFINITIONS\n\n- 1.9. “ **Payment Documentation** ” means all documents which are either a) specified in the Purchase Order which must be sent and approved by SDI as the condition for the payment of the Price; or b) if the relevant Purchase Order fails to specify the Payment Documentation: (i) a commercial invoice correctly stating the Price, (ii) (if applicable) a photocopy / original copy of the Final Acceptance Certificate bearing the SE’s (or its representative’s) signature; and (iii) if any third party Intellectual Property Right is involved in the manufacture, use, or delivery of the Products, Works or Services, all necessary documents or certificates which prove that the SE has the right to use, sell, or otherwise dispose the Products, the Works, or the Services; \n\n- 1.10.“ **Price** ” means the price for the Products, the Works or Services which SDI is obliged to pay to the Supplier under a relevant Purchase Order; \n\n\n\n- 1.11.“ **Privacy Laws** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.12.“ **Product** ” means any product which the SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.13.“ **Purchase Order** ” means any document which the SDI and the Supplier enter into which contemplates a transaction under which the Supplier is to deliver certain Products or Works to, or provide certain Services to, the SE; \n\n- 1.14.“ **SE** ” means the relevant Schneider Electric India entity on whose behalf SDI will place the Purchase Order on the Supplier, which shall include any of the following Schneider Electric India entities mentioned below: \n\n   - 1.14.1.Schneider Electric India Private Limited; \n\n   - 1.14.2.Schneider Electric Private Limited; \n\n   - 1.14.3.Schneider Electric IT Business India Private Limited \n\n   - 1.14.4.Schneider Electric President Systems Limited \n\n   - 1.14.5.Schneider Electric Infrastructure Limited \n\n   - 1.14.6.Schneider Electric Systems India Private Limited (formerly known as Invensys India Private Limited) \n\n   - 1.14.7.Eurotherm India Private Limited \n\n   - 1.14.8.Energy Grid Automation Transformers &amp; Switchgear India Private Limited; and \n\n   - 1.14.9.Schneider Electric Solar India Private Limited.']</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The document does not state any minimum order value or monetary threshold for a Purchase Order. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9999999999666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.01824678317384411</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>How many days of paid leave are the Supplier's on-site personnel entitled to?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', "context 2:\n## 17. SET-OFF\n\nSDI (in consultation with SE) may withhold amounts due under this Agreement on account of:  (a) claims arising out of or related to Supplier's breach or reasonably anticipated breach of this Agreement, (b) any amounts owed by Supplier to SE and/or SDI under this Agreement or otherwise; (c) non-conforming or deficient Services not yet corrected; (d) a reasonable doubt that Supplier can complete the Services for the unpaid portion of the Agreement price; or (e) any amounts owed by Supplier to SE and/or SDI or to an Affiliate under any other contracts, claims, demands, lawsuits or other matters.  If amounts owed by Supplier to SE and/or SDI exceed the unpaid balance of this Agreement, Supplier agrees to pay those amounts within forty-five calendar days after receipt of SDI’s notice identifying the amounts due.", 'context 3:\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Not addressed. This is a purchase T&amp;C, not an employment contract; it expressly states the Supplier's personnel are independent and not employees of SE/SDI, but says nothing about their leave entitlements. The correct response is that this is not covered.</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.07823683174726326</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>In which currency must invoices be denominated?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>["context 1:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'context 2:\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.', 'context 3:\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.']</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The document does not specify a currency for invoices. It details required invoice fields, taxes and GST handling, but no currency is stated. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.01623632649160952</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>List every distinct deadline or response window the Supplier must observe across the whole contract.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'context 2:\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', "context 3:\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>According to the contract, the key dates and timeframes that the Supplier needs to meet are:
+1. **Compliance Notice Response (8.4):**
+   - The Supplier must repair, rectify, or replace the Defective Items within the period specified in the Compliance Notice by SDI (in consultation with SE). 
+   - If no period is specified, the Supplier must act within **fifteen (15) working days** from the date of the Compliance Notice.
+2. **Challenge Period (4. Invoicing and Payment Terms):**
+   - The Supplier has **fifteen (15) days** from the issuance of a debit note by SDI to challenge it.
+3. **Export Controls Information (23. Export Controls and Compliance):**
+   - The Supplier must supply information on export controls and required permits or licenses within **three (3) working days** from receiving a Purchase Order.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Examples spanning the document: 15 days to challenge a debit note (Art. 4); 5 working days to respond to an Alteration Notice (Art. 15.1); 7 days to act after a Reminder Notice if none specified (Art. 6.3); 30 days to rectify a rectifiable breach (Art. 14.1(b)); 15 working days to repair/replace a Defective Item if none specified (Art. 8.4); 3 working days to supply export-control info after PO receipt (Art. 23); 24 hours to notify a Security Incident (Art. 31.3); 45 calendar days to pay set-off amounts (Art. 17). A complete answer requires sweeping the entire document.</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4511686888900219</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Summarize every scenario in which SE or SDI may withhold, deduct, or recover money from the Supplier.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'context 2:\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.', "context 3:\n## 17. SET-OFF\n\nSDI (in consultation with SE) may withhold amounts due under this Agreement on account of:  (a) claims arising out of or related to Supplier's breach or reasonably anticipated breach of this Agreement, (b) any amounts owed by Supplier to SE and/or SDI under this Agreement or otherwise; (c) non-conforming or deficient Services not yet corrected; (d) a reasonable doubt that Supplier can complete the Services for the unpaid portion of the Agreement price; or (e) any amounts owed by Supplier to SE and/or SDI or to an Affiliate under any other contracts, claims, demands, lawsuits or other matters.  If amounts owed by Supplier to SE and/or SDI exceed the unpaid balance of this Agreement, Supplier agrees to pay those amounts within forty-five calendar days after receipt of SDI’s notice identifying the amounts due."]</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SE or SDI can take back or keep money from the Supplier in the following cases:
+1. **Under Article 14.2 (Termination for Default):**
+   - SE has the sole discretion to return to the Supplier any Products or Works which it has received.
+   - The Supplier shall repay to SDI the price for any Products or Works which SDI has paid for but has either not received or has elected to return to the Supplier.
+2. **Under Article 17 (Set-Off):**
+   - SDI (in consultation with SE) may withhold amounts due under the Agreement on account of:
+     - Claims arising out of or related to the Supplier's breach or reasonably anticipated breach of the Agreement.
+     - Any amounts owed by the Supplier to SE and/or SDI under the Agreement or otherwise.
+     - Non-conforming or deficient Services not yet corrected.
+     - A reasonable doubt that the Supplier can complete the Services for the unpaid portion of the Agreement price.
+     - Any amounts owed by the Supplier to SE and/or SDI or to an Affiliate under any other contracts, claims, demands, lawsuits or other matters.
+If amounts owed by the Supplier to SE and/or SDI exceed the unpaid balance of the Agreement, the Supplier agrees to pay those amounts within forty-five calendar days after receipt of SDI’s notice identifying the amounts due.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Across the document these include: GST/input-tax-credit non-compliance withholding and recovery (Art. 5); debit notes for volume/quality/price disputes (Art. 4); set-off of amounts owed (Art. 17); liquidated damages for late delivery (Art. 6); repayment plus interest for Defective Items (Art. 8.4); deductions for losses from improper packing/shipping (Art. 21); and withholding money on third-party IP-infringement claims (Art. 12.1). A complete answer requires aggregating many sections.</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4393960243791236</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Overall, what are the main categories of obligation this contract places on the Supplier?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 20. ASSIGNMENT AND SUBCONTRACTING\n\nSDI shall have the right to assign its rights or obligations under the Agreement in part or in whole to any third party (including its affiliate) by notice to, but without consent of, the Supplier. However, the Supplier shall not assign or subcontract any obligation under the Agreement to any third party without the prior written consent of SDI. Without prejudice to the foregoing, SDI’s consent to the assignment or sub-contracting shall not release the Supplier from the obligations under the Agreement which have been assigned or subcontracted. Supplier assumes full responsibility to SE and SDI for the improper acts and omissions of its subcontractors or others employed or retained by Supplier in connection with the Agreement.', 'context 2:\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'context 3:\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).']</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The key responsibilities of the Supplier under this contract include:
+1. **Subcontracting and Assignment**:
+   - The Supplier shall not assign or subcontract any obligation under the Agreement to any third party without the prior written consent of SDI. 
+   - The Supplier assumes full responsibility for the improper acts or omissions of its subcontractors or others employed or retained by the Supplier in connection with the Agreement.
+2. **Export Controls and Compliance**:
+   - The Supplier acknowledges awareness of export and re-export controls regulations and is responsible for obtaining all necessary export and re-export permits or licenses at its own expense.
+   - The Supplier must supply SE and/or SDI with information regarding any applicable export controls and required permits or licenses within three (3) working days of receiving a Purchase Order.
+   - The Supplier must notify SE and SDI in writing of any changes to export and re-export controls regulations or licensing requirements that may affect SE’s benefits under the Agreement.
+   - The Supplier undertakes to comply with all export and re-export controls regulations and to indemnify SE and SDI against any liability, losses, damages, and expenses resulting from the Supplier’s non-compliance or violations.
+3. **Insurance**:
+   - The Supplier must maintain required insurance coverage for all Products, Services, Works, and raw materials during the term of the relevant Purchase Order and until the end of the corresponding Warranty Period, at its own cost.
+   - The Supplier must subscribe for insurance from reputable insurers satisfactory to SDI (in consultation with SE) and provide proof of such insurance and payment of insurance fees upon request.
+   - SDI (in consultation with SE) has the right to order the Supplier to suspend performance of a Purchase Order if the required proof of insurance coverage or compliance is not provided.
+These are the main responsibilities outlined in the given sections of the Agreement.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>High-level themes spanning the contract: deliver on time and to spec (Arts. 6, 8, 9); provide warranties and remedy defects (Art. 8); carry insurance (Art. 11); indemnify SE/SDI (Art. 10); respect and assign IP rights (Art. 12); maintain confidentiality (Arts. 1.4, 26); comply with tax/GST, export-control and other laws (Arts. 5, 22, 23); protect data and meet cyber-security minimums (Arts. 24, 31); supply documentation (Art. 25); and follow the Business Partner Code of Conduct (Art. 30). This is a whole-document synthesis.</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.3333333333</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5884413084553468</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>List all the ways a Purchase Order can be terminated under this contract and the condition for each.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>['context 1:\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'context 2:\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'context 3:\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>A Purchase Order can be cancelled or ended under this contract in the following methods and requirements:
+1. **Termination at Convenience (Article 13):**
+   - SDI (in consultation with SE) can terminate the Purchase Order in part or in whole without cause by giving 15 days' prior notice to the Supplier.
+   - The Supplier must:
+     - Immediately cease performance under the Purchase Order.
+     - Protect and hand over any ready Products and Works with relevant documentation.
+     - Use best efforts to terminate or assign existing orders with subcontractors or suppliers, as requested by SDI.
+   - The Supplier will be paid only for Products, Works, and Services that have been delivered or provided at the time of termination and meet the Agreement's requirements. No compensation for anticipated profits or other losses is allowed.
+2. **Change Order (Article 15):**
+   - SDI (in consultation with SE) can alter the scope of Products, Works, or Services via an Alteration Notice before delivery or completion.
+   - The Supplier must respond within five (5) working days:
+     - Indicating any additional cost and time required.
+     - Explaining why the alteration cannot be performed.
+     - Agreeing to perform the alteration without additional cost or time.
+   - If the Supplier fails to respond by the deadline, it is considered to agree to perform the Alteration Notice without additional charges or time.
+   - If the Supplier objects or SDI/SE disagree with the additional charges or time, SDI (in consultation with SE) can terminate the Purchase Order under Article 13.
+3. **Termination for Default (Article 14):**
+   - SDI (in consultation with SE) can terminate the Purchase Order immediately without compensation if the Supplier:
+     - Breaches any material provision of the Agreement and fails to rectify it within 30 days.
+     - Fails to deliver Products, Works, or complete Services as specified.
+     - Refuses to proceed with performance.
+     - Becomes insolvent, bankrupt, or performs an act that deprives SDI/SE of substantial benefits.
+   - SDI pays only for Products, Works, or Services received and kept by SE.
+   - The Supplier must repay the price for any Products or Works paid for but not received or returned.
+4. **Obligations Post-Termination:**
+   - Termination under Articles 13 or 14 does not affect the Supplier's obligations regarding Products, Works, or Services already delivered and paid for.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Termination at convenience: by SDI without cause on 15 days' notice (Art. 13). Termination for default: immediately, on a material breach, an unrectified breach (30 days), failure to deliver after a Reminder Notice, refusal to perform, or insolvency/bankruptcy (Art. 14). Via change order: if the parties cannot agree on a rejected/extra-cost Alteration Notice, SDI may terminate under Art. 13 (Art. 15.3). Delivery failure: termination after an unmet Reminder Notice period (Art. 6.3). Requires gathering distant sections.</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.3333333333</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6493441611810091</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>user_input</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>retrieved_contexts</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>context_recall</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>llm_context_precision_with_reference</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>faithfulness</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>semantic_similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What is the maximum cap on accumulated liquidated damages?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>['## 16. LIMITATION ON LIABILITY\n\nIn no event shall SE, SDI or their affiliates, employees, officers, and directors be liable for any punitive, consequential, incidental, special, or indirect damages, in any action arising from or related to this Agreement, whether based in contract, tort (including negligence), intended conduct or otherwise, including without limitation, damages relating to the loss of profits, business, income, savings, use, goodwill or revenue.  Notwithstanding anything contained herein, SE’s and/or  SDI’s maximum liability shall be limited to the payments to be made to Supplier on undisputed invoices.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.']</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The accumulated liquidated damages are capped at **10 % of the price of the related Purchase Order**.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10% of the Price of the related Purchase Order.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.615627404288304</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Which country's laws govern the Agreement?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>['## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', '## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.', '## 2. INTERPRETATION\n\n- 2.2. The provisions of these T&amp;C shall be interpreted according to the following rules: a) The article headings and marginal notes are for convenience of reference only and are not part of the Agreement, and shall not be taken into consideration in their construction and interpretation; \n\n   - b) Words importing persons shall include partnerships, firms, joint ventures, trusts, associations, companies and corporations and any organization or institution having legal capacity; \n\n   - c) Words importing the singular also include the plural and vice versa where the context requires. Words importing one gender also include other genders; \n\n   - d) With respect to the obligations that are binding on the Supplier under the Agreement, the Supplier shall also ensure that its subcontractors and suppliers comply with them to the extent applicable; and \n\ne) The words “including” or “includes” shall be deemed to be qualified by a reference to “without limitation”.', '## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.']</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The Agreement is governed by the laws of India.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The laws of India.</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6998807776087896</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>How many days does the Supplier have to challenge a debit note?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>["## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', '## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The Supplier has fifteen (15) days from the issuance of the debit note to challenge it.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>15 days from the issuing of the debit note.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8124670605011592</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Where will any arbitration proceeding take place?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>['## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', '## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.', '## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Any arbitration proceeding shall take place in New Delhi.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New Delhi.</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.520008088672027</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>If a vendor hands over goods late, how much can be docked for each week the shipment is overdue?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>['## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>For each week the goods are delivered late, the supplier may be charged liquidated damages equal to **1 % of the price of the undelivered products or works**. The total liquidated damages cannot exceed 10 % of the purchase‑order price.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1% of the Price of the undelivered Products/Works (or unprovided Services) per week of delay, capped overall at 10%.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5591995650645754</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Who foots the bill for obtaining the paperwork needed to ship products across borders legally?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>['## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', '## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', '## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The Supplier bears the cost of obtaining all required export‑re‑export permits, licenses and other shipping paperwork.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The Supplier, at its own expense, must obtain all necessary export and re-export permits or licenses.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8393643292979209</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>How soon does the seller get paid once the integrator has itself received money from the buyer?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>["## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', '## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The Supplier (seller) will be paid within five business days after SDI (the integrator) receives payment from SE (the buyer), provided all required documentation and invoice requirements are met.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Within 5 business days after SDI receives payment from SE (subject to correct invoicing and documentation).</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7798151251098774</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>If a buyer wants to walk away from an order even though the supplier did nothing wrong, how much advance warning must it give?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>['## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', '## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The buyer must give the supplier **15 days’ prior notice** before terminating the order without cause.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>15 days' prior notice (termination at convenience / without cause).</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5537582075859959</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Which ISO/IEC standards are named as the alignment benchmark for the Supplier's data-security safeguards?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>['## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', '## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', '## 1. DEFINITIONS\n\n- 1.4. “ **Confidential Information** ” means any and all information in any form that either Party provides to the other Party that either (i) has been marked or otherwise been identified as confidential; or (ii) is of such nature that a reasonable person would treat as confidential under like circumstances (regardless of whether it is disclosed before the execution of the Purchase Order (e.g., in any tendering documents inviting the Supplier to enter into the Purchase Order) or in the course of performing the Agreement), including, but not limited to, marketing and product plans, ideas, concepts, business plans, financial condition, employees and employee information, inventions, technical know-how, laboratory data, source codes, algorithms, decision technology and/or models, processes, designs, specifications, drawings, samples, improvements, developments, applications, engineering, manufacturing and marketing data and plans, software code (object and source), documentation, and functionality, security procedures and approaches, know-how, customer names and information, experimental work, distribution arrangements and trade secrets, and/or ideas. Confidential Information does not include any information which (i) is already known to the other Party at the time of disclosure; (ii) is independently developed without the benefit of the other Party’s Confidential Information; (iii) is received from a third party that is not under any confidentiality obligation towards the owner of the information; or (iv) has entered the public domain through no fault of the recipient;']</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The Supplier’s data‑security safeguards must be aligned with **ISO/IEC 27001** and **IEC 62443**.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001 or IEC 62443.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6573730108509093</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Under which Act will disputes be settled by arbitration?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>['## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', '## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.', '## 2. INTERPRETATION\n\n- 2.2. The provisions of these T&amp;C shall be interpreted according to the following rules: a) The article headings and marginal notes are for convenience of reference only and are not part of the Agreement, and shall not be taken into consideration in their construction and interpretation; \n\n   - b) Words importing persons shall include partnerships, firms, joint ventures, trusts, associations, companies and corporations and any organization or institution having legal capacity; \n\n   - c) Words importing the singular also include the plural and vice versa where the context requires. Words importing one gender also include other genders; \n\n   - d) With respect to the obligations that are binding on the Supplier under the Agreement, the Supplier shall also ensure that its subcontractors and suppliers comply with them to the extent applicable; and \n\ne) The words “including” or “includes” shall be deemed to be qualified by a reference to “without limitation”.', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Disputes will be settled by arbitration under the Arbitration and Conciliation Act, 1996.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The Arbitration and Conciliation Act, 1996 (referred to as 'IAC').</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6194351527120757</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>List the Quality Assessment Standards the Products must comply with under the warranty.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>['## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', '## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Products must comply with the following Quality Assessment Standards under the warranty:
+- ISO 9000  
+- ISO 26000  
+- ISO 14001  
+- ISO 50001  </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ISO9000, ISO26000, ISO14001 and ISO 50001 (or other internationally recognized applicable standards).</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.686011150265154</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>What is the proprietary web-based tool through which Suppliers must submit invoices?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', '## 1. DEFINITIONS\n\n- 1.9. “ **Payment Documentation** ” means all documents which are either a) specified in the Purchase Order which must be sent and approved by SDI as the condition for the payment of the Price; or b) if the relevant Purchase Order fails to specify the Payment Documentation: (i) a commercial invoice correctly stating the Price, (ii) (if applicable) a photocopy / original copy of the Final Acceptance Certificate bearing the SE’s (or its representative’s) signature; and (iii) if any third party Intellectual Property Right is involved in the manufacture, use, or delivery of the Products, Works or Services, all necessary documents or certificates which prove that the SE has the right to use, sell, or otherwise dispose the Products, the Works, or the Services; \n\n- 1.10.“ **Price** ” means the price for the Products, the Works or Services which SDI is obliged to pay to the Supplier under a relevant Purchase Order; \n\n\n\n- 1.11.“ **Privacy Laws** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.12.“ **Product** ” means any product which the SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.13.“ **Purchase Order** ” means any document which the SDI and the Supplier enter into which contemplates a transaction under which the Supplier is to deliver certain Products or Works to, or provide certain Services to, the SE; \n\n- 1.14.“ **SE** ” means the relevant Schneider Electric India entity on whose behalf SDI will place the Purchase Order on the Supplier, which shall include any of the following Schneider Electric India entities mentioned below: \n\n   - 1.14.1.Schneider Electric India Private Limited; \n\n   - 1.14.2.Schneider Electric Private Limited; \n\n   - 1.14.3.Schneider Electric IT Business India Private Limited \n\n   - 1.14.4.Schneider Electric President Systems Limited \n\n   - 1.14.5.Schneider Electric Infrastructure Limited \n\n   - 1.14.6.Schneider Electric Systems India Private Limited (formerly known as Invensys India Private Limited) \n\n   - 1.14.7.Eurotherm India Private Limited \n\n   - 1.14.8.Energy Grid Automation Transformers &amp; Switchgear India Private Limited; and \n\n   - 1.14.9.Schneider Electric Solar India Private Limited.', '## 19. INDEPENDENT SUPPLIER\n\nSupplier and his employees, agents, representatives, assigns, sub-suppliers etc. are independent suppliers and shall not be construed as agents, representatives, or employees of SE and/or SDI.']</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Suppliers must submit invoices via SDI’s proprietary web‑based tool, **Work Nexus®**.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Work Nexus(R), SDI's proprietary web-based tool.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5905263093023966</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A non-MSME supplier delivers goods two weeks late. Explain both the payment timeline that applies and the penalty for the delay.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>['## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', '## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>**Payment timeline for a non‑MSME supplier**
+1. **SE’s payment to SDI** – SE must pay SDI within **net 70 days** from the date SE receives the invoice.  
+2. **SDI’s payment to the Supplier** – Once SDI has received SE’s payment, SDI will process the Supplier’s payment **within five (5) business days**, provided that:
+   - all required documentation and the invoice are in the correct form, and  
+   - any debit‑note dispute (if any) has been resolved.
+So the Supplier will receive payment no later than 70 days + 5 business days after the invoice is issued, assuming all conditions are met.
+**Penalty for the two‑week delay**
+- Under clause 6.1(b), liquidated damages are **1 % of the Purchase Order price for each week of delay**.
+- A two‑week delay therefore incurs **2 % of the price** as liquidated damages (subject to the overall cap of 10 % of the Purchase Order price).
+- In addition, any extra costs incurred by SDI because of the late delivery (e.g., air‑shipping, extra manpower) are to be borne by the Supplier under clause 6.2.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Payment: SE pays SDI on Net 70-day terms for non-MSME vendors (from SE's receipt of invoice), and the Supplier is paid within 5 business days after SDI receives payment from SE. Penalty: liquidated damages of 1% of Price per week of delay, so ~2% for two weeks, subject to the overall 10% cap.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8478288286147204</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>What are the notice periods for terminating a Purchase Order for convenience versus for an unrectified breach?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>['## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', '## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.']</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>- **Termination for convenience:** The Supplier must be given **15 days’ prior notice** (Art. 13.1).
+- **Termination for an unrectified breach:** The Supplier must be given **30 days to rectify the breach** after receiving the notice; if the breach is not remedied within that 30‑day period, SDI may terminate (Art. 14.1 (b)).</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Termination at convenience requires 15 days' prior notice. Termination for default for a rectifiable breach allows termination if the Supplier fails to rectify within 30 days of SDI's notice.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9353447158237396</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>When does title pass to SE, and when does risk pass to SE, and why are they different points in time?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>['## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', '## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', '## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', '## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.']</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>**Title**
+Title and ownership of the Products, Works, or Services pass to SE when either  
+1. the Products or Works are delivered to the Delivery Point (or the Services are completed), **or**  
+2. a Purchase Order is terminated before delivery/completion, at the moment the Supplier receives the termination notice (as per Articles 13 and 14).
+**Risk**
+Risk of loss or damage remains with the Supplier **until the Supplier receives the Final Acceptance Certificate**. The issuance of that certificate does not relieve the Supplier of its other obligations under Article 8.
+**Why the two moments differ**
+Title can pass at delivery (or upon termination) to give SE ownership of the items, but the Supplier continues to bear the risk until SE formally accepts the goods/services through the Final Acceptance Certificate. This separation ensures that SE owns the items while the Supplier remains responsible for any loss, damage, or defects that may arise before the final acceptance is granted.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Title/ownership vests with SE when the Products/Works are delivered to the Delivery Point or the Services are completed. Risk, however, remains with the Supplier until the Supplier receives the Final Acceptance Certificate. So title can transfer before risk does.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7565000328836509</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>For a product found defective during the warranty period, what are the Supplier's options and the associated interest rate and time limit?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>['## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', '## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>If a product is deemed defective during the Warranty Period, the Supplier may:
+1. **Collect and repay** – at its own cost, retrieve the defective items and repay the price to SDI (or the designated customer) **with interest of 2 % above the prevailing prime lending rate**, calculated from the date SDI paid the price, and also compensate SE and SDI for any related losses; **or**
+2. **Repair, rectify or replace** – at its own cost, cure the defect **within the time‑frame specified in the Compliance Notice** (or, if no period is specified, within **fifteen (15) working days** from the date of the Compliance Notice).</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>At SDI's election the Supplier must either (a) collect the defective items and repay the Price with interest at 2% above the prevailing prime lending rate (plus compensate losses), or (b) repair/rectify/replace within the period specified, defaulting to 15 working days. The warranty period is, by default, 12 months.</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8544848862723662</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>What event triggers a 'Compliance Notice', and what must the Supplier do once it receives one? Use the document's own definitions.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>['## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 1. DEFINITIONS\n\nFor the purpose of, these General Terms and Conditions of Purchase (“T&amp;C”), the following terms shall have the meaning hereby assigned to them unless the context would obviously require otherwise:\n- 1.1. “ **Agreement”** means these T&amp;C and the Purchase Order, collectively;\n- 1.2. “ **Alteration Notice** ” shall have the meaning set out in Art. 15 of these T&amp;C;\n- 1.3. “ **Compliance Notice** ” shall have the meaning set out in Art. 8.4 of these T&amp;C; SDI will provide such a notice to Supplier via e-mail upon being requested to do so by SE.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A **Compliance Notice** is issued by SDI (by e‑mail) when SE asks SDI to do so – typically because a defect or non‑conformity has been identified during testing, inspection or acceptance.  
+Once the Supplier receives the Compliance Notice, it must, at SE’s election, **retrieve, replace, or rectify the defects** in accordance with Art. 8.4 of the T&amp;C.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>The definition of 'Compliance Notice' points to Art. 8.4. It is triggered when SE finds (itself or via a customer) that any Product/Work/Service is a 'Defective Item' during the Warranty Period. On receipt, the Supplier must, at SDI's election, either repay the Price plus 2% above prime lending rate (and compensate losses), or repair/replace within 15 working days.</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3333333333</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8754376290964385</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>If a Purchase Order does not state a warranty period for a Service, when does the warranty begin and how long does it last?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>['## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', '## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>If the Purchase Order does not specify a warranty period for a Service, the warranty starts on the later of (a) the date SE issues the Final Acceptance Certificate for that Service or (b) the date the Services are completed. The warranty then lasts for twelve (12) months from that start date.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>It lasts 12 months, running from the date SE issues the Final Acceptance Certificate for the Services or from when the Services are completed, whichever is later. (This requires combining the 'Warranty Period' default with the 'Final Acceptance Certificate' concept.)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8059430248304261</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A supplier has separately negotiated and executed a services agreement. A conflict then arises between that agreement, the Purchase Order, and these T&amp;C. Which prevails, and how do you know?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>['## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', '## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', '## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', '## 20. ASSIGNMENT AND SUBCONTRACTING\n\nSDI shall have the right to assign its rights or obligations under the Agreement in part or in whole to any third party (including its affiliate) by notice to, but without consent of, the Supplier. However, the Supplier shall not assign or subcontract any obligation under the Agreement to any third party without the prior written consent of SDI. Without prejudice to the foregoing, SDI’s consent to the assignment or sub-contracting shall not release the Supplier from the obligations under the Agreement which have been assigned or subcontracted. Supplier assumes full responsibility to SE and SDI for the improper acts and omissions of its subcontractors or others employed or retained by Supplier in connection with the Agreement.']</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>The services agreement that the parties have specifically negotiated and executed will prevail.  
+Clause 2.1 states that if there is an inconsistency between the Purchase Order and these T&amp;C, the T&amp;C win. However, it adds: *“Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.”*  
+Therefore, when a conflict exists among the services agreement, the Purchase Order, and the T&amp;C, the services agreement overrides the other two documents.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Normally the T&amp;C prevail over an inconsistent Purchase Order. However, where the parties specifically negotiate and execute a services agreement, that services agreement prevails over the T&amp;C to the extent of any conflict. (The Order of Precedence on p.1 plus Art. 2.1 establish this.)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9155565705324968</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>At what exact point are Products considered 'delivered' so that the payment process can begin? Pull together every condition the document attaches.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>['## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 1. DEFINITIONS\n\n- 1.5. “ **Defective Item** ” shall have the meaning set out in Art. 8.4 of these T&amp;C;\n- 1.6. “ **Delivery Point** ” means the location which the Purchase Order stipulates for the delivery of the Products or the Works or the Services or, if the Purchase Order fails to specify such location, a location of which the SE or SDI may notify to the Supplier within a reasonable period before the scheduled delivery date;\n- 1.7. “ **Final Acceptance Certificate** ” means the document which the SE, or its duly authorized representative, issues to the Supplier confirming that the Products, the Works or the Services comply with requirements under the Agreement, after having a reasonable opportunity to examine them according to Art. 9.3 of these T&amp;C;\n- 1.8. “ **Intellectual Property Right** ” means any intellectual property right, regardless of whether registered or not, including any: (i) patent, (ii) copyright (including moral right and author’s right); (iii) database right; (iv) know-how or trade secret, whether or not developed or reduced to practice; (v) industrial design; (vi) trademark, service mark, logo, domain name and keyword, and the goodwill associated with them; (vii) right of publicity; and (viii) any other proprietary right relating to intangible property anywhere in the world;', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>**Products (or Works) are deemed “delivered” only when all of the following conditions are satisfied (per Clause 6.4):**
+1. **Placement at the Delivery Point** – All Products and Works under the Purchase Order have been placed at the stipulated Delivery Point and are ready for pick‑up or use.  
+2. **Supplier Notification** – SE and SDI have received a notification from the Supplier confirming that delivery and completion have occurred.  
+3. **Required Documentation** – All documents listed in Article 24 of the Terms &amp; Conditions have been received by SE and SDI.  
+4. **Final Acceptance (if applicable)** – If any Product, Work, or Service requires replacement or repair under Article 8.4, the delivery of the Product/Work and the completion of the Service must be accompanied by a **Final Acceptance Certificate** issued by SE (or its authorized representative).  
+Only when these four criteria are met are the Products considered delivered, allowing the subsequent invoicing and payment process to proceed.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Products/Works are not considered delivered until: (a) all are placed at the Delivery Point ready for pickup/use; (b) SE and SDI receive the Supplier's delivery/completion notification; (c) all required documents are received; and (d) where repair/replacement applied, the relevant Final Acceptance Certificate is issued. Only once delivery is complete and a compliant invoice is submitted does the payment timeline run.</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.8333333332916666</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.8251159862527987</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>What late-payment interest rate must SDI pay the Supplier if SDI pays after the due date?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>['## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.']</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>The document does not specify any late-payment interest payable by SDI to the Supplier. (It specifies interest on defective-item repayments and on GST/credit reversals, but not a penalty for SDI's late payment.) The correct response is that this is not stated.</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.249999999975</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.051666416740992</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>What is the minimum order value or monetary threshold required to raise a Purchase Order under these terms?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>['## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', '## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', '## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', '## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).']</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The document does not state any minimum order value or monetary threshold for a Purchase Order. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.01824678317384411</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>How many days of paid leave are the Supplier's on-site personnel entitled to?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>['## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Not addressed. This is a purchase T&amp;C, not an employment contract; it expressly states the Supplier's personnel are independent and not employees of SE/SDI, but says nothing about their leave entitlements. The correct response is that this is not covered.</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5833333333041666</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.07823683174726326</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>In which currency must invoices be denominated?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>["## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', '## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', '## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The document does not specify a currency for invoices. It details required invoice fields, taxes and GST handling, but no currency is stated. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.01623632649160952</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>List every distinct deadline or response window the Supplier must observe across the whole contract.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>['## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>**Deadlines / response windows that the Supplier must observe (as set out in the provided terms):**
+1. **Delivery deadline after a Reminder Notice**  
+   - The Supplier must deliver the Products, Works or complete the Services **within the period specified in the Reminder Notice**.  
+   - **If the Reminder Notice does not specify a period**, the Supplier must deliver **within seven (7) days** from the date of that Reminder Notice.  
+2. **Challenge of a Debit Note**  
+   - When SDI issues a debit note, the Supplier has **fifteen (15) days** from the date of issuance to challenge it.  
+3. **Warranty‑period obligations** (ongoing service windows)  
+   - For Products: **12 months** after delivery *or* after SE issues a Final Acceptance Certificate (whichever is later).  
+   - For Services: **12 months** after SE issues a Final Acceptance Certificate for the Services (or from the date the Services are completed, whichever is later).  
+   - For repaired/replaced Products or Works: **12 months** after the repair or replacement delivery.  
+These are the only explicit time‑frames in the excerpt that require the Supplier to act or respond.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Examples spanning the document: 15 days to challenge a debit note (Art. 4); 5 working days to respond to an Alteration Notice (Art. 15.1); 7 days to act after a Reminder Notice if none specified (Art. 6.3); 30 days to rectify a rectifiable breach (Art. 14.1(b)); 15 working days to repair/replace a Defective Item if none specified (Art. 8.4); 3 working days to supply export-control info after PO receipt (Art. 23); 24 hours to notify a Security Incident (Art. 31.3); 45 calendar days to pay set-off amounts (Art. 17). A complete answer requires sweeping the entire document.</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5641497053694805</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Summarize every scenario in which SE or SDI may withhold, deduct, or recover money from the Supplier.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>['## 16. LIMITATION ON LIABILITY\n\nIn no event shall SE, SDI or their affiliates, employees, officers, and directors be liable for any punitive, consequential, incidental, special, or indirect damages, in any action arising from or related to this Agreement, whether based in contract, tort (including negligence), intended conduct or otherwise, including without limitation, damages relating to the loss of profits, business, income, savings, use, goodwill or revenue.  Notwithstanding anything contained herein, SE’s and/or  SDI’s maximum liability shall be limited to the payments to be made to Supplier on undisputed invoices.', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', '## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.', '## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.']</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>**Scenarios in which SE or SDI may withhold, deduct, or recover money from the Supplier**
+1. **Intellectual‑property infringement claims**  
+   * If a third party alleges (or threatens) that the Supplier’s Products, Works or Services infringe any Intellectual Property Right, SE and/or SDI may:  
+   – Withhold any money that is due or payable to the Supplier, and/or  
+   – Require the Supplier to provide additional security (an amount deemed reasonable by SE/SDI).  
+2. **Breach of the Purchase Order or the Terms &amp; Conditions**  
+   * When the Supplier breaches any obligation under the Purchase Order or these T&amp;C, causing consequential or incidental losses to SE or SDI, the Supplier must indemnify SE/SDI for all resulting liabilities, losses, damages, and expenses (including reasonable attorney’s fees).  
+   – SE/SDI can therefore recover those amounts from the Supplier (e.g., by offsetting them against payments).  
+These are the only circumstances described in the provided excerpts where SE or SDI have a contractual right to withhold, deduct, or recover funds from the Supplier.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Across the document these include: GST/input-tax-credit non-compliance withholding and recovery (Art. 5); debit notes for volume/quality/price disputes (Art. 4); set-off of amounts owed (Art. 17); liquidated damages for late delivery (Art. 6); repayment plus interest for Defective Items (Art. 8.4); deductions for losses from improper packing/shipping (Art. 21); and withholding money on third-party IP-infringement claims (Art. 12.1). A complete answer requires aggregating many sections.</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5562358863563432</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Overall, what are the main categories of obligation this contract places on the Supplier?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>['## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', '## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.', '## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.']</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The contract imposes the following broad categories of obligations on the Supplier:
+1. **Product and Service Warranty / Quality Guarantees** –  
+   - Warranty that the Supplier has full rights to manufacture, deliver and sell the Products, Works and Services (8.1).  
+   - Guarantees that the Products are new, well‑manufactured, defect‑free, fit for purpose, and meet the applicable quality standards (ISO 9000, ISO 26000, ISO 14001, ISO 5001, etc.) (8.2).
+2. **Data Protection and Cyber‑Security** –  
+   - Access, collection, storage and processing of SE/SDI data only for the purpose of fulfilling the Purchase Order and in accordance with written permission (31.1.i).  
+   - Implementation of appropriate administrative, technical and organisational safeguards (ISO/IEC 27001, IEC 62443) (31.1.ii‑v).  
+   - Maintenance of a business‑continuity plan addressing data‑ and cyber‑risk (31.2).  
+   - Prompt breach‑notification (within 24 hours) and cooperation in investigating any security incident (31.3).
+3. **Documentation Requirements** –  
+   - Delivery of drawings, manuals, certificates, inspection statements, warranty certificates and any necessary third‑party IP licences on or before delivery/completion (25.1).  
+   - Assurance that all documentation is accurate, error‑free and in English (unless otherwise stated) (25.2).
+4. **Export‑Control and Regulatory Compliance** –  
+   - Knowledge of, and compliance with, all applicable export and re‑export control laws; obtaining required licences at the Supplier’s expense (23).  
+   - Supplying SE/SDI with export‑control information within three working days of receiving the Purchase Order and notifying any regulatory changes (23).  
+   - Indemnifying SE and SDI for any loss resulting from non‑compliance (23).
+5. **Additional Operational Obligations** –  
+   - Maintaining a reasonable business continuity plan (31.2).  
+   - Cooperating with SE/SDI in investigations, remediation and any required addenda for enhanced data protection (31.3‑31.4).  
+These categories together constitute the Supplier’s core contractual duties.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>High-level themes spanning the contract: deliver on time and to spec (Arts. 6, 8, 9); provide warranties and remedy defects (Art. 8); carry insurance (Art. 11); indemnify SE/SDI (Art. 10); respect and assign IP rights (Art. 12); maintain confidentiality (Arts. 1.4, 26); comply with tax/GST, export-control and other laws (Arts. 5, 22, 23); protect data and meet cyber-security minimums (Arts. 24, 31); supply documentation (Art. 25); and follow the Business Partner Code of Conduct (Art. 30). This is a whole-document synthesis.</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6848746609406239</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>List all the ways a Purchase Order can be terminated under this contract and the condition for each.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>['## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', '## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', '## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>**Ways a Purchase Order can be terminated and the condition for each**
+| Termination route | Condition(s) that trigger it |
+|-------------------|------------------------------|
+| **1. Termination at convenience (Art. 13.1)** | SDI (in consultation with SE) may terminate a Purchase Order, in whole or in part, **without cause** by giving the Supplier **15 days’ prior notice**. |
+| **2. Termination for default (Art. 14.1)** | SDI (in consultation with SE) may terminate a Purchase Order, in whole or in part, **with immediate effect and without compensation** if any of the following occurs: &lt;ul&gt;&lt;li&gt;**a.** The Supplier breaches a **material provision** of the Agreement.&lt;/li&gt;&lt;li&gt;**b.** The Supplier breaches any provision of the Agreement **and fails to remedy the breach within 30 days** after receiving notice from SDI (in consultation with SE).&lt;/li&gt;&lt;li&gt;**c.** The Supplier **fails to deliver** the Products or Works, or **fails to complete** the Services as required under Art. 6.3.&lt;/li&gt;&lt;li&gt;**d.** The Supplier **refuses to proceed** with performance of the relevant Purchase Order.&lt;/li&gt;&lt;li&gt;**e.** The Supplier becomes **insolvent or bankrupt**, files a petition for voluntary winding‑up (except for reorganization), appoints a receiver, is placed under judicial management, assigns substantial assets to creditors, **or** does any act that, in SDI’s view (in consultation with SE), may deprive SE or SDI of a substantial benefit under the Purchase Order or the Agreement.&lt;/li&gt;&lt;/ul&gt; |
+These are the only termination mechanisms described in the provided contract terms.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Termination at convenience: by SDI without cause on 15 days' notice (Art. 13). Termination for default: immediately, on a material breach, an unrectified breach (30 days), failure to deliver after a Reminder Notice, refusal to perform, or insolvency/bankruptcy (Art. 14). Via change order: if the parties cannot agree on a rejected/extra-cost Alteration Notice, SDI may terminate under Art. 13 (Art. 15.3). Delivery failure: termination after an unmet Reminder Notice period (Art. 6.3). Requires gathering distant sections.</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7034872348940548</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/baseline_scores.xlsx
+++ b/baseline_scores.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="section_aware_chunking" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quey_rewriter" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hyde_expander_fusion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hyde_expander_contextual_retriever_fusion_rerank" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -4777,7 +4778,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['## 16. LIMITATION ON LIABILITY\n\nIn no event shall SE, SDI or their affiliates, employees, officers, and directors be liable for any punitive, consequential, incidental, special, or indirect damages, in any action arising from or related to this Agreement, whether based in contract, tort (including negligence), intended conduct or otherwise, including without limitation, damages relating to the loss of profits, business, income, savings, use, goodwill or revenue.  Notwithstanding anything contained herein, SE’s and/or  SDI’s maximum liability shall be limited to the payments to be made to Supplier on undisputed invoices.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.']</t>
+          <t>['Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets the liability limits for Schneider Electric and SDI under the purchase agreement and excludes most indirect damages while capping their maximum exposure to undisputed supplier invoice payments\n## 16. LIMITATION ON LIABILITY\n\nIn no event shall SE, SDI or their affiliates, employees, officers, and directors be liable for any punitive, consequential, incidental, special, or indirect damages, in any action arising from or related to this Agreement, whether based in contract, tort (including negligence), intended conduct or otherwise, including without limitation, damages relating to the loss of profits, business, income, savings, use, goodwill or revenue.  Notwithstanding anything contained herein, SE’s and/or  SDI’s maximum liability shall be limited to the payments to be made to Supplier on undisputed invoices.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.']</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4794,7 +4795,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.49999999995</v>
+        <v>0.9999999999</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -4811,7 +4812,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', '## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.', '## 2. INTERPRETATION\n\n- 2.2. The provisions of these T&amp;C shall be interpreted according to the following rules: a) The article headings and marginal notes are for convenience of reference only and are not part of the Agreement, and shall not be taken into consideration in their construction and interpretation; \n\n   - b) Words importing persons shall include partnerships, firms, joint ventures, trusts, associations, companies and corporations and any organization or institution having legal capacity; \n\n   - c) Words importing the singular also include the plural and vice versa where the context requires. Words importing one gender also include other genders; \n\n   - d) With respect to the obligations that are binding on the Supplier under the Agreement, the Supplier shall also ensure that its subcontractors and suppliers comply with them to the extent applicable; and \n\ne) The words “including” or “includes” shall be deemed to be qualified by a reference to “without limitation”.', '## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.']</t>
+          <t>['This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'This section appears in the General Terms and Conditions of Purchase governing Schneider Electric orders placed by SDI and sets a legal compliance obligation for the Supplier within the broader procurement agreement.\n## 22. COMPLIANCE WITH LAWS\n\nThe Supplier shall comply with all applicable laws in its performance of the Agreement, including without limitation, those set forth in Art. 22 and 23 of these T&amp;C.', 'This section sets the communication rules for the purchase agreement requiring all notices and correspondence between the Supplier and SDI to be in English and sent only through the contact details specified in the Purchase Order unless updated in writing\n## 28. COMMUNICATIONS\n\nAll communications between the Supplier and SDI shall be in English and in the form of e-mails, faxes, or letters and shall be sent to the address or e-mail accounts, or contact numbers (as the case may be) as shown on the Purchase Order, unless one Party otherwise notifies the other Party in writing.', 'Section on data protection obligations defining SE and SDI content controller roles supplier safeguards breach notification and compliance with privacy laws for services performed under the purchase order\n## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.']</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4845,7 +4846,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>["## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', '## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4879,12 +4880,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', '## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.', '## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+          <t>['This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Any arbitration proceeding shall take place in New Delhi.</t>
+          <t>The arbitration proceeding shall take place in New Delhi.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4902,7 +4903,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.520008088672027</v>
+        <v>0.4785408990588863</v>
       </c>
     </row>
     <row r="6">
@@ -4913,12 +4914,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.']</t>
+          <t>['Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>For each week the goods are delivered late, the supplier may be charged liquidated damages equal to **1 % of the price of the undelivered products or works**. The total liquidated damages cannot exceed 10 % of the purchase‑order price.</t>
+          <t>For each week the shipment is overdue, the vendor may be charged liquidated damages equal to **1 % of the price of the undelivered products or works** (capped at a total of 10 % of the purchase‑order price).</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4930,13 +4931,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.49999999995</v>
+        <v>0.9999999999</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5591995650645754</v>
+        <v>0.6034509765624639</v>
       </c>
     </row>
     <row r="7">
@@ -4947,12 +4948,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', '## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', '## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+          <t>['This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'Section 25 of the purchase terms sets out the supplier documentation requirements for delivering products works or services including manuals certificates inspection records warranty certificates and third party IP licenses before delivery completion\n## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Supplier bears the cost of obtaining all required export‑re‑export permits, licenses and other shipping paperwork.</t>
+          <t>The Supplier bears the cost of obtaining all required export‑ and re‑export permits or licenses.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4967,10 +4968,10 @@
         <v>0.99999999995</v>
       </c>
       <c r="G7" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8393643292979209</v>
+        <v>0.8614760731114615</v>
       </c>
     </row>
     <row r="8">
@@ -4981,12 +4982,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>["## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', '## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.']</t>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C']</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The Supplier (seller) will be paid within five business days after SDI (the integrator) receives payment from SE (the buyer), provided all required documentation and invoice requirements are met.</t>
+          <t>The seller (Supplier) will be paid within five (5) business days after SDI receives payment from the buyer (SE), provided all required documentation and invoice requirements are met.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5004,7 +5005,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7798151251098774</v>
+        <v>0.8725046025314891</v>
       </c>
     </row>
     <row r="9">
@@ -5015,12 +5016,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', '## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.']</t>
+          <t>['Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The buyer must give the supplier **15 days’ prior notice** before terminating the order without cause.</t>
+          <t>The buyer must give the supplier **15 days’ prior notice** before terminating the purchase order for convenience.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5032,13 +5033,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9999999999</v>
+        <v>0.49999999995</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5537582075859959</v>
+        <v>0.5170079578445395</v>
       </c>
     </row>
     <row r="10">
@@ -5049,12 +5050,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', '## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', '## 1. DEFINITIONS\n\n- 1.4. “ **Confidential Information** ” means any and all information in any form that either Party provides to the other Party that either (i) has been marked or otherwise been identified as confidential; or (ii) is of such nature that a reasonable person would treat as confidential under like circumstances (regardless of whether it is disclosed before the execution of the Purchase Order (e.g., in any tendering documents inviting the Supplier to enter into the Purchase Order) or in the course of performing the Agreement), including, but not limited to, marketing and product plans, ideas, concepts, business plans, financial condition, employees and employee information, inventions, technical know-how, laboratory data, source codes, algorithms, decision technology and/or models, processes, designs, specifications, drawings, samples, improvements, developments, applications, engineering, manufacturing and marketing data and plans, software code (object and source), documentation, and functionality, security procedures and approaches, know-how, customer names and information, experimental work, distribution arrangements and trade secrets, and/or ideas. Confidential Information does not include any information which (i) is already known to the other Party at the time of disclosure; (ii) is independently developed without the benefit of the other Party’s Confidential Information; (iii) is received from a third party that is not under any confidentiality obligation towards the owner of the information; or (iv) has entered the public domain through no fault of the recipient;']</t>
+          <t>['This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'Section on data protection obligations defining SE and SDI content controller roles supplier safeguards breach notification and compliance with privacy laws for services performed under the purchase order\n## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The Supplier’s data‑security safeguards must be aligned with **ISO/IEC 27001** and **IEC 62443**.</t>
+          <t>The standards referenced are **ISO/IEC 27001** and **IEC 62443**.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5072,7 +5073,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6573730108509093</v>
+        <v>0.8621569084765314</v>
       </c>
     </row>
     <row r="11">
@@ -5083,12 +5084,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', '## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.', '## 2. INTERPRETATION\n\n- 2.2. The provisions of these T&amp;C shall be interpreted according to the following rules: a) The article headings and marginal notes are for convenience of reference only and are not part of the Agreement, and shall not be taken into consideration in their construction and interpretation; \n\n   - b) Words importing persons shall include partnerships, firms, joint ventures, trusts, associations, companies and corporations and any organization or institution having legal capacity; \n\n   - c) Words importing the singular also include the plural and vice versa where the context requires. Words importing one gender also include other genders; \n\n   - d) With respect to the obligations that are binding on the Supplier under the Agreement, the Supplier shall also ensure that its subcontractors and suppliers comply with them to the extent applicable; and \n\ne) The words “including” or “includes” shall be deemed to be qualified by a reference to “without limitation”.', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+          <t>['This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'Section on data protection obligations defining SE and SDI content controller roles supplier safeguards breach notification and compliance with privacy laws for services performed under the purchase order\n## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.']</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Disputes will be settled by arbitration under the Arbitration and Conciliation Act, 1996.</t>
+          <t>The disputes will be settled by arbitration under the Arbitration and Conciliation Act, 1996.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5106,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6194351527120757</v>
+        <v>0.575386581068467</v>
       </c>
     </row>
     <row r="12">
@@ -5117,16 +5118,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', '## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+          <t>['This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section covers testing inspection and acceptance procedures including SEs right to issue a Compliance Notice and require the supplier to retrieve replace or rectify defective items under the purchase terms\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.']</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Products must comply with the following Quality Assessment Standards under the warranty:
+          <t>The warranty requires the Products to comply with the following Quality Assessment Standards:
 - ISO 9000  
 - ISO 26000  
 - ISO 14001  
-- ISO 50001  </t>
+- ISO 50001  
+(and any other internationally recognized standards applicable to the manufacture and delivery of the Products).</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5144,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.686011150265154</v>
+        <v>0.7002309898979174</v>
       </c>
     </row>
     <row r="13">
@@ -5155,12 +5157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>["## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', '## 1. DEFINITIONS\n\n- 1.9. “ **Payment Documentation** ” means all documents which are either a) specified in the Purchase Order which must be sent and approved by SDI as the condition for the payment of the Price; or b) if the relevant Purchase Order fails to specify the Payment Documentation: (i) a commercial invoice correctly stating the Price, (ii) (if applicable) a photocopy / original copy of the Final Acceptance Certificate bearing the SE’s (or its representative’s) signature; and (iii) if any third party Intellectual Property Right is involved in the manufacture, use, or delivery of the Products, Works or Services, all necessary documents or certificates which prove that the SE has the right to use, sell, or otherwise dispose the Products, the Works, or the Services; \n\n- 1.10.“ **Price** ” means the price for the Products, the Works or Services which SDI is obliged to pay to the Supplier under a relevant Purchase Order; \n\n\n\n- 1.11.“ **Privacy Laws** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.12.“ **Product** ” means any product which the SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.13.“ **Purchase Order** ” means any document which the SDI and the Supplier enter into which contemplates a transaction under which the Supplier is to deliver certain Products or Works to, or provide certain Services to, the SE; \n\n- 1.14.“ **SE** ” means the relevant Schneider Electric India entity on whose behalf SDI will place the Purchase Order on the Supplier, which shall include any of the following Schneider Electric India entities mentioned below: \n\n   - 1.14.1.Schneider Electric India Private Limited; \n\n   - 1.14.2.Schneider Electric Private Limited; \n\n   - 1.14.3.Schneider Electric IT Business India Private Limited \n\n   - 1.14.4.Schneider Electric President Systems Limited \n\n   - 1.14.5.Schneider Electric Infrastructure Limited \n\n   - 1.14.6.Schneider Electric Systems India Private Limited (formerly known as Invensys India Private Limited) \n\n   - 1.14.7.Eurotherm India Private Limited \n\n   - 1.14.8.Energy Grid Automation Transformers &amp; Switchgear India Private Limited; and \n\n   - 1.14.9.Schneider Electric Solar India Private Limited.', '## 19. INDEPENDENT SUPPLIER\n\nSupplier and his employees, agents, representatives, assigns, sub-suppliers etc. are independent suppliers and shall not be construed as agents, representatives, or employees of SE and/or SDI.']</t>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section sets the rules for assigning rights and subcontracting obligations under the purchase agreement including SDIs right to transfer its interests and the Suppliers need for prior written consent to subcontract or assign work\n## 20. ASSIGNMENT AND SUBCONTRACTING\n\nSDI shall have the right to assign its rights or obligations under the Agreement in part or in whole to any third party (including its affiliate) by notice to, but without consent of, the Supplier. However, the Supplier shall not assign or subcontract any obligation under the Agreement to any third party without the prior written consent of SDI. Without prejudice to the foregoing, SDI’s consent to the assignment or sub-contracting shall not release the Supplier from the obligations under the Agreement which have been assigned or subcontracted. Supplier assumes full responsibility to SE and SDI for the improper acts and omissions of its subcontractors or others employed or retained by Supplier in connection with the Agreement.']</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Suppliers must submit invoices via SDI’s proprietary web‑based tool, **Work Nexus®**.</t>
+          <t>Suppliers must submit invoices through SDI’s proprietary web‑based tool, **Work Nexus®**.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5178,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5905263093023966</v>
+        <v>0.5854972064313324</v>
       </c>
     </row>
     <row r="14">
@@ -5189,21 +5191,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', '## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
+          <t>['Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.']</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>**Payment timeline for a non‑MSME supplier**
-1. **SE’s payment to SDI** – SE must pay SDI within **net 70 days** from the date SE receives the invoice.  
-2. **SDI’s payment to the Supplier** – Once SDI has received SE’s payment, SDI will process the Supplier’s payment **within five (5) business days**, provided that:
-   - all required documentation and the invoice are in the correct form, and  
-   - any debit‑note dispute (if any) has been resolved.
-So the Supplier will receive payment no later than 70 days + 5 business days after the invoice is issued, assuming all conditions are met.
-**Penalty for the two‑week delay**
-- Under clause 6.1(b), liquidated damages are **1 % of the Purchase Order price for each week of delay**.
-- A two‑week delay therefore incurs **2 % of the price** as liquidated damages (subject to the overall cap of 10 % of the Purchase Order price).
-- In addition, any extra costs incurred by SDI because of the late delivery (e.g., air‑shipping, extra manpower) are to be borne by the Supplier under clause 6.2.</t>
+          <t>**Penalty for the delay**  
+- Under clause 6.1 (b), the supplier is liable for liquidated damages of **1 % of the price of the Products or Works for each week of delay**.  
+- Because the delivery was two weeks late, the supplier would owe **2 % of the purchase‑order price** in liquidated damages (subject to the overall cap of 10 % of the order price).  
+- In addition, any extra costs incurred by SE or SDI because of the late delivery (e.g., air‑shipping, additional manpower, storage, demurrage, etc.) must be borne by the supplier, and SE/SDI may deduct those amounts from any payment due to the supplier.
+**Payment timeline**  
+The provided excerpts do not specify a particular payment timeline that applies when a non‑MSME supplier delivers late. I don’t know.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5212,16 +5210,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.49999999995</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8478288286147204</v>
+        <v>0.7123286692598559</v>
       </c>
     </row>
     <row r="15">
@@ -5232,13 +5230,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', '## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.']</t>
+          <t>['Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C']</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>- **Termination for convenience:** The Supplier must be given **15 days’ prior notice** (Art. 13.1).
-- **Termination for an unrectified breach:** The Supplier must be given **30 days to rectify the breach** after receiving the notice; if the breach is not remedied within that 30‑day period, SDI may terminate (Art. 14.1 (b)).</t>
+          <t>- **Termination for convenience:** The Supplier must be given **15 days’ prior notice** before SDI (in consultation with SE) can terminate a Purchase Order without cause (Art. 13.1).
+- **Termination for an unrectified breach:** If the Supplier breaches a provision and does not remedy it, SDI (in consultation with SE) must give the Supplier **30 days’ notice** to rectify the breach; failure to do so within that period allows immediate termination for default (Art. 14.1 b).</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5253,10 +5251,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9353447158237396</v>
+        <v>0.8628811551798703</v>
       </c>
     </row>
     <row r="16">
@@ -5267,19 +5265,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', '## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', '## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', '## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.']</t>
+          <t>['This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section defines when title ownership and associated rights pass to Schneider Electric and when risk remains with the supplier until final acceptance overriding any Incoterms used in the purchase order\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.']</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>**Title**
-Title and ownership of the Products, Works, or Services pass to SE when either  
-1. the Products or Works are delivered to the Delivery Point (or the Services are completed), **or**  
-2. a Purchase Order is terminated before delivery/completion, at the moment the Supplier receives the termination notice (as per Articles 13 and 14).
-**Risk**
-Risk of loss or damage remains with the Supplier **until the Supplier receives the Final Acceptance Certificate**. The issuance of that certificate does not relieve the Supplier of its other obligations under Article 8.
+          <t>**Title (ownership)** passes to Schneider Electric (SE) when:
+* The Products or Works are delivered to the Delivery Point, **or**
+* The Services are completed, **or**
+* A Purchase Order is terminated before delivery/completion and the Supplier receives the termination notice (Art. 7.1).
+**Risk** (the responsibility for loss or damage) remains with the Supplier **until the Supplier receives the Final Acceptance Certificate** for the Products, Works, or Services (Art. 7.2).
 **Why the two moments differ**
-Title can pass at delivery (or upon termination) to give SE ownership of the items, but the Supplier continues to bear the risk until SE formally accepts the goods/services through the Final Acceptance Certificate. This separation ensures that SE owns the items while the Supplier remains responsible for any loss, damage, or defects that may arise before the final acceptance is granted.</t>
+* Title is transferred at delivery/completion (or upon termination) so that SE becomes the legal owner of the items at the point they are handed over.  
+* Risk is retained by the Supplier until SE formally accepts the delivery through the Final Acceptance Certificate, ensuring that SE is not exposed to loss or damage until it has verified that the goods or services meet the contractual requirements. This separation protects SE while still allowing ownership to pass earlier.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5289,15 +5287,1070 @@
       </c>
       <c r="E16" t="n">
         <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7489476824033345</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>For a product found defective during the warranty period, what are the Supplier's options and the associated interest rate and time limit?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>['This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'This is the indemnification clause in Schneider Electrics General Terms and Conditions of Purchase defining the Suppliers duty to indemnify SE and SDI for losses liabilities injuries defects breaches negligence and liens arising from the products works services or purchase order performance\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.']</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>If a product is deemed defective during the Warranty Period, the Supplier may:
+1. **Collect and refund** – at its own cost, retrieve the defective items and repay the price paid by SDI (or the designated customer) **with interest of 2 percent above the prevailing prime lending rate** (interest is calculated from the date SDI paid the price), and also compensate SE and SDI for any related losses.
+2. **Repair, rectify or replace** – at its own cost, fix or replace the defective items **within the time‑frame specified in the Compliance Notice**; if the notice does not state a period, the Supplier must act within **fifteen (15) working days** from the date of the notice.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>At SDI's election the Supplier must either (a) collect the defective items and repay the Price with interest at 2% above the prevailing prime lending rate (plus compensate losses), or (b) repair/rectify/replace within the period specified, defaulting to 15 working days. The warranty period is, by default, 12 months.</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8567440468883959</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>What event triggers a 'Compliance Notice', and what must the Supplier do once it receives one? Use the document's own definitions.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>['This section covers testing inspection and acceptance procedures including SEs right to issue a Compliance Notice and require the supplier to retrieve replace or rectify defective items under the purchase terms\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A “Compliance Notice” is issued when, during the Warranty Period, SE (or one of SE’s customers) determines that a Product, Work or Service is a **Defective Item** – i.e., it does not meet, or no longer meets, the warranties set out in the agreement.
+Once the Supplier receives a Compliance Notice, it must, at SE/SDI’s election, either:
+1. **Collect and refund** the defective items at its own cost, repay the price (with 2 % interest above the prevailing prime rate) and compensate SE/SDI for any losses, **or**  
+2. **Repair, rectify, or replace** the defective items at its own cost within the time period specified in the notice (or, if none is specified, within fifteen (15) working days).
+In short, the notice is triggered by the discovery of a defective item, and the Supplier must promptly retrieve, replace, or rectify the defect as directed.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>The definition of 'Compliance Notice' points to Art. 8.4. It is triggered when SE finds (itself or via a customer) that any Product/Work/Service is a 'Defective Item' during the Warranty Period. On receipt, the Supplier must, at SDI's election, either repay the Price plus 2% above prime lending rate (and compensate losses), or repair/replace within 15 working days.</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.249999999975</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.919502125235044</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>If a Purchase Order does not state a warranty period for a Service, when does the warranty begin and how long does it last?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>['Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 11 of the purchase terms sets out the suppliers insurance obligations requiring adequate insurance coverage from reputable insurers and allowing SDI to suspend performance if proof of coverage or premium payment is not provided\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'Section 25 of the purchase terms sets out the supplier documentation requirements for delivering products works or services including manuals certificates inspection records warranty certificates and third party IP licenses before delivery completion\n## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.']</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>When a Purchase Order does not specify a warranty period for a Service, the warranty starts on the later of:
+* the date SE issues the Final Acceptance Certificate for the Service, or  
+* the date the Service is completed,
+and it lasts for twelve (12) months from that start date.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>It lasts 12 months, running from the date SE issues the Final Acceptance Certificate for the Services or from when the Services are completed, whichever is later. (This requires combining the 'Warranty Period' default with the 'Final Acceptance Certificate' concept.)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3333333333</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7863301764417587</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A supplier has separately negotiated and executed a services agreement. A conflict then arises between that agreement, the Purchase Order, and these T&amp;C. Which prevails, and how do you know?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>['Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'This section sets the rules for assigning rights and subcontracting obligations under the purchase agreement including SDIs right to transfer its interests and the Suppliers need for prior written consent to subcontract or assign work\n## 20. ASSIGNMENT AND SUBCONTRACTING\n\nSDI shall have the right to assign its rights or obligations under the Agreement in part or in whole to any third party (including its affiliate) by notice to, but without consent of, the Supplier. However, the Supplier shall not assign or subcontract any obligation under the Agreement to any third party without the prior written consent of SDI. Without prejudice to the foregoing, SDI’s consent to the assignment or sub-contracting shall not release the Supplier from the obligations under the Agreement which have been assigned or subcontracted. Supplier assumes full responsibility to SE and SDI for the improper acts and omissions of its subcontractors or others employed or retained by Supplier in connection with the Agreement.', 'This section sets the communication rules for the purchase agreement requiring all notices and correspondence between the Supplier and SDI to be in English and sent only through the contact details specified in the Purchase Order unless updated in writing\n## 28. COMMUNICATIONS\n\nAll communications between the Supplier and SDI shall be in English and in the form of e-mails, faxes, or letters and shall be sent to the address or e-mail accounts, or contact numbers (as the case may be) as shown on the Purchase Order, unless one Party otherwise notifies the other Party in writing.']</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>The separately‑negotiated and executed services agreement will prevail. Section 2.1 states that, although the T&amp;C override any conflicting supplier terms and take precedence over the Purchase Order, “in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.” Therefore, for any conflict among the services agreement, the Purchase Order, and these T&amp;C, the services agreement controls.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Normally the T&amp;C prevail over an inconsistent Purchase Order. However, where the parties specifically negotiate and execute a services agreement, that services agreement prevails over the T&amp;C to the extent of any conflict. (The Order of Precedence on p.1 plus Art. 2.1 establish this.)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8767817687129522</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>At what exact point are Products considered 'delivered' so that the payment process can begin? Pull together every condition the document attaches.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>['This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section is part of the purchase terms for Schneider Electric and explains when delivery or performance is deemed complete under a purchase order including required placement at the delivery point notice of completion supporting documents and any replacement or repair obligations before acceptance\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', 'This is the indemnification clause in Schneider Electrics General Terms and Conditions of Purchase defining the Suppliers duty to indemnify SE and SDI for losses liabilities injuries defects breaches negligence and liens arising from the products works services or purchase order performance\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.']</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>According to the “Delivery and Performance” clause (Art. 6.4), a Product (or Work) is not deemed delivered – and therefore the supplier’s right to payment does not arise – until **all** of the following conditions are satisfied (unless the Purchase Order states otherwise):
+1. **Placement at the Delivery Point** – every Product and every Work covered by the Purchase Order has been placed at the designated Delivery Point and is ready for pick‑up or for use.  
+2. **Supplier Notification** – SE and SDI have received a formal notification from the Supplier confirming that delivery has been made and that the work is complete.  
+3. **Required Documentation** – all documents listed in Art. 24 of the General Terms and Conditions have been received by SE and SDI.  
+4. **Replacement/Repair (if applicable)** – if any Product, Work or Service is subject to a required replacement or repair under Art. 8.4, the replacement/repair must be completed **and** a Final Acceptance Certificate must have been issued for that Product, Work or Service.
+Only when **all four** of these criteria are met is the delivery considered complete, at which point the payment process may be initiated.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Products/Works are not considered delivered until: (a) all are placed at the Delivery Point ready for pickup/use; (b) SE and SDI receive the Supplier's delivery/completion notification; (c) all required documents are received; and (d) where repair/replacement applied, the relevant Final Acceptance Certificate is issued. Only once delivery is complete and a compliant invoice is submitted does the payment timeline run.</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.878175294119025</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>What late-payment interest rate must SDI pay the Supplier if SDI pays after the due date?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>['Section 5 of the purchase terms covering taxes and GST compliance including supporting documents invoice details reverse charge deductions for loss of input tax credit and reporting noncompliance to tax authorities\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 11 of the purchase terms sets out the suppliers insurance obligations requiring adequate insurance coverage from reputable insurers and allowing SDI to suspend performance if proof of coverage or premium payment is not provided\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).']</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>The document does not specify any late-payment interest payable by SDI to the Supplier. (It specifies interest on defective-item repayments and on GST/credit reversals, but not a penalty for SDI's late payment.) The correct response is that this is not stated.</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.249999999975</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.051666416740992</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>What is the minimum order value or monetary threshold required to raise a Purchase Order under these terms?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>['This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The document does not state any minimum order value or monetary threshold for a Purchase Order. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9999999999666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.01824678317384411</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>How many days of paid leave are the Supplier's on-site personnel entitled to?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>['This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section is part of the purchase terms and explains that the supplier and its personnel are independent contractors and not agents employees or representatives of SE or SDI\n## 19. INDEPENDENT SUPPLIER\n\nSupplier and his employees, agents, representatives, assigns, sub-suppliers etc. are independent suppliers and shall not be construed as agents, representatives, or employees of SE and/or SDI.']</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Not addressed. This is a purchase T&amp;C, not an employment contract; it expressly states the Supplier's personnel are independent and not employees of SE/SDI, but says nothing about their leave entitlements. The correct response is that this is not covered.</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.07823683174726326</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>In which currency must invoices be denominated?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'This section sets the communication rules for the purchase agreement requiring all notices and correspondence between the Supplier and SDI to be in English and sent only through the contact details specified in the Purchase Order unless updated in writing\n## 28. COMMUNICATIONS\n\nAll communications between the Supplier and SDI shall be in English and in the form of e-mails, faxes, or letters and shall be sent to the address or e-mail accounts, or contact numbers (as the case may be) as shown on the Purchase Order, unless one Party otherwise notifies the other Party in writing.']</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The document does not specify a currency for invoices. It details required invoice fields, taxes and GST handling, but no currency is stated. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.01623632649160952</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>List every distinct deadline or response window the Supplier must observe across the whole contract.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>['This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>**Deadlines / response windows that the Supplier must meet**
+| Contract clause | What the Supplier must do | Deadline / time‑frame |
+|-----------------|---------------------------|----------------------|
+| **15. CHANGE ORDER** – response to an Alteration Notice | Send a response to SDI (either cost &amp; time, reasons for inability, or agreement to proceed without extra cost/time) | **Within 5 working days** of the date of the Alteration Notice |
+| **23. EXPORT CONTROLS AND COMPLIANCE** – provide export‑control information | Supply SE and/or SDI in writing with details of any export‑control rules and required permits or licences for the Products/Works | **Within 3 working days** of receipt of the Purchase Order |
+| **31. DATA AND CYBER SECURITY TERMS** – security‑incident notification | Notify SE (via the Supplier Breach Notification Portal) and SDI (by e‑mail) of a confirmed or reasonably suspected security incident | **Within 24 hours** of the Supplier’s detection of the incident |
+These are the only distinct time‑limits explicitly stated in the supplied contract excerpts. If a deadline is not mentioned in the context, it is not listed.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Examples spanning the document: 15 days to challenge a debit note (Art. 4); 5 working days to respond to an Alteration Notice (Art. 15.1); 7 days to act after a Reminder Notice if none specified (Art. 6.3); 30 days to rectify a rectifiable breach (Art. 14.1(b)); 15 working days to repair/replace a Defective Item if none specified (Art. 8.4); 3 working days to supply export-control info after PO receipt (Art. 23); 24 hours to notify a Security Incident (Art. 31.3); 45 calendar days to pay set-off amounts (Art. 17). A complete answer requires sweeping the entire document.</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5335818754038175</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Summarize every scenario in which SE or SDI may withhold, deduct, or recover money from the Supplier.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>['This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>**Scenarios in which SE or SDI may withhold, deduct, or recover money from the Supplier**
+| Clause | Situation | What SDI/SE may do with the Supplier’s money |
+|--------|-----------|---------------------------------------------|
+| **5.7 (Taxes – invoice upload)** | Supplier fails to upload a valid invoice on the GSTN portal within two tax periods after SDI uploads it. | Supplier must bear the interest on the reversal of input‑tax credit (i.e., a monetary charge is imposed on the Supplier). |
+| **5.8 (Taxes – black‑listing / de‑registration)** | Supplier is black‑listed or de‑registered during the business relationship. | Supplier must indemnify SDI for the tax amount and any applicable interest, i.e., SDI recovers those amounts from the Supplier. |
+| **5.9 (Taxes – TDS)** | A Tax Deducted at Source (TDS) is applicable under law. | SDI deducts the prescribed TDS rate from the Supplier’s invoice before payment. |
+| **5.10 (Taxes – shortages / damages / disputes)** | SDI notifies the Supplier in writing of shortages or damages, or a payment dispute arises. | • Balance payment is **withheld** until the shortage/damage issue is settled. &lt;br&gt;• If a dispute is not resolved by the September following the FY‑end **and** the Supplier’s act causes loss of input‑tax credit to SDI, SDI **recovers** the lost credit amount from the Supplier. |
+| **13 (Termination for Convenience)** | SDI terminates a purchase order (partly or wholly) on 15‑day notice (no cause required). | Supplier is paid **only** for products, works, or services that have been manufactured, delivered, or performed and that meet all requirements at the time of termination. No further payment (including lost‑profit claims) is allowed. |
+| **14 (Termination for Default)** | Supplier commits a material breach, fails to rectify a breach within 30 days, fails to deliver/complete, refuses performance, or becomes insolvent/bankrupt, etc. | • SDI pays only for the goods/services that SE has received and elected to keep. &lt;br&gt;• SE may return any other goods/works to the Supplier. &lt;br&gt;• Supplier must **repay** SDI the price for any goods/works that SDI has paid for but has not received or that SDI has elected to return. |
+| **15 (Change Order – non‑agreement)** | Supplier responds that it cannot perform an alteration notice, or proposes additional cost/time that SDI/SE do not accept. | SDI/SE may terminate the purchase order under Art. 13. The Supplier then receives payment only for completed, conforming goods/works/services, with no claim for additional charges or lost profit. |
+**In summary**, money may be withheld, deducted, or recovered from the Supplier when:
+1. Tax‑related obligations are not met (invoice upload, black‑listing, TDS, loss of input‑tax credit).  
+2. There are documented shortages, damages, or payment disputes.  
+3. A purchase order is terminated – either for convenience or for default – limiting payment to only the portion already completed and conforming, and requiring repayment for any paid‑for but undelivered items.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Across the document these include: GST/input-tax-credit non-compliance withholding and recovery (Art. 5); debit notes for volume/quality/price disputes (Art. 4); set-off of amounts owed (Art. 17); liquidated damages for late delivery (Art. 6); repayment plus interest for Defective Items (Art. 8.4); deductions for losses from improper packing/shipping (Art. 21); and withholding money on third-party IP-infringement claims (Art. 12.1). A complete answer requires aggregating many sections.</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6046984601268717</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Overall, what are the main categories of obligation this contract places on the Supplier?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>['This section sets the rules for assigning rights and subcontracting obligations under the purchase agreement including SDIs right to transfer its interests and the Suppliers need for prior written consent to subcontract or assign work\n## 20. ASSIGNMENT AND SUBCONTRACTING\n\nSDI shall have the right to assign its rights or obligations under the Agreement in part or in whole to any third party (including its affiliate) by notice to, but without consent of, the Supplier. However, the Supplier shall not assign or subcontract any obligation under the Agreement to any third party without the prior written consent of SDI. Without prejudice to the foregoing, SDI’s consent to the assignment or sub-contracting shall not release the Supplier from the obligations under the Agreement which have been assigned or subcontracted. Supplier assumes full responsibility to SE and SDI for the improper acts and omissions of its subcontractors or others employed or retained by Supplier in connection with the Agreement.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The contract imposes three broad groups of obligations on the Supplier:
+1. **Assignment and Subcontracting** – the Supplier may not assign or subcontract any part of the agreement without SDI’s prior written consent, and remains fully responsible for the acts and omissions of any subcontractors it uses.
+2. **Warranty and Guarantee** – the Supplier must warrant that it has clear title to the products, works and services; that all deliverables are new, of commercially best quality, free of defects, and meet the functional, specification, and applicable ISO/other internationally‑recognized standards set out in the purchase order or the contract.
+3. **Termination‑at‑Convenience Compliance** – if SDI terminates a purchase order, the Supplier must immediately cease performance (including subcontractors), protect and hand over any ready‑for‑delivery items and documentation, cooperate in ending or assigning existing sub‑contracts, and accept payment only for completed, conforming goods, works or services, with no claim for lost or prospective profits.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>High-level themes spanning the contract: deliver on time and to spec (Arts. 6, 8, 9); provide warranties and remedy defects (Art. 8); carry insurance (Art. 11); indemnify SE/SDI (Art. 10); respect and assign IP rights (Art. 12); maintain confidentiality (Arts. 1.4, 26); comply with tax/GST, export-control and other laws (Arts. 5, 22, 23); protect data and meet cyber-security minimums (Arts. 24, 31); supply documentation (Art. 25); and follow the Business Partner Code of Conduct (Art. 30). This is a whole-document synthesis.</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5992545381643264</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>List all the ways a Purchase Order can be terminated under this contract and the condition for each.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>['Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'Section 18 of the purchase terms covering waiver of rights and stating that SE or SDI delay non enforcement or written waiver does not waive future breaches\n## 18. WAIVER\n\nAny non-enforcement of any term or condition of the Agreement or delay in enforcing or forbearance by SE or SDI shall not be construed as a waiver of such term or condition by SE or SDI. Further, any waiver in writing by SE or SDI of any provision or term of the Agreement shall not be interpreted as a waiver for future breach of the same provision or term.', 'Section 26 of the Schneider Electric General Terms and Conditions of Purchase sets out the suppliers confidentiality obligations including permitted disclosure on a need to know basis return or destruction of confidential materials and survival of the duty after completion or termination\n## 26. CONFIDENTIALITY\n\nThe Supplier shall keep all Confidential Information secret and shall not use any of it for any purpose other than the performance of the Agreement, except that, for the purpose of performance of the Agreement, the Supplier is allowed to disclose any Confidential Information, on a need-to-know basis, to his employees, subcontractors, or suppliers who undertake in writing not to disclose or otherwise misuse the Confidential Information. Upon the request by SDI, the Supplier shall execute a separate non-disclosure agreement in the form reasonably satisfactory to the SDI, undertaking not to disclose or misuse the Confidential Information.  If any Purchase Order is completed or otherwise terminated, the Supplier shall return or destroy (at the SDI’s request), at its own costs, all documents or other media which contain any Confidential Information.  The obligation set out in this Article or in any non-disclosure agreement shall survive the termination or completion of any Purchase Order or the Agreement.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>**Ways a Purchase Order can be terminated and the condition for each (as set out in the provided terms):**
+| Method of termination | Condition that triggers it |
+|-----------------------|----------------------------|
+| **Termination by SDI (in consultation with SE)** | The Supplier fails to deliver the Products/Works or provide the Services **within the time period specified in the Reminder Notice**; **or**, if the Reminder Notice does not specify a time period, the Supplier fails to deliver within **seven (7) days** after the date of the Reminder Notice. In such a case, SDI (after consulting SE) may exercise its sole discretion to terminate the Purchase Order in accordance with Article 14 of the terms. |
+*No other termination mechanisms are described in the supplied excerpts.*</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Termination at convenience: by SDI without cause on 15 days' notice (Art. 13). Termination for default: immediately, on a material breach, an unrectified breach (30 days), failure to deliver after a Reminder Notice, refusal to perform, or insolvency/bankruptcy (Art. 14). Via change order: if the parties cannot agree on a rejected/extra-cost Alteration Notice, SDI may terminate under Art. 13 (Art. 15.3). Delivery failure: termination after an unmet Reminder Notice period (Art. 6.3). Requires gathering distant sections.</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7254863149223914</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>user_input</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>retrieved_contexts</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>context_recall</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>llm_context_precision_with_reference</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>faithfulness</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>semantic_similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What is the maximum cap on accumulated liquidated damages?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>['Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets the liability limits for Schneider Electric and SDI under the purchase agreement and excludes most indirect damages while capping their maximum exposure to undisputed supplier invoice payments\n## 16. LIMITATION ON LIABILITY\n\nIn no event shall SE, SDI or their affiliates, employees, officers, and directors be liable for any punitive, consequential, incidental, special, or indirect damages, in any action arising from or related to this Agreement, whether based in contract, tort (including negligence), intended conduct or otherwise, including without limitation, damages relating to the loss of profits, business, income, savings, use, goodwill or revenue.  Notwithstanding anything contained herein, SE’s and/or  SDI’s maximum liability shall be limited to the payments to be made to Supplier on undisputed invoices.', 'This is the indemnification clause in Schneider Electrics General Terms and Conditions of Purchase defining the Suppliers duty to indemnify SE and SDI for losses liabilities injuries defects breaches negligence and liens arising from the products works services or purchase order performance\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.']</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The accumulated liquidated damages shall not exceed **10% of the Price of the related Purchase Order**.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10% of the Price of the related Purchase Order.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5739685591731463</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Which country's laws govern the Agreement?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>['This section appears in the General Terms and Conditions of Purchase governing Schneider Electric orders placed by SDI and sets a legal compliance obligation for the Supplier within the broader procurement agreement.\n## 22. COMPLIANCE WITH LAWS\n\nThe Supplier shall comply with all applicable laws in its performance of the Agreement, including without limitation, those set forth in Art. 22 and 23 of these T&amp;C.', 'This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.']</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The Agreement is governed by the laws of India.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The laws of India.</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6998807776087896</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>How many days does the Supplier have to challenge a debit note?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.']</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The Supplier has **fifteen (15) days** from the issuing of the debit note to challenge it.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>15 days from the issuing of the debit note.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7763720632543963</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Where will any arbitration proceeding take place?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>['This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'Definitions section listing key contractual terms for payment documentation price privacy laws product purchase order and the relevant Schneider Electric India entity SE \n## 1. DEFINITIONS\n\n- 1.9. “ **Payment Documentation** ” means all documents which are either a) specified in the Purchase Order which must be sent and approved by SDI as the condition for the payment of the Price; or b) if the relevant Purchase Order fails to specify the Payment Documentation: (i) a commercial invoice correctly stating the Price, (ii) (if applicable) a photocopy / original copy of the Final Acceptance Certificate bearing the SE’s (or its representative’s) signature; and (iii) if any third party Intellectual Property Right is involved in the manufacture, use, or delivery of the Products, Works or Services, all necessary documents or certificates which prove that the SE has the right to use, sell, or otherwise dispose the Products, the Works, or the Services; \n\n- 1.10.“ **Price** ” means the price for the Products, the Works or Services which SDI is obliged to pay to the Supplier under a relevant Purchase Order; \n\n\n\n- 1.11.“ **Privacy Laws** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.12.“ **Product** ” means any product which the SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.13.“ **Purchase Order** ” means any document which the SDI and the Supplier enter into which contemplates a transaction under which the Supplier is to deliver certain Products or Works to, or provide certain Services to, the SE; \n\n- 1.14.“ **SE** ” means the relevant Schneider Electric India entity on whose behalf SDI will place the Purchase Order on the Supplier, which shall include any of the following Schneider Electric India entities mentioned below: \n\n   - 1.14.1.Schneider Electric India Private Limited; \n\n   - 1.14.2.Schneider Electric Private Limited; \n\n   - 1.14.3.Schneider Electric IT Business India Private Limited \n\n   - 1.14.4.Schneider Electric President Systems Limited \n\n   - 1.14.5.Schneider Electric Infrastructure Limited \n\n   - 1.14.6.Schneider Electric Systems India Private Limited (formerly known as Invensys India Private Limited) \n\n   - 1.14.7.Eurotherm India Private Limited \n\n   - 1.14.8.Energy Grid Automation Transformers &amp; Switchgear India Private Limited; and \n\n   - 1.14.9.Schneider Electric Solar India Private Limited.']</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Any arbitration proceeding shall take place in **New Delhi**.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New Delhi.</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5728874182057554</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>If a vendor hands over goods late, how much can be docked for each week the shipment is overdue?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>['Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1% of the Price of the Products or Works for each week of delay, capped at 10% of the related Purchase Order price.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1% of the Price of the undelivered Products/Works (or unprovided Services) per week of delay, capped overall at 10%.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.888187082993913</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Who foots the bill for obtaining the paperwork needed to ship products across borders legally?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>['This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section is part of the purchase terms and explains that the supplier and its personnel are independent contractors and not agents employees or representatives of SE or SDI\n## 19. INDEPENDENT SUPPLIER\n\nSupplier and his employees, agents, representatives, assigns, sub-suppliers etc. are independent suppliers and shall not be construed as agents, representatives, or employees of SE and/or SDI.']</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The Supplier bears the cost of obtaining all necessary export and re-export permits or licenses needed to ship the products legally across borders.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The Supplier, at its own expense, must obtain all necessary export and re-export permits or licenses.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7982654571834662</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>How soon does the seller get paid once the integrator has itself received money from the buyer?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>['This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', "Section 17 of Schneider Electric General Terms and Conditions of Purchase on set off and withholding rights allowing SDI and SE to deduct or withhold payments for breaches, nonconforming services, and other amounts owed by the supplier\n## 17. SET-OFF\n\nSDI (in consultation with SE) may withhold amounts due under this Agreement on account of:  (a) claims arising out of or related to Supplier's breach or reasonably anticipated breach of this Agreement, (b) any amounts owed by Supplier to SE and/or SDI under this Agreement or otherwise; (c) non-conforming or deficient Services not yet corrected; (d) a reasonable doubt that Supplier can complete the Services for the unpaid portion of the Agreement price; or (e) any amounts owed by Supplier to SE and/or SDI or to an Affiliate under any other contracts, claims, demands, lawsuits or other matters.  If amounts owed by Supplier to SE and/or SDI exceed the unpaid balance of this Agreement, Supplier agrees to pay those amounts within forty-five calendar days after receipt of SDI’s notice identifying the amounts due.", "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The supplier is paid within **five (5) business days** after SDI receives payment from SE, provided the required documentation and correct invoice have been submitted.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Within 5 business days after SDI receives payment from SE (subject to correct invoicing and documentation).</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3333333333</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8363168559146203</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>If a buyer wants to walk away from an order even though the supplier did nothing wrong, how much advance warning must it give?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>['Section 11 of the purchase terms sets out the suppliers insurance obligations requiring adequate insurance coverage from reputable insurers and allowing SDI to suspend performance if proof of coverage or premium payment is not provided\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.']</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The buyer must give **15 days’ prior notice**.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>15 days' prior notice (termination at convenience / without cause).</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.249999999975</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5436946796101885</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Which ISO/IEC standards are named as the alignment benchmark for the Supplier's data-security safeguards?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>['This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'Section on data protection obligations defining SE and SDI content controller roles supplier safeguards breach notification and compliance with privacy laws for services performed under the purchase order\n## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The Supplier’s data-security safeguards are aligned with industry standards such as **ISO/IEC 27001** and **IEC 62443**.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001 or IEC 62443.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6496769862302005</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Under which Act will disputes be settled by arbitration?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>['This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.']</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Disputes will be settled by arbitration as per the **Arbitration and Conciliation Act, 1996**.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The Arbitration and Conciliation Act, 1996 (referred to as 'IAC').</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5577656772976319</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>List the Quality Assessment Standards the Products must comply with under the warranty.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>['This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'Section 9 describes the testing inspection and acceptance process for delivered products works and services including defect rectification re testing and the issuance of final acceptance certificate or compliance notice by SE or SDI\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.2. If any defect is discovered in the Products, Works or Services during the testing or inspection, at the request of SDI (on SE’s request to SDI) or their representative, the Supplier shall rectify such defect (or cause such defect to be rectified) and organize another testing or inspection, bearing all costs and expenses for re-testing or re-inspecting including SE’s costs in attending such retesting or re-inspection. For the avoidance of any doubt, SE’s attendance at testing/inspection or failure to do so shall not be interpreted as SE’s endorsement of, or acquiescence to, the quality of the Products, the Works or the Services and shall not relieve the Supplier from its obligations set out in Art. 8 of these T&amp;C. SE  shall have the right to examine the Products, Works, or the Services independently upon the delivery of all Products or all Works to the Delivery Point, or upon the completion of all Services under a Purchase Order.\n- 9.3. SE shall: \n\n   - a) issue a Final Acceptance Certificate if the examination does not reveal any Defective Item in the Products, the Works, or the Services; or \n\n   - b) SDI (if requested by SE) serve a Compliance Notice on the Supplier specifying any Defective Item in the Products, Works, or the Services according to Art. 8 of these T&amp;C if SE discovers any such Defective Item.']</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The Products must comply with:
+- ISO9000
+- ISO26000
+- ISO14001
+- ISO 50001
+and any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ISO9000, ISO26000, ISO14001 and ISO 50001 (or other internationally recognized applicable standards).</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7862982606911006</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>What is the proprietary web-based tool through which Suppliers must submit invoices?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This is the indemnification clause in Schneider Electrics General Terms and Conditions of Purchase defining the Suppliers duty to indemnify SE and SDI for losses liabilities injuries defects breaches negligence and liens arising from the products works services or purchase order performance\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.']</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Suppliers must submit invoices through SDI’s proprietary web-based tool, **Work Nexus®**.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Work Nexus(R), SDI's proprietary web-based tool.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5908792522633466</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A non-MSME supplier delivers goods two weeks late. Explain both the payment timeline that applies and the penalty for the delay.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>['Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.']</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>The supplier must still fulfill its obligations under the Agreement, and any extra costs caused by the late delivery are borne by the Supplier.
+For the delay penalty, liquidated damages apply at **1% of the price of the undelivered Products or unprovided Services per week of delay**, counted from the due date, with a **maximum cap of 10% of the related Purchase Order price**.
+As for the payment timeline, the context does **not** specify a separate payment timeline for late delivery. It only says SE and SDI may issue a **Reminder Notice**, and if the Supplier fails to deliver within the period stated in that notice, or within **7 days** if no period is stated, **SDI may terminate the Purchase Order**.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Payment: SE pays SDI on Net 70-day terms for non-MSME vendors (from SE's receipt of invoice), and the Supplier is paid within 5 business days after SDI receives payment from SE. Penalty: liquidated damages of 1% of Price per week of delay, so ~2% for two weeks, subject to the overall 10% cap.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7362557127182775</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>What are the notice periods for terminating a Purchase Order for convenience versus for an unrectified breach?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>['This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.']</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>For **termination for convenience**, SDI (in consultation with SE) may terminate a Purchase Order by giving **15 days’ prior notice** to the Supplier.
+For **termination for an unrectified breach**, the context does **not specify a fixed notice period**. It only says that if the Supplier fails to deliver within the period in a Reminder Notice (or **7 days** from the Reminder Notice if no period is specified), SDI may terminate the Purchase Order.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Termination at convenience requires 15 days' prior notice. Termination for default for a rectifiable breach allows termination if the Supplier fails to rectify within 30 days of SDI's notice.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8341369667780236</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>When does title pass to SE, and when does risk pass to SE, and why are they different points in time?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>['This section defines when title ownership and associated rights pass to Schneider Electric and when risk remains with the supplier until final acceptance overriding any Incoterms used in the purchase order\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.']</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Title and ownership pass to SE when the Products and Works are delivered to the Delivery Point, or when the Services are completed. If a Purchase Order is terminated before delivery/completion, title passes when the Supplier receives the termination notice.
+Risk, however, remains with the Supplier until the Supplier receives the Final Acceptance Certificate.
+They are different because Art. 7 expressly separates ownership from risk: SE gets title earlier, but the Supplier continues to bear the risk until final acceptance. It also says Incoterms in the Purchase Order do not change this rule.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Title/ownership vests with SE when the Products/Works are delivered to the Delivery Point or the Services are completed. Risk, however, remains with the Supplier until the Supplier receives the Final Acceptance Certificate. So title can transfer before risk does.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="F16" t="n">
         <v>0.9999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7565000328836509</v>
+        <v>0.8309849163747749</v>
       </c>
     </row>
     <row r="17">
@@ -5308,14 +6361,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', '## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+          <t>['This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 11 of the purchase terms sets out the suppliers insurance obligations requiring adequate insurance coverage from reputable insurers and allowing SDI to suspend performance if proof of coverage or premium payment is not provided\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).']</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>If a product is deemed defective during the Warranty Period, the Supplier may:
-1. **Collect and repay** – at its own cost, retrieve the defective items and repay the price to SDI (or the designated customer) **with interest of 2 % above the prevailing prime lending rate**, calculated from the date SDI paid the price, and also compensate SE and SDI for any related losses; **or**
-2. **Repair, rectify or replace** – at its own cost, cure the defect **within the time‑frame specified in the Compliance Notice** (or, if no period is specified, within **fifteen (15) working days** from the date of the Compliance Notice).</t>
+          <t>If a product is found defective during the Warranty Period, the Supplier must do either of the following, at SDI’s election:
+1. **Immediately collect the defective items at its own cost and refund the price**  
+   - Refund the Price to SDI (or its designated customer)  
+   - Pay **interest at 2% above the prevailing prime lending rate**, calculated from the date SDI paid the Price  
+   - Compensate SE and SDI for losses arising from the purchase, use, or resale of the defective items
+**OR**
+2. **Repair, rectify, or replace the defective items at its own cost**  
+   - Must be done within the period specified in the Compliance Notice  
+   - If no period is specified, then within **15 working days** from the date of the Compliance Notice</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5333,7 +6392,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8544848862723662</v>
+        <v>0.8578398343324996</v>
       </c>
     </row>
     <row r="18">
@@ -5344,13 +6403,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 1. DEFINITIONS\n\nFor the purpose of, these General Terms and Conditions of Purchase (“T&amp;C”), the following terms shall have the meaning hereby assigned to them unless the context would obviously require otherwise:\n- 1.1. “ **Agreement”** means these T&amp;C and the Purchase Order, collectively;\n- 1.2. “ **Alteration Notice** ” shall have the meaning set out in Art. 15 of these T&amp;C;\n- 1.3. “ **Compliance Notice** ” shall have the meaning set out in Art. 8.4 of these T&amp;C; SDI will provide such a notice to Supplier via e-mail upon being requested to do so by SE.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+          <t>['This section covers testing inspection and acceptance procedures including SEs right to issue a Compliance Notice and require the supplier to retrieve replace or rectify defective items under the purchase terms\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'Section 9 describes the testing inspection and acceptance process for delivered products works and services including defect rectification re testing and the issuance of final acceptance certificate or compliance notice by SE or SDI\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.2. If any defect is discovered in the Products, Works or Services during the testing or inspection, at the request of SDI (on SE’s request to SDI) or their representative, the Supplier shall rectify such defect (or cause such defect to be rectified) and organize another testing or inspection, bearing all costs and expenses for re-testing or re-inspecting including SE’s costs in attending such retesting or re-inspection. For the avoidance of any doubt, SE’s attendance at testing/inspection or failure to do so shall not be interpreted as SE’s endorsement of, or acquiescence to, the quality of the Products, the Works or the Services and shall not relieve the Supplier from its obligations set out in Art. 8 of these T&amp;C. SE  shall have the right to examine the Products, Works, or the Services independently upon the delivery of all Products or all Works to the Delivery Point, or upon the completion of all Services under a Purchase Order.\n- 9.3. SE shall: \n\n   - a) issue a Final Acceptance Certificate if the examination does not reveal any Defective Item in the Products, the Works, or the Services; or \n\n   - b) SDI (if requested by SE) serve a Compliance Notice on the Supplier specifying any Defective Item in the Products, Works, or the Services according to Art. 8 of these T&amp;C if SE discovers any such Defective Item.', 'This chunk is from the Definitions section of Schneider Electric General Terms and Conditions of Purchase and it defines key contract terms including Agreement Alteration Notice and Compliance Notice\n## 1. DEFINITIONS\n\nFor the purpose of, these General Terms and Conditions of Purchase (“T&amp;C”), the following terms shall have the meaning hereby assigned to them unless the context would obviously require otherwise:\n- 1.1. “ **Agreement”** means these T&amp;C and the Purchase Order, collectively;\n- 1.2. “ **Alteration Notice** ” shall have the meaning set out in Art. 15 of these T&amp;C;\n- 1.3. “ **Compliance Notice** ” shall have the meaning set out in Art. 8.4 of these T&amp;C; SDI will provide such a notice to Supplier via e-mail upon being requested to do so by SE.']</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A **Compliance Notice** is issued by SDI (by e‑mail) when SE asks SDI to do so – typically because a defect or non‑conformity has been identified during testing, inspection or acceptance.  
-Once the Supplier receives the Compliance Notice, it must, at SE’s election, **retrieve, replace, or rectify the defects** in accordance with Art. 8.4 of the T&amp;C.</t>
+          <t>A **“Compliance Notice”** is triggered when **SE finds that a Product, Work, or Service fails to meet, or ceases to meet, any of the warranties** during the **Warranty Period**, i.e., a **“Defective Item”** under **Art. 8.4**.
+Once the Supplier receives the Compliance Notice, the Supplier must, **at SE’s election**, either:
+- **collect the Defective Items at its own cost and repay the Price** for them, with interest, and compensate for losses; or
+- **repair, rectify, or replace the Defective Items at its own cost** within the period specified in the Compliance Notice, or within **15 working days** if no period is specified.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5359,16 +6420,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3333333333</v>
+        <v>0.5833333333041666</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8754376290964385</v>
+        <v>0.8538118035867663</v>
       </c>
     </row>
     <row r="19">
@@ -5379,12 +6440,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', '## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+          <t>['This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'Section 11 of the purchase terms sets out the suppliers insurance obligations requiring adequate insurance coverage from reputable insurers and allowing SDI to suspend performance if proof of coverage or premium payment is not provided\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>If the Purchase Order does not specify a warranty period for a Service, the warranty starts on the later of (a) the date SE issues the Final Acceptance Certificate for that Service or (b) the date the Services are completed. The warranty then lasts for twelve (12) months from that start date.</t>
+          <t>If the Purchase Order does not state a Warranty Period for a Service, the warranty period is **12 months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later**.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5393,16 +6454,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9999999999</v>
+        <v>0.99999999995</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8059430248304261</v>
+        <v>0.771154873014646</v>
       </c>
     </row>
     <row r="20">
@@ -5413,14 +6474,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', '## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', '## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', '## 20. ASSIGNMENT AND SUBCONTRACTING\n\nSDI shall have the right to assign its rights or obligations under the Agreement in part or in whole to any third party (including its affiliate) by notice to, but without consent of, the Supplier. However, the Supplier shall not assign or subcontract any obligation under the Agreement to any third party without the prior written consent of SDI. Without prejudice to the foregoing, SDI’s consent to the assignment or sub-contracting shall not release the Supplier from the obligations under the Agreement which have been assigned or subcontracted. Supplier assumes full responsibility to SE and SDI for the improper acts and omissions of its subcontractors or others employed or retained by Supplier in connection with the Agreement.']</t>
+          <t>['Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'This is the indemnification clause in Schneider Electrics General Terms and Conditions of Purchase defining the Suppliers duty to indemnify SE and SDI for losses liabilities injuries defects breaches negligence and liens arising from the products works services or purchase order performance\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The services agreement that the parties have specifically negotiated and executed will prevail.  
-Clause 2.1 states that if there is an inconsistency between the Purchase Order and these T&amp;C, the T&amp;C win. However, it adds: *“Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.”*  
-Therefore, when a conflict exists among the services agreement, the Purchase Order, and the T&amp;C, the services agreement overrides the other two documents.</t>
+          <t>The separately negotiated and executed services agreement prevails over these T&amp;C to the extent of any discrepancy or conflict.
+How I know:
+- Section 2.1 states that these T&amp;C apply to all Purchase Orders and prevail over conflicting Purchase Order terms.
+- But it also expressly says that if the parties specifically negotiate and execute a services agreement, then that services agreement prevails over these T&amp;C to the extent of any discrepancy or conflict.
+So, in a conflict:
+1. The services agreement prevails over these T&amp;C.
+2. These T&amp;C prevail over the Purchase Order.
+3. Therefore, the services agreement would control over both the Purchase Order and these T&amp;C on conflicting points.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5435,10 +6501,10 @@
         <v>0.9999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9155565705324968</v>
+        <v>0.836012721605311</v>
       </c>
     </row>
     <row r="21">
@@ -5449,17 +6515,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 1. DEFINITIONS\n\n- 1.5. “ **Defective Item** ” shall have the meaning set out in Art. 8.4 of these T&amp;C;\n- 1.6. “ **Delivery Point** ” means the location which the Purchase Order stipulates for the delivery of the Products or the Works or the Services or, if the Purchase Order fails to specify such location, a location of which the SE or SDI may notify to the Supplier within a reasonable period before the scheduled delivery date;\n- 1.7. “ **Final Acceptance Certificate** ” means the document which the SE, or its duly authorized representative, issues to the Supplier confirming that the Products, the Works or the Services comply with requirements under the Agreement, after having a reasonable opportunity to examine them according to Art. 9.3 of these T&amp;C;\n- 1.8. “ **Intellectual Property Right** ” means any intellectual property right, regardless of whether registered or not, including any: (i) patent, (ii) copyright (including moral right and author’s right); (iii) database right; (iv) know-how or trade secret, whether or not developed or reduced to practice; (v) industrial design; (vi) trademark, service mark, logo, domain name and keyword, and the goodwill associated with them; (vii) right of publicity; and (viii) any other proprietary right relating to intangible property anywhere in the world;', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+          <t>['This section is part of the purchase terms for Schneider Electric and explains when delivery or performance is deemed complete under a purchase order including required placement at the delivery point notice of completion supporting documents and any replacement or repair obligations before acceptance\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'Section 9 describes the testing inspection and acceptance process for delivered products works and services including defect rectification re testing and the issuance of final acceptance certificate or compliance notice by SE or SDI\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.2. If any defect is discovered in the Products, Works or Services during the testing or inspection, at the request of SDI (on SE’s request to SDI) or their representative, the Supplier shall rectify such defect (or cause such defect to be rectified) and organize another testing or inspection, bearing all costs and expenses for re-testing or re-inspecting including SE’s costs in attending such retesting or re-inspection. For the avoidance of any doubt, SE’s attendance at testing/inspection or failure to do so shall not be interpreted as SE’s endorsement of, or acquiescence to, the quality of the Products, the Works or the Services and shall not relieve the Supplier from its obligations set out in Art. 8 of these T&amp;C. SE  shall have the right to examine the Products, Works, or the Services independently upon the delivery of all Products or all Works to the Delivery Point, or upon the completion of all Services under a Purchase Order.\n- 9.3. SE shall: \n\n   - a) issue a Final Acceptance Certificate if the examination does not reveal any Defective Item in the Products, the Works, or the Services; or \n\n   - b) SDI (if requested by SE) serve a Compliance Notice on the Supplier specifying any Defective Item in the Products, Works, or the Services according to Art. 8 of these T&amp;C if SE discovers any such Defective Item.']</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>**Products (or Works) are deemed “delivered” only when all of the following conditions are satisfied (per Clause 6.4):**
-1. **Placement at the Delivery Point** – All Products and Works under the Purchase Order have been placed at the stipulated Delivery Point and are ready for pick‑up or use.  
-2. **Supplier Notification** – SE and SDI have received a notification from the Supplier confirming that delivery and completion have occurred.  
-3. **Required Documentation** – All documents listed in Article 24 of the Terms &amp; Conditions have been received by SE and SDI.  
-4. **Final Acceptance (if applicable)** – If any Product, Work, or Service requires replacement or repair under Article 8.4, the delivery of the Product/Work and the completion of the Service must be accompanied by a **Final Acceptance Certificate** issued by SE (or its authorized representative).  
-Only when these four criteria are met are the Products considered delivered, allowing the subsequent invoicing and payment process to proceed.</t>
+          <t>Products are not considered “delivered” until all of the following conditions are met:
+1. All Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up or use.
+2. SE and SDI have received notification from the Supplier regarding the delivery and completion.
+3. SE and SDI have received all documents required under Article 24 of the T&amp;C.
+4. If any Product, Work, or Service requires replacement or repair under Article 8.4, delivery/completion is only deemed to occur once the relevant Product/Work is delivered and the Service is completed with respect to which a Final Acceptance Certificate has been issued.
+Only when these conditions are satisfied is delivery deemed complete under the purchase terms.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5468,16 +6534,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8333333332916666</v>
+        <v>0.9999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8251159862527987</v>
+        <v>0.8833045972791664</v>
       </c>
     </row>
     <row r="22">
@@ -5488,12 +6554,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.']</t>
+          <t>['Section 5 of the purchase terms covering taxes and GST compliance including supporting documents invoice details reverse charge deductions for loss of input tax credit and reporting noncompliance to tax authorities\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.', 'This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>I don't know.</t>
+          <t>I don’t know. The context specifies interest rates for supplier-related issues, but it does not state a late-payment interest rate SDI must pay the Supplier if SDI pays after the due date.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5502,16 +6568,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.249999999975</v>
+        <v>0.5833333333041666</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>0.051666416740992</v>
+        <v>0.8249523764712474</v>
       </c>
     </row>
     <row r="23">
@@ -5522,12 +6588,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>['## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', '## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', '## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', '## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).']</t>
+          <t>['This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'This section is part of the purchase terms for Schneider Electric and explains when delivery or performance is deemed complete under a purchase order including required placement at the delivery point notice of completion supporting documents and any replacement or repair obligations before acceptance\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.']</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>I don't know.</t>
+          <t>I don’t know. The provided context does not specify any minimum order value or monetary threshold for raising a Purchase Order.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5536,16 +6602,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.99999999995</v>
+        <v>0.5833333333041666</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.01824678317384411</v>
+        <v>0.7498948195812707</v>
       </c>
     </row>
     <row r="24">
@@ -5556,7 +6622,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', '## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.']</t>
+          <t>['This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section is part of the purchase terms and explains that the supplier and its personnel are independent contractors and not agents employees or representatives of SE or SDI\n## 19. INDEPENDENT SUPPLIER\n\nSupplier and his employees, agents, representatives, assigns, sub-suppliers etc. are independent suppliers and shall not be construed as agents, representatives, or employees of SE and/or SDI.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5570,13 +6636,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5833333333041666</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>0.07823683174726326</v>
@@ -5590,12 +6656,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>["## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", '## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', '## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', '## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'Definitions section listing key contractual terms for payment documentation price privacy laws product purchase order and the relevant Schneider Electric India entity SE \n## 1. DEFINITIONS\n\n- 1.9. “ **Payment Documentation** ” means all documents which are either a) specified in the Purchase Order which must be sent and approved by SDI as the condition for the payment of the Price; or b) if the relevant Purchase Order fails to specify the Payment Documentation: (i) a commercial invoice correctly stating the Price, (ii) (if applicable) a photocopy / original copy of the Final Acceptance Certificate bearing the SE’s (or its representative’s) signature; and (iii) if any third party Intellectual Property Right is involved in the manufacture, use, or delivery of the Products, Works or Services, all necessary documents or certificates which prove that the SE has the right to use, sell, or otherwise dispose the Products, the Works, or the Services; \n\n- 1.10.“ **Price** ” means the price for the Products, the Works or Services which SDI is obliged to pay to the Supplier under a relevant Purchase Order; \n\n\n\n- 1.11.“ **Privacy Laws** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.12.“ **Product** ” means any product which the SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.13.“ **Purchase Order** ” means any document which the SDI and the Supplier enter into which contemplates a transaction under which the Supplier is to deliver certain Products or Works to, or provide certain Services to, the SE; \n\n- 1.14.“ **SE** ” means the relevant Schneider Electric India entity on whose behalf SDI will place the Purchase Order on the Supplier, which shall include any of the following Schneider Electric India entities mentioned below: \n\n   - 1.14.1.Schneider Electric India Private Limited; \n\n   - 1.14.2.Schneider Electric Private Limited; \n\n   - 1.14.3.Schneider Electric IT Business India Private Limited \n\n   - 1.14.4.Schneider Electric President Systems Limited \n\n   - 1.14.5.Schneider Electric Infrastructure Limited \n\n   - 1.14.6.Schneider Electric Systems India Private Limited (formerly known as Invensys India Private Limited) \n\n   - 1.14.7.Eurotherm India Private Limited \n\n   - 1.14.8.Energy Grid Automation Transformers &amp; Switchgear India Private Limited; and \n\n   - 1.14.9.Schneider Electric Solar India Private Limited.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>I don't know.</t>
+          <t>I don’t know.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5607,13 +6673,13 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.99999999995</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.01623632649160952</v>
+        <v>0.01409077964445835</v>
       </c>
     </row>
     <row r="26">
@@ -5624,22 +6690,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', '## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', '## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', "## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+          <t>['Section 9 of the purchase terms covering testing inspection and acceptance of products works and services before delivery or completion\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.1. To the extent required by law, applicable industrial standards, or the  Purchase Order, the Supplier shall carry out (and ensure its subcontractors and suppliers carry out), at no cost to the  SE or  SDI, all testing and inspection of the Products, the Works and the Services before it notifies   SE and SDI of the delivery or completion according Art. 6.4(b) of these T&amp;C. The Supplier shall notify the SE and SDI of such testing or inspection; and SE shall have the right (but not obligation) to witness such testing and inspection. The Supplier shall provide the SE with full access to such testing or inspection and all related results.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.']</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>**Deadlines / response windows that the Supplier must observe (as set out in the provided terms):**
-1. **Delivery deadline after a Reminder Notice**  
-   - The Supplier must deliver the Products, Works or complete the Services **within the period specified in the Reminder Notice**.  
-   - **If the Reminder Notice does not specify a period**, the Supplier must deliver **within seven (7) days** from the date of that Reminder Notice.  
-2. **Challenge of a Debit Note**  
-   - When SDI issues a debit note, the Supplier has **fifteen (15) days** from the date of issuance to challenge it.  
-3. **Warranty‑period obligations** (ongoing service windows)  
-   - For Products: **12 months** after delivery *or* after SE issues a Final Acceptance Certificate (whichever is later).  
-   - For Services: **12 months** after SE issues a Final Acceptance Certificate for the Services (or from the date the Services are completed, whichever is later).  
-   - For repaired/replaced Products or Works: **12 months** after the repair or replacement delivery.  
-These are the only explicit time‑frames in the excerpt that require the Supplier to act or respond.</t>
+          <t>The Supplier must observe these distinct deadlines or response windows mentioned in the context:
+1. **Before delivery/completion for testing and inspection (Art. 9.1)**  
+   - The Supplier must carry out all required testing and inspection **before** notifying SE and SDI of delivery or completion.
+2. **5 working days to respond to an Alteration Notice (Art. 15.1)**  
+   - The Supplier must respond to SDI **within five (5) working days** from the date of the Alteration Notice.
+3. **If no response to Alteration Notice (Art. 15.2)**  
+   - If the Supplier does not respond within the 5 working days, it is deemed to have agreed.  
+   - This is not a separate deadline, but it is the consequence of missing the 5-working-day window.
+4. **7 days after Reminder Notice, if no period is specified (Art. 6.3)**  
+   - If the Reminder Notice does not state a period, the Supplier must perform within **seven (7) days from the date of the Reminder Notice**.
+5. **Within the period specified in the Reminder Notice (Art. 6.3)**  
+   - If the Reminder Notice specifies a period, the Supplier must deliver or perform within that stated period.
+6. **3 working days to provide export control information (Art. 23)**  
+   - The Supplier must supply SE and/or SDI with export control rules and permit/license information **within three (3) working days from receipt of the Purchase Order**.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5648,7 +6717,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -5657,7 +6726,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5641497053694805</v>
+        <v>0.5421752438169813</v>
       </c>
     </row>
     <row r="27">
@@ -5668,20 +6737,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['## 16. LIMITATION ON LIABILITY\n\nIn no event shall SE, SDI or their affiliates, employees, officers, and directors be liable for any punitive, consequential, incidental, special, or indirect damages, in any action arising from or related to this Agreement, whether based in contract, tort (including negligence), intended conduct or otherwise, including without limitation, damages relating to the loss of profits, business, income, savings, use, goodwill or revenue.  Notwithstanding anything contained herein, SE’s and/or  SDI’s maximum liability shall be limited to the payments to be made to Supplier on undisputed invoices.', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', '## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.', '## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.']</t>
+          <t>["Section 17 of Schneider Electric General Terms and Conditions of Purchase on set off and withholding rights allowing SDI and SE to deduct or withhold payments for breaches, nonconforming services, and other amounts owed by the supplier\n## 17. SET-OFF\n\nSDI (in consultation with SE) may withhold amounts due under this Agreement on account of:  (a) claims arising out of or related to Supplier's breach or reasonably anticipated breach of this Agreement, (b) any amounts owed by Supplier to SE and/or SDI under this Agreement or otherwise; (c) non-conforming or deficient Services not yet corrected; (d) a reasonable doubt that Supplier can complete the Services for the unpaid portion of the Agreement price; or (e) any amounts owed by Supplier to SE and/or SDI or to an Affiliate under any other contracts, claims, demands, lawsuits or other matters.  If amounts owed by Supplier to SE and/or SDI exceed the unpaid balance of this Agreement, Supplier agrees to pay those amounts within forty-five calendar days after receipt of SDI’s notice identifying the amounts due.", 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>**Scenarios in which SE or SDI may withhold, deduct, or recover money from the Supplier**
-1. **Intellectual‑property infringement claims**  
-   * If a third party alleges (or threatens) that the Supplier’s Products, Works or Services infringe any Intellectual Property Right, SE and/or SDI may:  
-   – Withhold any money that is due or payable to the Supplier, and/or  
-   – Require the Supplier to provide additional security (an amount deemed reasonable by SE/SDI).  
-2. **Breach of the Purchase Order or the Terms &amp; Conditions**  
-   * When the Supplier breaches any obligation under the Purchase Order or these T&amp;C, causing consequential or incidental losses to SE or SDI, the Supplier must indemnify SE/SDI for all resulting liabilities, losses, damages, and expenses (including reasonable attorney’s fees).  
-   – SE/SDI can therefore recover those amounts from the Supplier (e.g., by offsetting them against payments).  
-These are the only circumstances described in the provided excerpts where SE or SDI have a contractual right to withhold, deduct, or recover funds from the Supplier.</t>
+          <t xml:space="preserve">SE or SDI may withhold, deduct, or recover money from the Supplier in these scenarios:
+- **Breach or anticipated breach:** They may withhold amounts due if there are claims arising from the Supplier’s breach, or reasonably anticipated breach, of the Agreement.
+- **Other amounts already owed:** They may withhold amounts due for any money the Supplier owes to SE and/or SDI under the Agreement or otherwise.
+- **Non-conforming or deficient services:** They may withhold payment for services that are not conforming or are deficient until corrected.
+- **Doubt about completion:** They may withhold amounts if there is reasonable doubt that the Supplier can complete the Services for the unpaid portion of the contract price.
+- **Amounts owed under other matters:** They may withhold amounts the Supplier owes to SE and/or SDI, or to an Affiliate, under any other contracts, claims, demands, lawsuits, or other matters.
+- **Exceeding unpaid balance:** If the amounts owed by the Supplier exceed the unpaid balance of the Agreement, the Supplier must pay those amounts within 45 calendar days after receiving SDI’s notice identifying the amounts due.
+- **IP infringement claims:** If a third party alleges or threatens an IP infringement claim, SE and SDI may withhold any money due or to become due to the Supplier, or require additional security.
+- **Tax/invoice issues:**  
+  - If the Supplier fails to upload a valid GST invoice and SDI uploads it instead, and the Supplier does not complete the required action within the next two tax periods, the Supplier must bear interest applicable on reversal of input tax credit.  
+  - If the Supplier is blacklisted or deregistered, the Supplier must indemnify SDI for tax and interest losses.  
+  - TDS may be deducted at the prescribed rate.  
+  - If shortages or damages are reported in writing, balance payment is released only after settlement.  
+  - If a payment dispute is not settled due to any act of the Supplier and SDI loses input credit on the invoice, SDI may recover that loss from the Supplier.
+- **Termination for default:** If the Supplier defaults and the order is terminated, SDI only pays for products/works/services received and kept by SE, and the Supplier must repay amounts for products or works paid for but not received or returned.
+</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5690,16 +6766,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.9999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5562358863563432</v>
+        <v>0.5659951026325887</v>
       </c>
     </row>
     <row r="28">
@@ -5710,31 +6786,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', '## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.', '## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.']</t>
+          <t>['This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section on data protection obligations defining SE and SDI content controller roles supplier safeguards breach notification and compliance with privacy laws for services performed under the purchase order\n## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.']</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The contract imposes the following broad categories of obligations on the Supplier:
-1. **Product and Service Warranty / Quality Guarantees** –  
-   - Warranty that the Supplier has full rights to manufacture, deliver and sell the Products, Works and Services (8.1).  
-   - Guarantees that the Products are new, well‑manufactured, defect‑free, fit for purpose, and meet the applicable quality standards (ISO 9000, ISO 26000, ISO 14001, ISO 5001, etc.) (8.2).
-2. **Data Protection and Cyber‑Security** –  
-   - Access, collection, storage and processing of SE/SDI data only for the purpose of fulfilling the Purchase Order and in accordance with written permission (31.1.i).  
-   - Implementation of appropriate administrative, technical and organisational safeguards (ISO/IEC 27001, IEC 62443) (31.1.ii‑v).  
-   - Maintenance of a business‑continuity plan addressing data‑ and cyber‑risk (31.2).  
-   - Prompt breach‑notification (within 24 hours) and cooperation in investigating any security incident (31.3).
-3. **Documentation Requirements** –  
-   - Delivery of drawings, manuals, certificates, inspection statements, warranty certificates and any necessary third‑party IP licences on or before delivery/completion (25.1).  
-   - Assurance that all documentation is accurate, error‑free and in English (unless otherwise stated) (25.2).
-4. **Export‑Control and Regulatory Compliance** –  
-   - Knowledge of, and compliance with, all applicable export and re‑export control laws; obtaining required licences at the Supplier’s expense (23).  
-   - Supplying SE/SDI with export‑control information within three working days of receiving the Purchase Order and notifying any regulatory changes (23).  
-   - Indemnifying SE and SDI for any loss resulting from non‑compliance (23).
-5. **Additional Operational Obligations** –  
-   - Maintaining a reasonable business continuity plan (31.2).  
-   - Cooperating with SE/SDI in investigations, remediation and any required addenda for enhanced data protection (31.3‑31.4).  
-These categories together constitute the Supplier’s core contractual duties.</t>
+          <t>The contract places the Supplier under three main categories of obligation:
+1. **Export controls and compliance**  
+   The Supplier must know and comply with applicable export and re-export laws, obtain required permits or licenses, provide related information to SE/SDI, notify them of changes, and indemnify them for non-compliance.
+2. **Warranty and guarantee obligations**  
+   The Supplier must warrant that the products, works, and services meet required standards for quality, performance, specification, title, merchantability, fitness for purpose, and applicable international standards.
+3. **Data protection obligations**  
+   The Supplier must process SE and SDI content only as instructed, maintain appropriate safeguards, comply with privacy laws, and immediately notify SE/SDI of any known or suspected unauthorized access or use.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5749,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6848746609406239</v>
+        <v>0.6854094814576731</v>
       </c>
     </row>
     <row r="29">
@@ -5763,17 +6826,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', '## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', '## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', '## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.']</t>
+          <t>['This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>**Ways a Purchase Order can be terminated and the condition for each**
-| Termination route | Condition(s) that trigger it |
-|-------------------|------------------------------|
-| **1. Termination at convenience (Art. 13.1)** | SDI (in consultation with SE) may terminate a Purchase Order, in whole or in part, **without cause** by giving the Supplier **15 days’ prior notice**. |
-| **2. Termination for default (Art. 14.1)** | SDI (in consultation with SE) may terminate a Purchase Order, in whole or in part, **with immediate effect and without compensation** if any of the following occurs: &lt;ul&gt;&lt;li&gt;**a.** The Supplier breaches a **material provision** of the Agreement.&lt;/li&gt;&lt;li&gt;**b.** The Supplier breaches any provision of the Agreement **and fails to remedy the breach within 30 days** after receiving notice from SDI (in consultation with SE).&lt;/li&gt;&lt;li&gt;**c.** The Supplier **fails to deliver** the Products or Works, or **fails to complete** the Services as required under Art. 6.3.&lt;/li&gt;&lt;li&gt;**d.** The Supplier **refuses to proceed** with performance of the relevant Purchase Order.&lt;/li&gt;&lt;li&gt;**e.** The Supplier becomes **insolvent or bankrupt**, files a petition for voluntary winding‑up (except for reorganization), appoints a receiver, is placed under judicial management, assigns substantial assets to creditors, **or** does any act that, in SDI’s view (in consultation with SE), may deprive SE or SDI of a substantial benefit under the Purchase Order or the Agreement.&lt;/li&gt;&lt;/ul&gt; |
-These are the only termination mechanisms described in the provided contract terms.</t>
+          <t xml:space="preserve">A Purchase Order can be terminated under this contract in the following ways:
+1. **Termination for convenience**
+   - **Condition:** SDI (in consultation with SE) may terminate a Purchase Order, in part or in whole, **without cause**, by giving the Supplier **15 days’ prior notice**.
+2. **Termination for late delivery / non-performance after reminder notice**
+   - **Condition:** If the Supplier fails to deliver the Products or Works or provide the Services within the period specified in the **Reminder Notice**, or **within 7 days** from the Reminder Notice if no period is specified, SDI (in consultation with SE) may terminate the Purchase Order.
+3. **Termination for change order issues**
+   - **Condition:** If the Supplier either:
+     - states it **cannot perform** the Alteration Notice, or
+     - proposes **additional charges or time** and SE/SDI **do not agree**,
+     then SDI (in consultation with SE) may terminate the relevant Purchase Order.
+4. **Termination for default**
+   - **Condition:** SDI (in consultation with SE) may terminate immediately, without compensation, if the Supplier:
+     - commits a **material breach**,
+     - commits any breach and fails to **cure it within 30 days** after notice (if curable),
+     - fails to deliver or complete the Services as set out in Art. 6.3,
+     - **refuses to proceed** with performance,
+     - becomes **insolvent or bankrupt**, enters winding up/receivership/judicial management, assigns assets for creditors, or otherwise acts in a way that may deprive SE or SDI of substantial benefit under the Purchase Order or Agreement.
+</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5782,16 +6857,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.499999999975</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7034872348940548</v>
+        <v>0.7644086184500909</v>
       </c>
     </row>
   </sheetData>

--- a/baseline_scores.xlsx
+++ b/baseline_scores.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="4" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="first_iteration" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="section_aware_chunking" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quey_rewriter" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hyde_expander_fusion" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hyde_expander_contextual_retriever_fusion_rerank" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hyde_expander_contextual_retrie" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crag(hyde_expander_rewritter_fusion_rerank)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1541,45 +1542,45 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>user_input</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>retrieved_contexts</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>reference</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>context_recall</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>llm_context_precision_with_reference</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>faithfulness</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>semantic_similarity</t>
         </is>
@@ -2574,45 +2575,45 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>user_input</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>retrieved_contexts</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>reference</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>context_recall</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>llm_context_precision_with_reference</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>faithfulness</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>semantic_similarity</t>
         </is>
@@ -3649,45 +3650,45 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>user_input</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>retrieved_contexts</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>reference</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>context_recall</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>llm_context_precision_with_reference</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>faithfulness</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>semantic_similarity</t>
         </is>
@@ -4726,45 +4727,45 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>user_input</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>retrieved_contexts</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>reference</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>context_recall</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>llm_context_precision_with_reference</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>faithfulness</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>semantic_similarity</t>
         </is>
@@ -5789,45 +5790,45 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>user_input</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>retrieved_contexts</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>reference</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>context_recall</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>llm_context_precision_with_reference</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>faithfulness</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>semantic_similarity</t>
         </is>
@@ -6872,4 +6873,1090 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>user_input</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>retrieved_contexts</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>context_recall</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>llm_context_precision_with_reference</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>faithfulness</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>semantic_similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What is the maximum cap on accumulated liquidated damages?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>['Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets the liability limits for Schneider Electric and SDI under the purchase agreement and excludes most indirect damages while capping their maximum exposure to undisputed supplier invoice payments\n## 16. LIMITATION ON LIABILITY\n\nIn no event shall SE, SDI or their affiliates, employees, officers, and directors be liable for any punitive, consequential, incidental, special, or indirect damages, in any action arising from or related to this Agreement, whether based in contract, tort (including negligence), intended conduct or otherwise, including without limitation, damages relating to the loss of profits, business, income, savings, use, goodwill or revenue.  Notwithstanding anything contained herein, SE’s and/or  SDI’s maximum liability shall be limited to the payments to be made to Supplier on undisputed invoices.', 'This is the indemnification clause in Schneider Electrics General Terms and Conditions of Purchase defining the Suppliers duty to indemnify SE and SDI for losses liabilities injuries defects breaches negligence and liens arising from the products works services or purchase order performance\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.']</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The accumulated liquidated damages shall not exceed **10% of the Price of the related Purchase Order**.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10% of the Price of the related Purchase Order.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5739685591731463</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Which country's laws govern the Agreement?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>['This section appears in the General Terms and Conditions of Purchase governing Schneider Electric orders placed by SDI and sets a legal compliance obligation for the Supplier within the broader procurement agreement.\n## 22. COMPLIANCE WITH LAWS\n\nThe Supplier shall comply with all applicable laws in its performance of the Agreement, including without limitation, those set forth in Art. 22 and 23 of these T&amp;C.', 'This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'This section appears near the end of the Schneider Electric General Terms and Conditions of Purchase and sets the severability rule for the Agreement meaning if one clause is invalid the rest remains in force\n## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.']</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The Agreement is governed by the laws of India.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The laws of India.</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6998807776087896</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>How many days does the Supplier have to challenge a debit note?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C']</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The Supplier has fifteen (15) days from the issuing of the debit note to challenge it.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>15 days from the issuing of the debit note.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8085939276622207</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Where will any arbitration proceeding take place?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>['This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'This section appears near the end of the Schneider Electric General Terms and Conditions of Purchase and sets the severability rule for the Agreement meaning if one clause is invalid the rest remains in force\n## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'Definitions section listing key contractual terms for payment documentation price privacy laws product purchase order and the relevant Schneider Electric India entity SE \n## 1. DEFINITIONS\n\n- 1.9. “ **Payment Documentation** ” means all documents which are either a) specified in the Purchase Order which must be sent and approved by SDI as the condition for the payment of the Price; or b) if the relevant Purchase Order fails to specify the Payment Documentation: (i) a commercial invoice correctly stating the Price, (ii) (if applicable) a photocopy / original copy of the Final Acceptance Certificate bearing the SE’s (or its representative’s) signature; and (iii) if any third party Intellectual Property Right is involved in the manufacture, use, or delivery of the Products, Works or Services, all necessary documents or certificates which prove that the SE has the right to use, sell, or otherwise dispose the Products, the Works, or the Services; \n\n- 1.10.“ **Price** ” means the price for the Products, the Works or Services which SDI is obliged to pay to the Supplier under a relevant Purchase Order; \n\n\n\n- 1.11.“ **Privacy Laws** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.12.“ **Product** ” means any product which the SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.13.“ **Purchase Order** ” means any document which the SDI and the Supplier enter into which contemplates a transaction under which the Supplier is to deliver certain Products or Works to, or provide certain Services to, the SE; \n\n- 1.14.“ **SE** ” means the relevant Schneider Electric India entity on whose behalf SDI will place the Purchase Order on the Supplier, which shall include any of the following Schneider Electric India entities mentioned below: \n\n   - 1.14.1.Schneider Electric India Private Limited; \n\n   - 1.14.2.Schneider Electric Private Limited; \n\n   - 1.14.3.Schneider Electric IT Business India Private Limited \n\n   - 1.14.4.Schneider Electric President Systems Limited \n\n   - 1.14.5.Schneider Electric Infrastructure Limited \n\n   - 1.14.6.Schneider Electric Systems India Private Limited (formerly known as Invensys India Private Limited) \n\n   - 1.14.7.Eurotherm India Private Limited \n\n   - 1.14.8.Energy Grid Automation Transformers &amp; Switchgear India Private Limited; and \n\n   - 1.14.9.Schneider Electric Solar India Private Limited.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Any arbitration proceeding shall take place at New Delhi.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New Delhi.</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5064862475860408</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>If a vendor hands over goods late, how much can be docked for each week the shipment is overdue?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>['Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'Section 5 of the purchase terms covering taxes and GST compliance including supporting documents invoice details reverse charge deductions for loss of input tax credit and reporting noncompliance to tax authorities\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.']</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>For each week of delay, liquidated damages of **1% of the Price of the delayed Products/Works or unprovided Services** can be charged, calculated from the Purchase Order due date.
+The total liquidated damages are capped at **10% of the Price of the related Purchase Order**.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1% of the Price of the undelivered Products/Works (or unprovided Services) per week of delay, capped overall at 10%.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.677337315305566</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Who foots the bill for obtaining the paperwork needed to ship products across borders legally?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>['This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'Section 25 of the purchase terms sets out the supplier documentation requirements for delivering products works or services including manuals certificates inspection records warranty certificates and third party IP licenses before delivery completion\n## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.']</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The Supplier foots the bill: it must obtain all necessary export and re-export permits or licenses at its own expense.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The Supplier, at its own expense, must obtain all necessary export and re-export permits or licenses.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5833333333041666</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8941183146766664</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>How soon does the seller get paid once the integrator has itself received money from the buyer?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>['This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section defines when title ownership and associated rights pass to Schneider Electric and when risk remains with the supplier until final acceptance overriding any Incoterms used in the purchase order\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The seller/Supplier’s payment will be processed within **five (5) business days after SDI receives payment from SE**, provided the required documentation is submitted and the invoice is in correct form.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Within 5 business days after SDI receives payment from SE (subject to correct invoicing and documentation).</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3333333333</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8797329368456719</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>If a buyer wants to walk away from an order even though the supplier did nothing wrong, how much advance warning must it give?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>['Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The buyer must give **15 days’ prior notice** to terminate the Purchase Order without cause.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>15 days' prior notice (termination at convenience / without cause).</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5002155981739758</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Which ISO/IEC standards are named as the alignment benchmark for the Supplier's data-security safeguards?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>['This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'Section on data protection obligations defining SE and SDI content controller roles supplier safeguards breach notification and compliance with privacy laws for services performed under the purchase order\n## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.']</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The named alignment benchmarks are **ISO/IEC 27001** and **IEC 62443**.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001 or IEC 62443.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5132687160494688</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Under which Act will disputes be settled by arbitration?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>['This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'This section appears near the end of the Schneider Electric General Terms and Conditions of Purchase and sets the severability rule for the Agreement meaning if one clause is invalid the rest remains in force\n## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.']</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Disputes will be settled by arbitration under the **Arbitration and Conciliation Act, 1996 (“IAC”)**.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The Arbitration and Conciliation Act, 1996 (referred to as 'IAC').</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7468070254737843</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>List the Quality Assessment Standards the Products must comply with under the warranty.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>['This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'Section 9 describes the testing inspection and acceptance process for delivered products works and services including defect rectification re testing and the issuance of final acceptance certificate or compliance notice by SE or SDI\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.2. If any defect is discovered in the Products, Works or Services during the testing or inspection, at the request of SDI (on SE’s request to SDI) or their representative, the Supplier shall rectify such defect (or cause such defect to be rectified) and organize another testing or inspection, bearing all costs and expenses for re-testing or re-inspecting including SE’s costs in attending such retesting or re-inspection. For the avoidance of any doubt, SE’s attendance at testing/inspection or failure to do so shall not be interpreted as SE’s endorsement of, or acquiescence to, the quality of the Products, the Works or the Services and shall not relieve the Supplier from its obligations set out in Art. 8 of these T&amp;C. SE  shall have the right to examine the Products, Works, or the Services independently upon the delivery of all Products or all Works to the Delivery Point, or upon the completion of all Services under a Purchase Order.\n- 9.3. SE shall: \n\n   - a) issue a Final Acceptance Certificate if the examination does not reveal any Defective Item in the Products, the Works, or the Services; or \n\n   - b) SDI (if requested by SE) serve a Compliance Notice on the Supplier specifying any Defective Item in the Products, Works, or the Services according to Art. 8 of these T&amp;C if SE discovers any such Defective Item.', 'Section 25 of the purchase terms sets out the supplier documentation requirements for delivering products works or services including manuals certificates inspection records warranty certificates and third party IP licenses before delivery completion\n## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.']</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Under the warranty, the Products must comply with:
+- ISO9000
+- ISO26000
+- ISO14001
+- ISO 50001
+- Any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ISO9000, ISO26000, ISO14001 and ISO 50001 (or other internationally recognized applicable standards).</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7750067442234996</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>What is the proprietary web-based tool through which Suppliers must submit invoices?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section is part of the purchase terms and explains that the supplier and its personnel are independent contractors and not agents employees or representatives of SE or SDI\n## 19. INDEPENDENT SUPPLIER\n\nSupplier and his employees, agents, representatives, assigns, sub-suppliers etc. are independent suppliers and shall not be construed as agents, representatives, or employees of SE and/or SDI.', 'Section 5 of the purchase terms covering taxes and GST compliance including supporting documents invoice details reverse charge deductions for loss of input tax credit and reporting noncompliance to tax authorities\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.']</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Suppliers must submit invoices via SDI’s proprietary web-based tool, **Work Nexus®**.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Work Nexus(R), SDI's proprietary web-based tool.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5974345404946122</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A non-MSME supplier delivers goods two weeks late. Explain both the payment timeline that applies and the penalty for the delay.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>['Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>For a non-MSME supplier, SDI processes payment within five (5) business days after SDI receives payment from SE, provided the invoice and required documentation are correct and complete. SE’s payment term to SDI is Net seventy (70) days from SE’s receipt of the invoice.
+For the two-week late delivery, liquidated damages apply at 1% per week of delay, calculated from the due date, on the price of the goods not delivered on time. So the delay penalty would be 2% of the price of the late-delivered goods, subject to the overall cap of 10% of the related Purchase Order price. Any extra costs caused by the late delivery are also borne by the Supplier.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Payment: SE pays SDI on Net 70-day terms for non-MSME vendors (from SE's receipt of invoice), and the Supplier is paid within 5 business days after SDI receives payment from SE. Penalty: liquidated damages of 1% of Price per week of delay, so ~2% for two weeks, subject to the overall 10% cap.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4499999999775</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.867204363890792</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>What are the notice periods for terminating a Purchase Order for convenience versus for an unrectified breach?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>['This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'This chunk is from the Definitions section of Schneider Electric General Terms and Conditions of Purchase and it defines key contract terms including Agreement Alteration Notice and Compliance Notice\n## 1. DEFINITIONS\n\nFor the purpose of, these General Terms and Conditions of Purchase (“T&amp;C”), the following terms shall have the meaning hereby assigned to them unless the context would obviously require otherwise:\n- 1.1. “ **Agreement”** means these T&amp;C and the Purchase Order, collectively;\n- 1.2. “ **Alteration Notice** ” shall have the meaning set out in Art. 15 of these T&amp;C;\n- 1.3. “ **Compliance Notice** ” shall have the meaning set out in Art. 8.4 of these T&amp;C; SDI will provide such a notice to Supplier via e-mail upon being requested to do so by SE.', 'Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.']</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>For termination for convenience: **15 days’ prior notice**.
+For an unrectified breach: the context does not provide a general breach termination notice period. It only states that for late delivery/performance, if the Supplier does not comply within the period in the **Reminder Notice**, or if no period is specified, within **7 days** from the Reminder Notice, SDI may terminate the Purchase Order.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Termination at convenience requires 15 days' prior notice. Termination for default for a rectifiable breach allows termination if the Supplier fails to rectify within 30 days of SDI's notice.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8772765959918571</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>When does title pass to SE, and when does risk pass to SE, and why are they different points in time?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>['This section defines when title ownership and associated rights pass to Schneider Electric and when risk remains with the supplier until final acceptance overriding any Incoterms used in the purchase order\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', 'This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.']</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Unless otherwise stated in the Purchase Order:
+- **Title passes to SE** when:
+  - the Products or Works are delivered to the Delivery Point, or the Services are completed; or
+  - if the Purchase Order is terminated before delivery/completion, when the Supplier receives the termination notice.
+- **Risk passes to SE** only when the Supplier receives the **Final Acceptance Certificate**.
+They are different points in time because Article 7 expressly separates ownership from risk: title may vest in SE at delivery/completion or termination, but risk **nevertheless remains with the Supplier until Final Acceptance Certificate**. Incoterms or other trading terms in the Purchase Order do not alter this rule.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Title/ownership vests with SE when the Products/Works are delivered to the Delivery Point or the Services are completed. Risk, however, remains with the Supplier until the Supplier receives the Final Acceptance Certificate. So title can transfer before risk does.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7649403532204375</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>For a product found defective during the warranty period, what are the Supplier's options and the associated interest rate and time limit?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>['This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 11 of the purchase terms sets out the suppliers insurance obligations requiring adequate insurance coverage from reputable insurers and allowing SDI to suspend performance if proof of coverage or premium payment is not provided\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'This section covers testing inspection and acceptance procedures including SEs right to issue a Compliance Notice and require the supplier to retrieve replace or rectify defective items under the purchase terms\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>For a product found defective during the Warranty Period, the Supplier must, at SDI’s election:
+1. **Collect the defective item at its own cost** and repay the price with **interest at 2% above the prevailing prime lending rate**, calculated from the date SDI paid the price, plus compensate losses; or  
+2. **Repair, rectify, or replace** the defective item at its own cost within the period stated in the Compliance Notice, or if no period is stated, within **15 working days** from the date of the Compliance Notice.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>At SDI's election the Supplier must either (a) collect the defective items and repay the Price with interest at 2% above the prevailing prime lending rate (plus compensate losses), or (b) repair/rectify/replace within the period specified, defaulting to 15 working days. The warranty period is, by default, 12 months.</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8805523076570628</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>What event triggers a 'Compliance Notice', and what must the Supplier do once it receives one? Use the document's own definitions.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>['This section covers testing inspection and acceptance procedures including SEs right to issue a Compliance Notice and require the supplier to retrieve replace or rectify defective items under the purchase terms\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'Section 9 describes the testing inspection and acceptance process for delivered products works and services including defect rectification re testing and the issuance of final acceptance certificate or compliance notice by SE or SDI\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.2. If any defect is discovered in the Products, Works or Services during the testing or inspection, at the request of SDI (on SE’s request to SDI) or their representative, the Supplier shall rectify such defect (or cause such defect to be rectified) and organize another testing or inspection, bearing all costs and expenses for re-testing or re-inspecting including SE’s costs in attending such retesting or re-inspection. For the avoidance of any doubt, SE’s attendance at testing/inspection or failure to do so shall not be interpreted as SE’s endorsement of, or acquiescence to, the quality of the Products, the Works or the Services and shall not relieve the Supplier from its obligations set out in Art. 8 of these T&amp;C. SE  shall have the right to examine the Products, Works, or the Services independently upon the delivery of all Products or all Works to the Delivery Point, or upon the completion of all Services under a Purchase Order.\n- 9.3. SE shall: \n\n   - a) issue a Final Acceptance Certificate if the examination does not reveal any Defective Item in the Products, the Works, or the Services; or \n\n   - b) SDI (if requested by SE) serve a Compliance Notice on the Supplier specifying any Defective Item in the Products, Works, or the Services according to Art. 8 of these T&amp;C if SE discovers any such Defective Item.', 'This chunk is from the Definitions section of Schneider Electric General Terms and Conditions of Purchase and it defines key contract terms including Agreement Alteration Notice and Compliance Notice\n## 1. DEFINITIONS\n\nFor the purpose of, these General Terms and Conditions of Purchase (“T&amp;C”), the following terms shall have the meaning hereby assigned to them unless the context would obviously require otherwise:\n- 1.1. “ **Agreement”** means these T&amp;C and the Purchase Order, collectively;\n- 1.2. “ **Alteration Notice** ” shall have the meaning set out in Art. 15 of these T&amp;C;\n- 1.3. “ **Compliance Notice** ” shall have the meaning set out in Art. 8.4 of these T&amp;C; SDI will provide such a notice to Supplier via e-mail upon being requested to do so by SE.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C']</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A **“Compliance Notice”** is triggered when, during the Warranty Period, **SE finds**—itself or through one of its customers—that any Product, Work, or Service fails to meet the warranties and is therefore a **“Defective Item”**. Under the definition, **SDI provides the Compliance Notice to the Supplier by e-mail when requested by SE**.
+Once the Supplier receives it, the Supplier must, at SDI’s election if requested by SE:
+- **collect the Defective Items at its own cost**, repay the Price with interest, and compensate SE/SDI for losses; or
+- **repair, rectify, or replace the Defective Items at its own cost** within the period stated in the Compliance Notice, or if no period is stated, within **15 working days**.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>The definition of 'Compliance Notice' points to Art. 8.4. It is triggered when SE finds (itself or via a customer) that any Product/Work/Service is a 'Defective Item' during the Warranty Period. On receipt, the Supplier must, at SDI's election, either repay the Price plus 2% above prime lending rate (and compensate losses), or repair/replace within 15 working days.</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9201977565497745</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>If a Purchase Order does not state a warranty period for a Service, when does the warranty begin and how long does it last?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>['This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'Section 11 of the purchase terms sets out the suppliers insurance obligations requiring adequate insurance coverage from reputable insurers and allowing SDI to suspend performance if proof of coverage or premium payment is not provided\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 25 of the purchase terms sets out the supplier documentation requirements for delivering products works or services including manuals certificates inspection records warranty certificates and third party IP licenses before delivery completion\n## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.']</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>If the Purchase Order does not state a warranty period for a Service, the warranty lasts **twelve (12) months** starting from the later of:
+- the date SE issues the **Final Acceptance Certificate** for the relevant Services; or
+- the date the Services are completed.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>It lasts 12 months, running from the date SE issues the Final Acceptance Certificate for the Services or from when the Services are completed, whichever is later. (This requires combining the 'Warranty Period' default with the 'Final Acceptance Certificate' concept.)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8320938821124139</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A supplier has separately negotiated and executed a services agreement. A conflict then arises between that agreement, the Purchase Order, and these T&amp;C. Which prevails, and how do you know?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>['Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'This is the indemnification clause in Schneider Electrics General Terms and Conditions of Purchase defining the Suppliers duty to indemnify SE and SDI for losses liabilities injuries defects breaches negligence and liens arising from the products works services or purchase order performance\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.', 'Section 25 of the purchase terms sets out the supplier documentation requirements for delivering products works or services including manuals certificates inspection records warranty certificates and third party IP licenses before delivery completion\n## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.', 'This chunk is from the Definitions section of Schneider Electric General Terms and Conditions of Purchase and it defines key contract terms including Agreement Alteration Notice and Compliance Notice\n## 1. DEFINITIONS\n\nFor the purpose of, these General Terms and Conditions of Purchase (“T&amp;C”), the following terms shall have the meaning hereby assigned to them unless the context would obviously require otherwise:\n- 1.1. “ **Agreement”** means these T&amp;C and the Purchase Order, collectively;\n- 1.2. “ **Alteration Notice** ” shall have the meaning set out in Art. 15 of these T&amp;C;\n- 1.3. “ **Compliance Notice** ” shall have the meaning set out in Art. 8.4 of these T&amp;C; SDI will provide such a notice to Supplier via e-mail upon being requested to do so by SE.', 'This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.']</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>The separately negotiated and executed services agreement prevails to the extent of any discrepancy or conflict.
+Section 2.1 says:
+- If the Purchase Order conflicts with the T&amp;C, the T&amp;C prevail.
+- But if the parties specifically negotiate and execute a services agreement, that services agreement prevails over the T&amp;C to the extent of the conflict.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Normally the T&amp;C prevail over an inconsistent Purchase Order. However, where the parties specifically negotiate and execute a services agreement, that services agreement prevails over the T&amp;C to the extent of any conflict. (The Order of Precedence on p.1 plus Art. 2.1 establish this.)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9111330361164227</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>At what exact point are Products considered 'delivered' so that the payment process can begin? Pull together every condition the document attaches.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>['This section is part of the purchase terms for Schneider Electric and explains when delivery or performance is deemed complete under a purchase order including required placement at the delivery point notice of completion supporting documents and any replacement or repair obligations before acceptance\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'Definitions section listing key contractual terms for payment documentation price privacy laws product purchase order and the relevant Schneider Electric India entity SE \n## 1. DEFINITIONS\n\n- 1.9. “ **Payment Documentation** ” means all documents which are either a) specified in the Purchase Order which must be sent and approved by SDI as the condition for the payment of the Price; or b) if the relevant Purchase Order fails to specify the Payment Documentation: (i) a commercial invoice correctly stating the Price, (ii) (if applicable) a photocopy / original copy of the Final Acceptance Certificate bearing the SE’s (or its representative’s) signature; and (iii) if any third party Intellectual Property Right is involved in the manufacture, use, or delivery of the Products, Works or Services, all necessary documents or certificates which prove that the SE has the right to use, sell, or otherwise dispose the Products, the Works, or the Services; \n\n- 1.10.“ **Price** ” means the price for the Products, the Works or Services which SDI is obliged to pay to the Supplier under a relevant Purchase Order; \n\n\n\n- 1.11.“ **Privacy Laws** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.12.“ **Product** ” means any product which the SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.13.“ **Purchase Order** ” means any document which the SDI and the Supplier enter into which contemplates a transaction under which the Supplier is to deliver certain Products or Works to, or provide certain Services to, the SE; \n\n- 1.14.“ **SE** ” means the relevant Schneider Electric India entity on whose behalf SDI will place the Purchase Order on the Supplier, which shall include any of the following Schneider Electric India entities mentioned below: \n\n   - 1.14.1.Schneider Electric India Private Limited; \n\n   - 1.14.2.Schneider Electric Private Limited; \n\n   - 1.14.3.Schneider Electric IT Business India Private Limited \n\n   - 1.14.4.Schneider Electric President Systems Limited \n\n   - 1.14.5.Schneider Electric Infrastructure Limited \n\n   - 1.14.6.Schneider Electric Systems India Private Limited (formerly known as Invensys India Private Limited) \n\n   - 1.14.7.Eurotherm India Private Limited \n\n   - 1.14.8.Energy Grid Automation Transformers &amp; Switchgear India Private Limited; and \n\n   - 1.14.9.Schneider Electric Solar India Private Limited.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.']</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Unless the Purchase Order states otherwise, Products are considered “delivered” only when all of these conditions are met:
+1. **All Products and all Works under the relevant Purchase Order** have been placed at the **Delivery Point** and are **ready for pick up or use**.
+2. **SE and SDI have received the Supplier’s notification** of delivery and completion.
+3. **SE and SDI have received all documents required under Art. 24** of the T&amp;C.
+4. If any Product, Work, or Service requires **replacement or repair under Art. 8.4**, delivery is not complete until that replacement/repair-related delivery or completion has occurred and a **Final Acceptance Certificate** has been issued.
+For payment to begin, the Supplier must also provide the required **Payment Documentation** and have it approved by SDI. If the Purchase Order does not specify the documents, this includes:
+- a correct commercial invoice stating the Price;
+- if applicable, a copy/original of the **Final Acceptance Certificate** signed by SE or its representative;
+- if third-party IP is involved, documents proving SE’s right to use, sell, or dispose of the Products, Works, or Services.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Products/Works are not considered delivered until: (a) all are placed at the Delivery Point ready for pickup/use; (b) SE and SDI receive the Supplier's delivery/completion notification; (c) all required documents are received; and (d) where repair/replacement applied, the relevant Final Acceptance Certificate is issued. Only once delivery is complete and a compliant invoice is submitted does the payment timeline run.</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.8758424411380648</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>What late-payment interest rate must SDI pay the Supplier if SDI pays after the due date?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>['Section 5 of the purchase terms covering taxes and GST compliance including supporting documents invoice details reverse charge deductions for loss of input tax credit and reporting noncompliance to tax authorities\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.', 'This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>I don’t know. The context does not specify any late-payment interest rate that SDI must pay the Supplier if SDI pays after the due date.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>The document does not specify any late-payment interest payable by SDI to the Supplier. (It specifies interest on defective-item repayments and on GST/credit reversals, but not a penalty for SDI's late payment.) The correct response is that this is not stated.</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8874999999778125</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8448491631243153</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>What is the minimum order value or monetary threshold required to raise a Purchase Order under these terms?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>['This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'This section is part of the purchase terms for Schneider Electric and explains when delivery or performance is deemed complete under a purchase order including required placement at the delivery point notice of completion supporting documents and any replacement or repair obligations before acceptance\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The document does not state any minimum order value or monetary threshold for a Purchase Order. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.99999999998</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.0284605604661656</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>How many days of paid leave are the Supplier's on-site personnel entitled to?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>['This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section is part of the purchase terms and explains that the supplier and its personnel are independent contractors and not agents employees or representatives of SE or SDI\n## 19. INDEPENDENT SUPPLIER\n\nSupplier and his employees, agents, representatives, assigns, sub-suppliers etc. are independent suppliers and shall not be construed as agents, representatives, or employees of SE and/or SDI.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Not addressed. This is a purchase T&amp;C, not an employment contract; it expressly states the Supplier's personnel are independent and not employees of SE/SDI, but says nothing about their leave entitlements. The correct response is that this is not covered.</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.8874999999778125</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.07576467665923348</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>In which currency must invoices be denominated?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'Section 5 of the purchase terms covering taxes and GST compliance including supporting documents invoice details reverse charge deductions for loss of input tax credit and reporting noncompliance to tax authorities\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.', 'Definitions section listing key contractual terms for payment documentation price privacy laws product purchase order and the relevant Schneider Electric India entity SE \n## 1. DEFINITIONS\n\n- 1.9. “ **Payment Documentation** ” means all documents which are either a) specified in the Purchase Order which must be sent and approved by SDI as the condition for the payment of the Price; or b) if the relevant Purchase Order fails to specify the Payment Documentation: (i) a commercial invoice correctly stating the Price, (ii) (if applicable) a photocopy / original copy of the Final Acceptance Certificate bearing the SE’s (or its representative’s) signature; and (iii) if any third party Intellectual Property Right is involved in the manufacture, use, or delivery of the Products, Works or Services, all necessary documents or certificates which prove that the SE has the right to use, sell, or otherwise dispose the Products, the Works, or the Services; \n\n- 1.10.“ **Price** ” means the price for the Products, the Works or Services which SDI is obliged to pay to the Supplier under a relevant Purchase Order; \n\n\n\n- 1.11.“ **Privacy Laws** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.12.“ **Product** ” means any product which the SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.13.“ **Purchase Order** ” means any document which the SDI and the Supplier enter into which contemplates a transaction under which the Supplier is to deliver certain Products or Works to, or provide certain Services to, the SE; \n\n- 1.14.“ **SE** ” means the relevant Schneider Electric India entity on whose behalf SDI will place the Purchase Order on the Supplier, which shall include any of the following Schneider Electric India entities mentioned below: \n\n   - 1.14.1.Schneider Electric India Private Limited; \n\n   - 1.14.2.Schneider Electric Private Limited; \n\n   - 1.14.3.Schneider Electric IT Business India Private Limited \n\n   - 1.14.4.Schneider Electric President Systems Limited \n\n   - 1.14.5.Schneider Electric Infrastructure Limited \n\n   - 1.14.6.Schneider Electric Systems India Private Limited (formerly known as Invensys India Private Limited) \n\n   - 1.14.7.Eurotherm India Private Limited \n\n   - 1.14.8.Energy Grid Automation Transformers &amp; Switchgear India Private Limited; and \n\n   - 1.14.9.Schneider Electric Solar India Private Limited.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The document does not specify a currency for invoices. It details required invoice fields, taxes and GST handling, but no currency is stated. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.99999999998</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.02484482910675776</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>List every distinct deadline or response window the Supplier must observe across the whole contract.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>['This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.']</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>The distinct Supplier deadlines/response windows stated in the context are:
+- **Within 5 working days from the Alteration Notice**: respond to SDI with additional cost/time, reasons for inability, or agreement to perform without extra cost/time.
+- **Within the period stated in a Reminder Notice** for late delivery/performance; if no period is stated, **within 7 days from the date of the Reminder Notice**.
+- **Immediately upon termination notice**: cease performance and cause subcontractors/suppliers to cease performance.
+- **By the statutory return due dates**: upload invoice details in GST statutory returns.
+- **Within 3 working days from receipt of the Purchase Order**: provide SE and/or SDI written information on applicable export controls and required permits/licenses.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Examples spanning the document: 15 days to challenge a debit note (Art. 4); 5 working days to respond to an Alteration Notice (Art. 15.1); 7 days to act after a Reminder Notice if none specified (Art. 6.3); 30 days to rectify a rectifiable breach (Art. 14.1(b)); 15 working days to repair/replace a Defective Item if none specified (Art. 8.4); 3 working days to supply export-control info after PO receipt (Art. 23); 24 hours to notify a Security Incident (Art. 31.3); 45 calendar days to pay set-off amounts (Art. 17). A complete answer requires sweeping the entire document.</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8055555555287036</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4705007251468653</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Summarize every scenario in which SE or SDI may withhold, deduct, or recover money from the Supplier.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>["Section 17 of Schneider Electric General Terms and Conditions of Purchase on set off and withholding rights allowing SDI and SE to deduct or withhold payments for breaches, nonconforming services, and other amounts owed by the supplier\n## 17. SET-OFF\n\nSDI (in consultation with SE) may withhold amounts due under this Agreement on account of:  (a) claims arising out of or related to Supplier's breach or reasonably anticipated breach of this Agreement, (b) any amounts owed by Supplier to SE and/or SDI under this Agreement or otherwise; (c) non-conforming or deficient Services not yet corrected; (d) a reasonable doubt that Supplier can complete the Services for the unpaid portion of the Agreement price; or (e) any amounts owed by Supplier to SE and/or SDI or to an Affiliate under any other contracts, claims, demands, lawsuits or other matters.  If amounts owed by Supplier to SE and/or SDI exceed the unpaid balance of this Agreement, Supplier agrees to pay those amounts within forty-five calendar days after receipt of SDI’s notice identifying the amounts due.", 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'This is the indemnification clause in Schneider Electrics General Terms and Conditions of Purchase defining the Suppliers duty to indemnify SE and SDI for losses liabilities injuries defects breaches negligence and liens arising from the products works services or purchase order performance\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.']</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SE or SDI may withhold, deduct, set off, or recover money from the Supplier in these scenarios:
+- **Set-off / withholding generally:** SDI, in consultation with SE, may withhold amounts due for:
+  - Supplier’s breach or reasonably anticipated breach.
+  - Any amounts Supplier owes SE and/or SDI under the Agreement or otherwise.
+  - Non-conforming or deficient Services not yet corrected.
+  - Reasonable doubt that Supplier can complete the Services for the unpaid Agreement price.
+  - Amounts owed by Supplier to SE, SDI, or an Affiliate under other contracts, claims, demands, lawsuits, or other matters.
+  - If amounts owed exceed the unpaid balance, Supplier must pay the excess within 45 calendar days after SDI’s notice.
+- **Intellectual property claims:** If a third party brings or threatens an IP infringement claim, Supplier must indemnify SE and SDI for liabilities, losses, damages, legal fees, court costs, and other claim-resolution costs. SE and SDI may also withhold money due or to become due to Supplier, or require additional security.
+- **Packing and shipping issues:** Supplier must bear losses or damage caused by insufficient packing, including costs, expenses, freight, and taxes for return and redelivery. Supplier must indemnify SE and/or SDI for increased costs caused by improper or delayed shipping documents, including storage, demurrage, and tariff charges. SE and SDI may deduct amounts owed from payments due or to become due.
+- **Termination for Supplier default:** If SDI terminates for default, SDI pays only for Products, Works, or Services SE received and elects to keep. Supplier must repay SDI for any Products or Works paid for but not received or returned to Supplier.
+- **Indemnification generally:** Supplier must indemnify SE, SDI, and affiliates for liabilities, losses, damages, and expenses, including reasonable attorney’s fees, arising from:
+  - Manufacture or delivery of Products or Works, or provision of Services.
+  - Performance or breach of obligations under the Purchase Order or T&amp;C.
+  - Death, bodily injury, or property damage from use, defects, warranty non-compliance, or Supplier’s execution of the Purchase Order.
+  - Intentional, wrongful, or negligent acts or omissions by Supplier, affiliates, or subcontractors.
+  - Liens or encumbrances relating to Products, Works, or Services.
+  - Consequential and incidental losses caused by Supplier’s breach.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Across the document these include: GST/input-tax-credit non-compliance withholding and recovery (Art. 5); debit notes for volume/quality/price disputes (Art. 4); set-off of amounts owed (Art. 17); liquidated damages for late delivery (Art. 6); repayment plus interest for Defective Items (Art. 8.4); deductions for losses from improper packing/shipping (Art. 21); and withholding money on third-party IP-infringement claims (Art. 12.1). A complete answer requires aggregating many sections.</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9999999999666667</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5585156165616608</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Overall, what are the main categories of obligation this contract places on the Supplier?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>['This section sets the rules for assigning rights and subcontracting obligations under the purchase agreement including SDIs right to transfer its interests and the Suppliers need for prior written consent to subcontract or assign work\n## 20. ASSIGNMENT AND SUBCONTRACTING\n\nSDI shall have the right to assign its rights or obligations under the Agreement in part or in whole to any third party (including its affiliate) by notice to, but without consent of, the Supplier. However, the Supplier shall not assign or subcontract any obligation under the Agreement to any third party without the prior written consent of SDI. Without prejudice to the foregoing, SDI’s consent to the assignment or sub-contracting shall not release the Supplier from the obligations under the Agreement which have been assigned or subcontracted. Supplier assumes full responsibility to SE and SDI for the improper acts and omissions of its subcontractors or others employed or retained by Supplier in connection with the Agreement.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.']</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The contract places the main categories of obligations on the Supplier as follows:
+- **Assignment and subcontracting controls:** Supplier cannot assign or subcontract obligations without SDI’s prior written consent and remains responsible for assigned/subcontracted work and subcontractor acts or omissions.
+- **Export control compliance:** Supplier must comply with export/re-export laws, obtain required permits/licenses, provide required information to SE/SDI, notify changes, and indemnify SE/SDI for non-compliance.
+- **Packing, shipping, and documentation:** Supplier must properly pack products/works, prepare shipping and customs documents correctly and on time, and cover losses or extra costs caused by failures.
+- **Warranty and quality standards:** Supplier must ensure works and services meet purchase order requirements, applicable specifications, high performance standards, and listed quality standards.
+- **Termination support:** If SDI terminates for convenience, Supplier must stop work, protect and hand over completed products/works and documents, address subcontractor/supplier commitments, and accept payment only for completed conforming items/services, with no claim for lost profits.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>High-level themes spanning the contract: deliver on time and to spec (Arts. 6, 8, 9); provide warranties and remedy defects (Art. 8); carry insurance (Art. 11); indemnify SE/SDI (Art. 10); respect and assign IP rights (Art. 12); maintain confidentiality (Arts. 1.4, 26); comply with tax/GST, export-control and other laws (Arts. 5, 22, 23); protect data and meet cyber-security minimums (Arts. 24, 31); supply documentation (Art. 25); and follow the Business Partner Code of Conduct (Art. 30). This is a whole-document synthesis.</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.926829268292683</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.645320347788251</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>List all the ways a Purchase Order can be terminated under this contract and the condition for each.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>['This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'Section 26 of the Schneider Electric General Terms and Conditions of Purchase sets out the suppliers confidentiality obligations including permitted disclosure on a need to know basis return or destruction of confidential materials and survival of the duty after completion or termination\n## 26. CONFIDENTIALITY\n\nThe Supplier shall keep all Confidential Information secret and shall not use any of it for any purpose other than the performance of the Agreement, except that, for the purpose of performance of the Agreement, the Supplier is allowed to disclose any Confidential Information, on a need-to-know basis, to his employees, subcontractors, or suppliers who undertake in writing not to disclose or otherwise misuse the Confidential Information. Upon the request by SDI, the Supplier shall execute a separate non-disclosure agreement in the form reasonably satisfactory to the SDI, undertaking not to disclose or misuse the Confidential Information.  If any Purchase Order is completed or otherwise terminated, the Supplier shall return or destroy (at the SDI’s request), at its own costs, all documents or other media which contain any Confidential Information.  The obligation set out in this Article or in any non-disclosure agreement shall survive the termination or completion of any Purchase Order or the Agreement.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>A Purchase Order can be terminated in the following ways:
+1. **Termination for convenience (Art. 13)**
+   - **Who:** SDI, in consultation with SE.
+   - **Condition:** Without cause, in whole or in part, by giving the Supplier **15 days’ prior notice**.
+   - Supplier is paid only for completed conforming Products, Works, or Services, with no lost profits.
+2. **Termination for default (Art. 14)**
+   - **Who:** SDI, in consultation with SE.
+   - **Condition:** Immediate termination, wholly or partially, if the Supplier:
+     - breaches a material provision;
+     - breaches any provision and fails to rectify it within **30 days** after notice, if rectifiable;
+     - fails to deliver Products/Works or complete Services as described in Art. 6.3;
+     - refuses to proceed with performance of the Purchase Order; or
+     - becomes insolvent, bankrupt, enters winding up, receivership, judicial management, assigns substantial assets to creditors, or otherwise risks depriving SE or SDI of substantial benefit.
+3. **Termination for late delivery or late performance (Art. 6.3 / Art. 14)**
+   - **Who:** SDI, in consultation with SE.
+   - **Condition:** If the Supplier fails to deliver Products/Works or provide Services within the period stated in a Reminder Notice, or if no period is stated, within **7 days** from the Reminder Notice.
+4. **Termination following a Change Order issue (Art. 15.3 / Art. 13)**
+   - **Who:** SDI, in consultation with SE.
+   - **Condition:** If, after an Alteration Notice:
+     - the Supplier says it cannot perform the alteration; or
+     - the Supplier requests additional cost or time and SE or SDI does not agree.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Termination at convenience: by SDI without cause on 15 days' notice (Art. 13). Termination for default: immediately, on a material breach, an unrectified breach (30 days), failure to deliver after a Reminder Notice, refusal to perform, or insolvency/bankruptcy (Art. 14). Via change order: if the parties cannot agree on a rejected/extra-cost Alteration Notice, SDI may terminate under Art. 13 (Art. 15.3). Delivery failure: termination after an unmet Reminder Notice period (Art. 6.3). Requires gathering distant sections.</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.32499999998375</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6661221894976357</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/baseline_scores.xlsx
+++ b/baseline_scores.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hyde_expander_fusion" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hyde_expander_contextual_retrie" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crag(hyde_expander_rewritter_fusion_rerank)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="selfRAG(hyde_expander_rewritter_fusion_rerank)" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -7959,4 +7960,1073 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>user_input</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>retrieved_contexts</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>context_recall</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>llm_context_precision_with_reference</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>faithfulness</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>semantic_similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What is the maximum cap on accumulated liquidated damages?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>['Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets the liability limits for Schneider Electric and SDI under the purchase agreement and excludes most indirect damages while capping their maximum exposure to undisputed supplier invoice payments\n## 16. LIMITATION ON LIABILITY\n\nIn no event shall SE, SDI or their affiliates, employees, officers, and directors be liable for any punitive, consequential, incidental, special, or indirect damages, in any action arising from or related to this Agreement, whether based in contract, tort (including negligence), intended conduct or otherwise, including without limitation, damages relating to the loss of profits, business, income, savings, use, goodwill or revenue.  Notwithstanding anything contained herein, SE’s and/or  SDI’s maximum liability shall be limited to the payments to be made to Supplier on undisputed invoices.', 'This is the indemnification clause in Schneider Electrics General Terms and Conditions of Purchase defining the Suppliers duty to indemnify SE and SDI for losses liabilities injuries defects breaches negligence and liens arising from the products works services or purchase order performance\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.']</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The accumulated liquidated damages shall not exceed **10% of the Price of the related Purchase Order**.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10% of the Price of the related Purchase Order.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5739684842059045</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Which country's laws govern the Agreement?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>['This section appears in the General Terms and Conditions of Purchase governing Schneider Electric orders placed by SDI and sets a legal compliance obligation for the Supplier within the broader procurement agreement.\n## 22. COMPLIANCE WITH LAWS\n\nThe Supplier shall comply with all applicable laws in its performance of the Agreement, including without limitation, those set forth in Art. 22 and 23 of these T&amp;C.', 'This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'This section appears near the end of the Schneider Electric General Terms and Conditions of Purchase and sets the severability rule for the Agreement meaning if one clause is invalid the rest remains in force\n## 29. SEVERABILITY\n\nIf any provision of the Agreement is rendered void, illegal or unenforceable by any legislation to which it is subject, it shall, to the extent required, be severed from the Agreement and rendered ineffective as far as possible without modifying the remaining provisions of the Agreement, and shall not in any way affect any other circumstances of or the validity or enforcement of the Agreement.']</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The Agreement is governed by and construed in accordance with the laws of **India**.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The laws of India.</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.633480319731221</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>How many days does the Supplier have to challenge a debit note?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.']</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The Supplier has **fifteen (15) days** from the issuing of the debit note to challenge it.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>15 days from the issuing of the debit note.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7763720790285034</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Where will any arbitration proceeding take place?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>['This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'This section covers testing inspection and acceptance procedures including SEs right to issue a Compliance Notice and require the supplier to retrieve replace or rectify defective items under the purchase terms\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section sets the communication rules for the purchase agreement requiring all notices and correspondence between the Supplier and SDI to be in English and sent only through the contact details specified in the Purchase Order unless updated in writing\n## 28. COMMUNICATIONS\n\nAll communications between the Supplier and SDI shall be in English and in the form of e-mails, faxes, or letters and shall be sent to the address or e-mail accounts, or contact numbers (as the case may be) as shown on the Purchase Order, unless one Party otherwise notifies the other Party in writing.']</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Any arbitration proceeding shall take place at New Delhi.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New Delhi.</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5064863301382982</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>If a vendor hands over goods late, how much can be docked for each week the shipment is overdue?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>['Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.']</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>For each week of delay, liquidated damages of **1% of the Price of the Products or Works not yet delivered** may be docked, calculated from the Purchase Order due date.
+The total liquidated damages are capped at **10% of the Price of the related Purchase Order**.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1% of the Price of the undelivered Products/Works (or unprovided Services) per week of delay, capped overall at 10%.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6447900572288305</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Who foots the bill for obtaining the paperwork needed to ship products across borders legally?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>['This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'Section 9 of the purchase terms covering testing inspection and acceptance of products works and services before delivery or completion\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.1. To the extent required by law, applicable industrial standards, or the  Purchase Order, the Supplier shall carry out (and ensure its subcontractors and suppliers carry out), at no cost to the  SE or  SDI, all testing and inspection of the Products, the Works and the Services before it notifies   SE and SDI of the delivery or completion according Art. 6.4(b) of these T&amp;C. The Supplier shall notify the SE and SDI of such testing or inspection; and SE shall have the right (but not obligation) to witness such testing and inspection. The Supplier shall provide the SE with full access to such testing or inspection and all related results.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense."]</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The Supplier foots the bill. The Supplier must obtain all necessary export and re-export permits or licenses at its own expense.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The Supplier, at its own expense, must obtain all necessary export and re-export permits or licenses.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5833333333041666</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8772870858151571</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>How soon does the seller get paid once the integrator has itself received money from the buyer?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section defines when title ownership and associated rights pass to Schneider Electric and when risk remains with the supplier until final acceptance overriding any Incoterms used in the purchase order\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', 'Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.']</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The seller’s payment will be processed within **five (5) business days after SDI receives payment from SE**, provided the required documentation and correctly submitted invoice are in place.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Within 5 business days after SDI receives payment from SE (subject to correct invoicing and documentation).</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8730780116115504</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>If a buyer wants to walk away from an order even though the supplier did nothing wrong, how much advance warning must it give?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>['Section 11 of the purchase terms sets out the suppliers insurance obligations requiring adequate insurance coverage from reputable insurers and allowing SDI to suspend performance if proof of coverage or premium payment is not provided\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>It must give **15 days’ prior notice** to the Supplier.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>15 days' prior notice (termination at convenience / without cause).</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3333333333</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5980731918425751</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Which ISO/IEC standards are named as the alignment benchmark for the Supplier's data-security safeguards?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>['This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'Section on data protection obligations defining SE and SDI content controller roles supplier safeguards breach notification and compliance with privacy laws for services performed under the purchase order\n## 24. DATA PROTECTION LAWS\n\n“SE and SDI Content” means documents, materials and/or data that SE or SDI provides (or is provided on behalf of SE or SDI) in any format to Supplier, including personally identifiable information of SE, SDI, SE’s group companies, the SE’s and SDI’s or its group companies’ employees and/or the SE’s and SDI’s customers, in order for Supplier to perform the Services. The Parties acknowledge and agree that SE and SDI will be the controller of the SE and SDI Content for purposes of all applicable laws relating to data privacy, trans-border data flows and data protection (“Privacy Laws”), with rights to determine the purposes for which SE and SDI Content is processed and the means of processing, and nothing in this Agreement will restrict or limit in any way SE’s or SDI’s rights as owner and/or controller of SE and SDI Content. As such controller of SE and SDI Content, SE and SDI direct Supplier (and Supplier agrees) to process the SE and SDI Content exclusively in accordance with and/or as anticipated by the Agreement and as may be subsequently instructed by SE or SDI, from time to time. Supplier Safeguards: Supplier represents and warrants that it has adopted all reasonable physical, technical and organizational safeguards against accidental, unauthorized or unlawful destruction, loss, alteration, disclosure, access, use processing of the SE and SDI Content. Supplier will immediately notify SE and SDI in the event of any known or suspected unauthorized access to or use of the SE and SDI Content. Without prejudice to the foregoing, the Supplier shall (i) comply with all Privacy Laws; and (ii) not place the SE or SDI in breach of any requirements of Privacy Laws or other valid legal or regulatory process.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.']</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The named alignment benchmarks are **ISO/IEC 27001** or **IEC 62443**.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001 or IEC 62443.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5183742503145388</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Under which Act will disputes be settled by arbitration?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>['This section sets the governing law and arbitration process for disputes under the purchase terms between SDI and the Supplier on behalf of Schneider Electric India.\n## 27. APPLICABLE LAWS AND DISPUTE RESOLUTION\n\n- 27.1.This Agreement shall be governed by and construed in accordance with the laws of India and shall benefit and be binding upon the Parties hereto, their respective successors and assigns. \n\n- 27.2.The Parties agree that, any and all disputes, claims, controversy or causes of action (‘Dispute”) which the Parties are unable to resolve for any reason after negotiations, shall be completely and finally settled by submission of any such Dispute to arbitration to be settled as per the Arbitration and Conciliation Act, 1996 (“IAC”) then in effect. The arbitration shall be heard and determined by a sole arbitrator to be appointed by the SE and SDI. (in consultation with SE).  Any arbitration proceeding shall take place at New Delhi.  The language of the arbitration shall be English. Any award made by the arbitrator shall be final and binding on the Parties. The Parties shall equally bear the costs relating to such arbitration including the arbitrator’s fees. The Agreement shall be subject to exclusive jurisdiction of appropriate court of New Delhi jurisdiction for the purposes only of compelling compliance with the above arbitration provisions and for enforcement of any arbitration award made in accordance with the above provisions.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.', 'This section sets the communication rules for the purchase agreement requiring all notices and correspondence between the Supplier and SDI to be in English and sent only through the contact details specified in the Purchase Order unless updated in writing\n## 28. COMMUNICATIONS\n\nAll communications between the Supplier and SDI shall be in English and in the form of e-mails, faxes, or letters and shall be sent to the address or e-mail accounts, or contact numbers (as the case may be) as shown on the Purchase Order, unless one Party otherwise notifies the other Party in writing.']</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Disputes will be settled by arbitration under the **Arbitration and Conciliation Act, 1996 (“IAC”)**.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The Arbitration and Conciliation Act, 1996 (referred to as 'IAC').</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7468069679384286</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>List the Quality Assessment Standards the Products must comply with under the warranty.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>['This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'Section 9 describes the testing inspection and acceptance process for delivered products works and services including defect rectification re testing and the issuance of final acceptance certificate or compliance notice by SE or SDI\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.2. If any defect is discovered in the Products, Works or Services during the testing or inspection, at the request of SDI (on SE’s request to SDI) or their representative, the Supplier shall rectify such defect (or cause such defect to be rectified) and organize another testing or inspection, bearing all costs and expenses for re-testing or re-inspecting including SE’s costs in attending such retesting or re-inspection. For the avoidance of any doubt, SE’s attendance at testing/inspection or failure to do so shall not be interpreted as SE’s endorsement of, or acquiescence to, the quality of the Products, the Works or the Services and shall not relieve the Supplier from its obligations set out in Art. 8 of these T&amp;C. SE  shall have the right to examine the Products, Works, or the Services independently upon the delivery of all Products or all Works to the Delivery Point, or upon the completion of all Services under a Purchase Order.\n- 9.3. SE shall: \n\n   - a) issue a Final Acceptance Certificate if the examination does not reveal any Defective Item in the Products, the Works, or the Services; or \n\n   - b) SDI (if requested by SE) serve a Compliance Notice on the Supplier specifying any Defective Item in the Products, Works, or the Services according to Art. 8 of these T&amp;C if SE discovers any such Defective Item.', 'Section 25 of the purchase terms sets out the supplier documentation requirements for delivering products works or services including manuals certificates inspection records warranty certificates and third party IP licenses before delivery completion\n## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.']</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The Products must comply with:
+- ISO9000
+- ISO26000
+- ISO14001
+- ISO 50001
+- Any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ISO9000, ISO26000, ISO14001 and ISO 50001 (or other internationally recognized applicable standards).</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8014889357922395</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>What is the proprietary web-based tool through which Suppliers must submit invoices?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section is part of the purchase terms and explains that the supplier and its personnel are independent contractors and not agents employees or representatives of SE or SDI\n## 19. INDEPENDENT SUPPLIER\n\nSupplier and his employees, agents, representatives, assigns, sub-suppliers etc. are independent suppliers and shall not be construed as agents, representatives, or employees of SE and/or SDI.', 'Section 5 of the purchase terms covering taxes and GST compliance including supporting documents invoice details reverse charge deductions for loss of input tax credit and reporting noncompliance to tax authorities\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.']</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Suppliers must submit invoices via SDI’s proprietary web-based tool, **Work Nexus®**.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Work Nexus(R), SDI's proprietary web-based tool.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.597434424258684</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A non-MSME supplier delivers goods two weeks late. Explain both the payment timeline that applies and the penalty for the delay.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>['Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 5 of the purchase terms covering taxes and GST compliance including supporting documents invoice details reverse charge deductions for loss of input tax credit and reporting noncompliance to tax authorities\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.']</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Payment: SE pays SDI on Net 70-day terms for non-MSME vendors (from SE's receipt of invoice), and the Supplier is paid within 5 business days after SDI receives payment from SE. Penalty: liquidated damages of 1% of Price per week of delay, so ~2% for two weeks, subject to the overall 10% cap.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1091739546308006</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>What are the notice periods for terminating a Purchase Order for convenience versus for an unrectified breach?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>['This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'Section 26 of the Schneider Electric General Terms and Conditions of Purchase sets out the suppliers confidentiality obligations including permitted disclosure on a need to know basis return or destruction of confidential materials and survival of the duty after completion or termination\n## 26. CONFIDENTIALITY\n\nThe Supplier shall keep all Confidential Information secret and shall not use any of it for any purpose other than the performance of the Agreement, except that, for the purpose of performance of the Agreement, the Supplier is allowed to disclose any Confidential Information, on a need-to-know basis, to his employees, subcontractors, or suppliers who undertake in writing not to disclose or otherwise misuse the Confidential Information. Upon the request by SDI, the Supplier shall execute a separate non-disclosure agreement in the form reasonably satisfactory to the SDI, undertaking not to disclose or misuse the Confidential Information.  If any Purchase Order is completed or otherwise terminated, the Supplier shall return or destroy (at the SDI’s request), at its own costs, all documents or other media which contain any Confidential Information.  The obligation set out in this Article or in any non-disclosure agreement shall survive the termination or completion of any Purchase Order or the Agreement.', 'Section 6 of the purchase terms setting out delivery and performance obligations and remedies for delay including reminder notices and liquidated damages\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.1. The Parties acknowledge that the time for the delivery of the Products or Works and for the completion of the Services under any Purchase Order is of the essence. In case of any delay in delivery or completion,  SDI (if requested by SE) shall be entitled to: \n\n\n\na) serve a reminder notice (“Reminder Notice”) on the Supplier requesting the delivery of the Products or Works or the completion of the Services immediately or within a period specified in the Reminder Notice; and \n\n   - b) for each week of delay (calculating from the due date provided for in the Purchase Order), liquidated damages of 1% of the Price of the Products or Works which have not yet been delivered, or the Services which have not been provided without prejudice to the other rights or remedies at law or in equity available to SE and/or SDI. The accumulated liquidated damages herein shall not exceed 10% of the Price of related Purchase Order.']</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>- **Termination for convenience:** SDI, in consultation with SE, may terminate a Purchase Order by giving the Supplier **15 days’ prior notice**.
+- **Termination for unrectified breach/delay:** If the Supplier fails to deliver or perform within the period stated in the **Reminder Notice**, or if no period is stated, within **7 days from the date of the Reminder Notice**, SDI may terminate the Purchase Order.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Termination at convenience requires 15 days' prior notice. Termination for default for a rectifiable breach allows termination if the Supplier fails to rectify within 30 days of SDI's notice.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8368131587711432</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>When does title pass to SE, and when does risk pass to SE, and why are they different points in time?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>['This section defines when title ownership and associated rights pass to Schneider Electric and when risk remains with the supplier until final acceptance overriding any Incoterms used in the purchase order\n## 7. TITLE AND RISK\n\n- 7.1. Unless otherwise stated in the Purchase Order, the title and ownership (including any necessary Intellectual Property Rights) in the Products, Works, Services or any other deliverables under the Agreement (including but not limited to any work-in progress, data, drawings, technical documents, and any other works and ideas created during the process of manufacture or the delivery of the Products or Works, or the provision of the Services) shall vest with SE when: \n\n   - a) the Products and Works are delivered to the Delivery Point or the Services are completed (as the case maybe); or b) if any Purchase Order is terminated for whatever reason before the delivery of the Products or Works, or before the completion of the Services, when the Supplier receives the termination notice according to Art. 13 and 14 of these T&amp;C. \n\n- 7.2. The risk of the Products, Works, or Services shall nevertheless remain with the Supplier until the Supplier receives the Final Acceptance Certificate. For the avoidance of any doubt, the issuance of the Final Acceptance Certificate does not release the Supplier from its obligations under Art. 8 of these T&amp;C. \n\n- 7.3. For the avoidance of any doubt, notwithstanding Art. 2.1 of these T&amp;C, any trading terminology (whether defined in the ICC INCOTERMS 2010 or the effective version or otherwise) used in the Purchase Order shall not be interpreted to alter any provision in this Art. 7 of these T&amp;C.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 9 describes the testing inspection and acceptance process for delivered products works and services including defect rectification re testing and the issuance of final acceptance certificate or compliance notice by SE or SDI\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.2. If any defect is discovered in the Products, Works or Services during the testing or inspection, at the request of SDI (on SE’s request to SDI) or their representative, the Supplier shall rectify such defect (or cause such defect to be rectified) and organize another testing or inspection, bearing all costs and expenses for re-testing or re-inspecting including SE’s costs in attending such retesting or re-inspection. For the avoidance of any doubt, SE’s attendance at testing/inspection or failure to do so shall not be interpreted as SE’s endorsement of, or acquiescence to, the quality of the Products, the Works or the Services and shall not relieve the Supplier from its obligations set out in Art. 8 of these T&amp;C. SE  shall have the right to examine the Products, Works, or the Services independently upon the delivery of all Products or all Works to the Delivery Point, or upon the completion of all Services under a Purchase Order.\n- 9.3. SE shall: \n\n   - a) issue a Final Acceptance Certificate if the examination does not reveal any Defective Item in the Products, the Works, or the Services; or \n\n   - b) SDI (if requested by SE) serve a Compliance Notice on the Supplier specifying any Defective Item in the Products, Works, or the Services according to Art. 8 of these T&amp;C if SE discovers any such Defective Item.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.']</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Unless otherwise stated in the Purchase Order, title and ownership pass to SE when:
+- the Products or Works are delivered to the Delivery Point, or the Services are completed; or
+- if the Purchase Order is terminated before delivery/completion, when the Supplier receives the termination notice.
+Risk does not pass at the same time. Risk remains with the Supplier until the Supplier receives the Final Acceptance Certificate.
+They are different points in time because Art. 7 expressly separates ownership from risk: SE may obtain title on delivery/completion, but the Supplier continues to bear risk until final acceptance confirms that no Defective Item is found. Any Incoterms used in the Purchase Order do not change this rule.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Title/ownership vests with SE when the Products/Works are delivered to the Delivery Point or the Services are completed. Risk, however, remains with the Supplier until the Supplier receives the Final Acceptance Certificate. So title can transfer before risk does.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8448805977906371</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>For a product found defective during the warranty period, what are the Supplier's options and the associated interest rate and time limit?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>['This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 11 of the purchase terms sets out the suppliers insurance obligations requiring adequate insurance coverage from reputable insurers and allowing SDI to suspend performance if proof of coverage or premium payment is not provided\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'This section covers testing inspection and acceptance procedures including SEs right to issue a Compliance Notice and require the supplier to retrieve replace or rectify defective items under the purchase terms\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>For a product found defective during the Warranty Period, the Supplier must, at SDI’s election:
+1. **Collect the defective product at its own cost and refund the Price**, with **interest at 2% above the prevailing prime lending rate**, calculated from the date SDI paid the Price; or  
+2. **Repair, rectify, or replace the defective product at its own cost** within the period specified in the Compliance Notice, or if no period is specified, within **15 working days** from the date of the Compliance Notice.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>At SDI's election the Supplier must either (a) collect the defective items and repay the Price with interest at 2% above the prevailing prime lending rate (plus compensate losses), or (b) repair/rectify/replace within the period specified, defaulting to 15 working days. The warranty period is, by default, 12 months.</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8729480966605432</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>What event triggers a 'Compliance Notice', and what must the Supplier do once it receives one? Use the document's own definitions.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>['This section covers testing inspection and acceptance procedures including SEs right to issue a Compliance Notice and require the supplier to retrieve replace or rectify defective items under the purchase terms\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.4. Upon the receipt of the Compliance Notice, the Supplier shall, at SE’s election, retrieve, replace, or rectify the defects according to Art. 8.4 of these T&amp;C.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', 'Section 9 describes the testing inspection and acceptance process for delivered products works and services including defect rectification re testing and the issuance of final acceptance certificate or compliance notice by SE or SDI\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.2. If any defect is discovered in the Products, Works or Services during the testing or inspection, at the request of SDI (on SE’s request to SDI) or their representative, the Supplier shall rectify such defect (or cause such defect to be rectified) and organize another testing or inspection, bearing all costs and expenses for re-testing or re-inspecting including SE’s costs in attending such retesting or re-inspection. For the avoidance of any doubt, SE’s attendance at testing/inspection or failure to do so shall not be interpreted as SE’s endorsement of, or acquiescence to, the quality of the Products, the Works or the Services and shall not relieve the Supplier from its obligations set out in Art. 8 of these T&amp;C. SE  shall have the right to examine the Products, Works, or the Services independently upon the delivery of all Products or all Works to the Delivery Point, or upon the completion of all Services under a Purchase Order.\n- 9.3. SE shall: \n\n   - a) issue a Final Acceptance Certificate if the examination does not reveal any Defective Item in the Products, the Works, or the Services; or \n\n   - b) SDI (if requested by SE) serve a Compliance Notice on the Supplier specifying any Defective Item in the Products, Works, or the Services according to Art. 8 of these T&amp;C if SE discovers any such Defective Item.', 'This chunk is from the Definitions section of Schneider Electric General Terms and Conditions of Purchase and it defines key contract terms including Agreement Alteration Notice and Compliance Notice\n## 1. DEFINITIONS\n\nFor the purpose of, these General Terms and Conditions of Purchase (“T&amp;C”), the following terms shall have the meaning hereby assigned to them unless the context would obviously require otherwise:\n- 1.1. “ **Agreement”** means these T&amp;C and the Purchase Order, collectively;\n- 1.2. “ **Alteration Notice** ” shall have the meaning set out in Art. 15 of these T&amp;C;\n- 1.3. “ **Compliance Notice** ” shall have the meaning set out in Art. 8.4 of these T&amp;C; SDI will provide such a notice to Supplier via e-mail upon being requested to do so by SE.', 'This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C']</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A “Compliance Notice” is triggered when SE finds that any Product, Work, or Service fails or ceases to meet the warranties—i.e., it is a “Defective Item” under Art. 8.4. SDI provides the notice to the Supplier by e-mail when requested by SE.
+Once the Supplier receives it, the Supplier must, at SDI’s/SE’s election:
+- collect the Defective Items at its own cost, repay the price with interest, and compensate for related losses; or
+- repair, rectify, or replace the Defective Items at its own cost within the period stated in the Compliance Notice, or if no period is stated, within 15 working days.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>The definition of 'Compliance Notice' points to Art. 8.4. It is triggered when SE finds (itself or via a customer) that any Product/Work/Service is a 'Defective Item' during the Warranty Period. On receipt, the Supplier must, at SDI's election, either repay the Price plus 2% above prime lending rate (and compensate losses), or repair/replace within 15 working days.</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9063549524446546</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>If a Purchase Order does not state a warranty period for a Service, when does the warranty begin and how long does it last?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>['This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'Section 11 of the purchase terms sets out the suppliers insurance obligations requiring adequate insurance coverage from reputable insurers and allowing SDI to suspend performance if proof of coverage or premium payment is not provided\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 25 of the purchase terms sets out the supplier documentation requirements for delivering products works or services including manuals certificates inspection records warranty certificates and third party IP licenses before delivery completion\n## 25. DOCUMENTATION\n\n- 25.1.Unless otherwise stated in the Order, the Supplier shall supply to the SE, on or before the delivery of the Products or the Works or the completion of the Services, the following documents: \n\n   - a) three copies of the drawings, operating manuals, user manuals, and technical catalogues or literature in relation to the Products, Works, and Services; \n\n   - b) an original copy of quality certificates with respect to the major materials used in manufacturing the Products or the Works, or in providing the Services; \n\n   - c) three copies of statements signed by the Supplier confirming the relevant Products, Works, or Service have passed inspection and testing according to Art. 9 of these T&amp;C; \n\n   - d) one original warranty certificate with respect to each Product and each Work which shall restate the Supplier’s aftersales obligations under Art. 8.4 of these T&amp;C; and \n\n   - e) if any third party Intellectual Property Rights are used or incorporated into the Products, Works, or Services, a license that such third-party issues to authorize the manufacture, sales, and use of the relevant Products, Works, or Services. \n\n- 25.2.All the above-mentioned documents shall be eligible, accurate, and free-of-error. Unless otherwise stated in the Purchase Order, all the documents shall be written in English language. The Supplier shall be responsible for any loss or damages suffered by SE or SDI as a result of the use of documentation which contains incorrect or inaccurate information.']</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>If the Purchase Order does not state a warranty period for a Service, the warranty lasts **twelve (12) months** starting from the **later of**:
+- the date SE issues the Final Acceptance Certificate for the relevant Services; or  
+- the date the Services are completed.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>It lasts 12 months, running from the date SE issues the Final Acceptance Certificate for the Services or from when the Services are completed, whichever is later. (This requires combining the 'Warranty Period' default with the 'Final Acceptance Certificate' concept.)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8188069183911464</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A supplier has separately negotiated and executed a services agreement. A conflict then arises between that agreement, the Purchase Order, and these T&amp;C. Which prevails, and how do you know?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>['Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'This is the indemnification clause in Schneider Electrics General Terms and Conditions of Purchase defining the Suppliers duty to indemnify SE and SDI for losses liabilities injuries defects breaches negligence and liens arising from the products works services or purchase order performance\n## 10. INDEMNIFICATION\n\nThe Supplier shall indemnify and hold harmless SE and SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives and assigns) against any and all liabilities, losses, damages and expenses (including reasonable attorney’s fees) which are awarded against or incurred by SE or SDI and their affiliates (including but not limited to SE’s and SDI’s directors, officers, employees, agents, representatives, and assigns ) in connection with the following (a) manufacture or delivery of the Products or the Works, the provision of the Services, or (b) from any performance or breach of any obligation under the Purchase Order or these T&amp;C; (c) death, bodily injury, or loss or damage to real or tangible personal property resulting from the use of or any actual or alleged defect in the Products, Works and/or Services, or from the failure of the Products, Works and/or Services to comply with the warranties hereunder or caused by the Supplier in execution of the Purchase Order; (d) any intentional, wrongful or negligent act or omission of Supplier or any of its affiliates or subcontractors; (e) any liens or encumbrances relating to any Products, Works and/or Services.  The Supplier also acknowledges that any breach of the Purchase Order or these T&amp;C will cause consequential and incidental losses to SE and SDI, which shall be covered by the indemnification set out in the previous paragraph.', 'This chunk is from the Definitions section of Schneider Electric General Terms and Conditions of Purchase and it defines key contract terms including Agreement Alteration Notice and Compliance Notice\n## 1. DEFINITIONS\n\nFor the purpose of, these General Terms and Conditions of Purchase (“T&amp;C”), the following terms shall have the meaning hereby assigned to them unless the context would obviously require otherwise:\n- 1.1. “ **Agreement”** means these T&amp;C and the Purchase Order, collectively;\n- 1.2. “ **Alteration Notice** ” shall have the meaning set out in Art. 15 of these T&amp;C;\n- 1.3. “ **Compliance Notice** ” shall have the meaning set out in Art. 8.4 of these T&amp;C; SDI will provide such a notice to Supplier via e-mail upon being requested to do so by SE.', 'This section continues Article 1 Definitions in the Schneider Electric General Terms and Conditions of Purchase, defining key terms used throughout the procurement agreement including services supplier T&amp;C warranty period and works\n## 1. DEFINITIONS\n\n- 1.15. **“SE Content** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.16.“ **Reminder Notice** ” shall have the meaning set out in Art. 6.1 of these T&amp;C.  SDI will serve such a notice to Supplier via e- mail upon being requested to do so by SE. \n\n- 1.17.“ **Service** ” means any service which SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.18.“ **Supplier** ” means any individual or entity which agrees to supply or is in the process of supplying Products or Services to the SE, regardless of whether a Purchase Order has been entered into; \n\n- 1.19." **T&amp;C** " means these general terms and conditions of purchase and also includes supplements &amp; amendments made by SDI from time to time; \n\n- 1.20.“ **Warranty Period** ” means the period during which the Supplier shall provide after-sales services for the Products, Services or Works, which period shall be: a) a period stated in the relevant Purchase Order or b) if the relevant Purchase Order fails to state a Warranty Period, with respect to any Product: i) a period of twelve (12) months after the relevant Products are delivered to SE; ii) a period of twelve (12) months from the date when SE issues a Final Acceptance Certificate for all Products which the Supplier delivered under the Purchase Order with respect to the relevant Product; or iii) with respect to any Product delivered as a repaired or replaced Product according to Art. 8.4 of these T&amp;C, twelve (12) months after the delivery of the same; whichever occurs later; or with respect to any Service: i) twelve (12) months from the date when SE issues a Final Acceptance Certificate for the relevant Services or when the Services are completed, whichever is later; or ii) with respect to any Work which is repaired or replaced after the Final Acceptance Certificate is granted, twelve (12) months after the such repairing or replacement; \n\n- 1.21.“ **Works** ” means any deliverable (including real property, movable property, document, or media) in relation to which the Service is to be provided, or the output from a Service provided.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.']</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>The separately negotiated and executed services agreement prevails over these T&amp;C to the extent of any discrepancy or conflict.
+Section 2.1 says:
+- These T&amp;C prevail over any inconsistent provision in the Purchase Order.
+- However, if the parties specifically negotiate and execute a services agreement, that services agreement prevails over the T&amp;C to the extent of any discrepancy or conflict.
+So, based on the stated hierarchy: **services agreement prevails over conflicting T&amp;C, and T&amp;C prevail over conflicting Purchase Order terms.** The context does not expressly state a direct rule for a conflict between the services agreement and the Purchase Order.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Normally the T&amp;C prevail over an inconsistent Purchase Order. However, where the parties specifically negotiate and execute a services agreement, that services agreement prevails over the T&amp;C to the extent of any conflict. (The Order of Precedence on p.1 plus Art. 2.1 establish this.)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8796208111443623</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>At what exact point are Products considered 'delivered' so that the payment process can begin? Pull together every condition the document attaches.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>['This section is part of the purchase terms for Schneider Electric and explains when delivery or performance is deemed complete under a purchase order including required placement at the delivery point notice of completion supporting documents and any replacement or repair obligations before acceptance\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'Section 9 describes the testing inspection and acceptance process for delivered products works and services including defect rectification re testing and the issuance of final acceptance certificate or compliance notice by SE or SDI\n## 9. TEST, INSPECTION AND ACCEPTANCE\n\n- 9.2. If any defect is discovered in the Products, Works or Services during the testing or inspection, at the request of SDI (on SE’s request to SDI) or their representative, the Supplier shall rectify such defect (or cause such defect to be rectified) and organize another testing or inspection, bearing all costs and expenses for re-testing or re-inspecting including SE’s costs in attending such retesting or re-inspection. For the avoidance of any doubt, SE’s attendance at testing/inspection or failure to do so shall not be interpreted as SE’s endorsement of, or acquiescence to, the quality of the Products, the Works or the Services and shall not relieve the Supplier from its obligations set out in Art. 8 of these T&amp;C. SE  shall have the right to examine the Products, Works, or the Services independently upon the delivery of all Products or all Works to the Delivery Point, or upon the completion of all Services under a Purchase Order.\n- 9.3. SE shall: \n\n   - a) issue a Final Acceptance Certificate if the examination does not reveal any Defective Item in the Products, the Works, or the Services; or \n\n   - b) SDI (if requested by SE) serve a Compliance Notice on the Supplier specifying any Defective Item in the Products, Works, or the Services according to Art. 8 of these T&amp;C if SE discovers any such Defective Item.', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Products/Works are not considered delivered until: (a) all are placed at the Delivery Point ready for pickup/use; (b) SE and SDI receive the Supplier's delivery/completion notification; (c) all required documents are received; and (d) where repair/replacement applied, the relevant Final Acceptance Certificate is issued. Only once delivery is complete and a compliant invoice is submitted does the payment timeline run.</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.09085865103623453</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>What late-payment interest rate must SDI pay the Supplier if SDI pays after the due date?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>['Section 5 of the purchase terms covering taxes and GST compliance including supporting documents invoice details reverse charge deductions for loss of input tax credit and reporting noncompliance to tax authorities\n## 5. TAXES\n\n- 5.3. If the Supplier fails to furnish necessary supporting documents i.e. tax invoices / customs invoices/ BOE, etc. in respect of the duties, taxes &amp; Cess which are eligible for input tax credit, the amount shall be deducted from the payment due to the Supplier or will be recovered separately, as the case may be.\n- 5.4. If the Supplier does not disclose all the mandatory details correctly on their invoice(s) or on the GSTN which restricts SDI to claim input tax credit or SDI is required to reverse such credit, then the amount of loss of credit will be deducted from the payment due to the Supplier with consequential interest or will be separately recovered, as the case may be.\n- 5.5. In case SDI has to pay GST on reverse charge basis, the Supplier would not charge GST on its invoices. Further, the Supplier undertakes to comply with the provisions of GST law as may be applicable.\n- 5.6. In case of non-payment of GST or delay in payment of GST or any other material non-compliance by the supplier under the GST law, SDI shall reserve right to intimate to the GST authorities about such non-compliance.', 'This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.']</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>The document does not specify any late-payment interest payable by SDI to the Supplier. (It specifies interest on defective-item repayments and on GST/credit reversals, but not a penalty for SDI's late payment.) The correct response is that this is not stated.</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.99999999998</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.05487591016759702</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>What is the minimum order value or monetary threshold required to raise a Purchase Order under these terms?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>['This section sets the minimum data privacy and cyber security obligations for suppliers handling SE or SDI data under the purchase order including permitted use of data security safeguards business continuity incident notification within 24 hours cooperation on investigations and any required security addendum\n## 31. DATA AND CYBER SECURITY TERMS (MINIMUM REQUIREMENTS)\n\n- 31.1.Where Supplier has access to, collects, stores or otherwise processes data from or on behalf of SE or SDI (e.g. including, as the case may, data from SE customers, resellers, or users) in connection with its provision of the Services (“ **Data** ”), including any data that may be generated by the Services itself, Supplier shall at a minimum: \n\n   - i. Only access, collect, store or otherwise process Data for the sole purpose of fulfilling Supplier’s obligations under the Purchase Order, or as otherwise expressly permitted by SE or SDI in writing; \n\n   - ii. Maintain reasonable and appropriate administrative, technical and organizational measures and safeguards to preserve and protect the security, integrity and confidentiality of the Data, aligned with applicable industry standards such as ISO / IEC 27001 or IEC 62443; \n\n   - iii. Should the Services contain any software, firmware or chipsets; the development and productions of such shall demonstrably aligned with good industry practices and standards such as ISO/IEC 27001 or IEC 62443; \n\n\n\n   - iv. Comply with any other privacy or security policies or procedures that SE or SDI may provide or make available from time to time to the Supplier as the context requires; especially when Supplier has access to SE or SDI IT systems or network, either at SE or SDI location or remotely; and \n\n   - v. Any infrastructure, systems, services, products or platforms used by Supplier to access, collect, store, or otherwise process Data, including data gathered from third-parties on behalf of SE or SDI, shall be developed, maintained, and operated in accordance with industry-recognized security requirements and  Secure Development Lifecycle practices, including but not limited to, secure application development, vulnerability management, and compliance with applicable regulations and requirements. \n\n- 31.2.Supplier shall maintain a reasonable and industry appropriate business continuity plan to ensure its provision of the Supply, taking into account data and cybersecurity risks included in its comprehensive risk analyses, contingency plan and solutions for its continuous delivery and operations. \n\n- 31.3.In the event Supplier detects a confirmed or reasonably suspected misuse, compromise, or unauthorized access, destruction, loss, alteration, acquisition or disclosure of any Data, security breach or suspected vulnerability, whether in Suppliers’ IT systems or network, or in relation to the Supplier  (“ **Security Incident** ”): \n\n   - i. Supplier shall notify within twenty-four (24) hours (a) SE through SE’s Supplier Breach Notification Portal at: &lt;u&gt;https://www.se.com/ww/en/work/support/cybersecurity/report-an-incident.jsp#Suppliers; and (b) SDI through e-mail;&lt;/u&gt; \n\n   - ii. Such notification shall contain at a minimum: (a) a brief description of the Security Incident, (b) any  SE or SDI Systems or Data affected by the Security Incident, (c) any persons involved with the Security Incident, including any persons who made any unauthorized use or received an unauthorized disclosure, if known, (d) what Supplier has done or shall due to investigate the Security Incident, to mitigate any deleterious effects, and to protect against any further harm or other similar Security Incidents; and (e) any other information requested by SE or SDI relating to the Security Incident; \n\n   - iii. Take prompt steps to investigate, contain, and remediate any Security Incident and cooperate with SE and SDI in any subsequent investigation and response in connection with the Supplier’s IT systems or networks, or in relation to the Supply, and evidence demonstrating the completion of those activities.  Unless otherwise specified hereto, each party will bear its own cost in relation to its performance and action contemplated as determined herein. \n\n- 31.4.In addition to the above and in case the performance of the Purchase Order necessitates specific or enhanced protection measures for Data, the Parties will enter into a specific and appropriate addendum considering the level of cybersecurity required by the circumstances as reasonably determined by SE and SDI.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.', 'Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.', 'This section is part of the purchase terms for Schneider Electric and explains when delivery or performance is deemed complete under a purchase order including required placement at the delivery point notice of completion supporting documents and any replacement or repair obligations before acceptance\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.4. For the avoidance of doubt, unless otherwise stated in the Purchase Order, the Products or Works shall not be considered to have been delivered and the Service shall not be considered to have been performed until: \n\n   - a) all Products and all Works under the relevant Purchase Order have been placed at the Delivery Point and are ready for pick up, or for use; \n\n   - b)  SE and SDI has received a notification from the Supplier regarding the delivery and completion; \n\n   - c) all documents set out in Art. 24 of these T&amp;C have been received by SE and SDI; and \n\n   - d) if any Product, Work or Service requires replacement or repair according to Art. 8.4 of these T&amp;C, the delivery of the Product or the Work and the completion of the Service with respect to which a Final Acceptance Certificate has been issued.', 'Section 26 of the Schneider Electric General Terms and Conditions of Purchase sets out the suppliers confidentiality obligations including permitted disclosure on a need to know basis return or destruction of confidential materials and survival of the duty after completion or termination\n## 26. CONFIDENTIALITY\n\nThe Supplier shall keep all Confidential Information secret and shall not use any of it for any purpose other than the performance of the Agreement, except that, for the purpose of performance of the Agreement, the Supplier is allowed to disclose any Confidential Information, on a need-to-know basis, to his employees, subcontractors, or suppliers who undertake in writing not to disclose or otherwise misuse the Confidential Information. Upon the request by SDI, the Supplier shall execute a separate non-disclosure agreement in the form reasonably satisfactory to the SDI, undertaking not to disclose or misuse the Confidential Information.  If any Purchase Order is completed or otherwise terminated, the Supplier shall return or destroy (at the SDI’s request), at its own costs, all documents or other media which contain any Confidential Information.  The obligation set out in this Article or in any non-disclosure agreement shall survive the termination or completion of any Purchase Order or the Agreement.']</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The document does not state any minimum order value or monetary threshold for a Purchase Order. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.99999999998</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.02846049730589946</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>How many days of paid leave are the Supplier's on-site personnel entitled to?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>['This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'This section is part of the purchase terms and explains that the supplier and its personnel are independent contractors and not agents employees or representatives of SE or SDI\n## 19. INDEPENDENT SUPPLIER\n\nSupplier and his employees, agents, representatives, assigns, sub-suppliers etc. are independent suppliers and shall not be construed as agents, representatives, or employees of SE and/or SDI.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.', "This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.']</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Not addressed. This is a purchase T&amp;C, not an employment contract; it expressly states the Supplier's personnel are independent and not employees of SE/SDI, but says nothing about their leave entitlements. The correct response is that this is not covered.</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9166666666361111</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0757647063566681</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>In which currency must invoices be denominated?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>["This section covers invoice submission through Work Nexus billing requirements debit notes payment timing tied to SE payment to SDI and inspection rejection rights for nonconforming products or services\n## 4. INVOICING AND PAYMENT TERMS\n\nSupplier will be required to submit invoices via SDI’s proprietary web-based tool, Work Nexus® and all invoices shall identify: (i) corresponding SDI’s bill to address (ii) SDI Purchase Order number; (iii) date of invoice issuance (the day when Supplier submits its invoice in Work Nexus®); (iv) the delivery date; (v) the agreed price of the Service Product delivered; (vi) any applicable taxes. SDI reserves the right to suspend payment of any invoice which fails to comply with SDI’s requirements. Any disagreement by SE as regards to the volume or quality of the delivered Product or Service or the invoiced price, shall lead to the issuing of a debit note by SDI. Supplier shall have fifteen (15) days as from the issuing of the debit note to challenge the latter. Each invoice must state the references used by SDI and those of the corresponding Purchase Order and must comply with the provisions of SDI’s Billing Instructions provided to Supplier by SDI after receipt of Purchase Order. Unless otherwise expressly agreed by SDI, a separate invoice must be issued for each Purchase Order and each invoice must contain a description of the invoiced Product and Service and the unit prices and amounts delivered. \n\nSupplier’s payments will be processed within five (5) business days after SDI receives payment from SE; provided that (i) all contractually required documentation has been submitted to SDI, and (ii) Supplier submits its invoice in correct form containing all mandatory details as defined in this clause of T&amp;C and SDI’s Billing Instructions, and (iii) SDI will have no obligation to pay Supplier unless and until SE pays SDI for the invoiced Service and Product. SE’s payment terms to SDI are Net seventy (70) days for Non-MSME vendors and net thirty-five (35) days for MSME vendors from receipt of the invoice by SE. \n\nPayment will not be deemed acceptance of Products or Services, and such Products or Services will be subject to inspection, test, acceptance or rejection. At SE's or SDI’s option, SE and/or SDI may reject Products or Services that do not comply with SE's acceptance criteria, or require Supplier to repair or replace such Products or re-perform such Services without charge and in a timely manner. SE and/or SDI may return non-conforming Products to Supplier at Supplier's expense.", 'This section appears in the General Terms and Conditions of Purchase and sets out the tax compliance obligations for the supplier including GST invoicing input tax credit requirements withholding of GST payment and correct HSN SAC classification.\n## 5. TAXES\n\n- 5.1. The Supplier is legally responsible for proper &amp; correct compliances under GST to facilitate Availment of Input Tax Credit by SDI. Supplier shall declare the details of the invoices in their statutory returns to be uploaded by the due dates. SDI reserves right to withhold payment of GST amount if the same is not reflected in the applicable statutory Form of SDI on GSTN portal. Such payment shall remain withheld till the time SDI is provided evidence that such invoice has been uploaded on GSTN portal and GST has been paid. Consequential interest shall also be withheld from the payment due against supply bills. In absence of a suitable timely response a Debit Note will be issued to appropriate the amount withheld and/ or to raise recovery of the appropriate amount. SDI also reserves right to take a proper legal recourse.\n- 5.2. The Supplier shall furnish the correct HSN / SAC classification /Customs tariff Head in their quotation/invoices. If the credit for the duties, taxes and Cess under GST provision/ rules is found to be not admissible at any stage subsequently owing to wrong tariff head, then the Supplier shall be liable to refund/pay such non-admissible credit amount with consequential interest.', 'Definitions section listing key contractual terms for payment documentation price privacy laws product purchase order and the relevant Schneider Electric India entity SE \n## 1. DEFINITIONS\n\n- 1.9. “ **Payment Documentation** ” means all documents which are either a) specified in the Purchase Order which must be sent and approved by SDI as the condition for the payment of the Price; or b) if the relevant Purchase Order fails to specify the Payment Documentation: (i) a commercial invoice correctly stating the Price, (ii) (if applicable) a photocopy / original copy of the Final Acceptance Certificate bearing the SE’s (or its representative’s) signature; and (iii) if any third party Intellectual Property Right is involved in the manufacture, use, or delivery of the Products, Works or Services, all necessary documents or certificates which prove that the SE has the right to use, sell, or otherwise dispose the Products, the Works, or the Services; \n\n- 1.10.“ **Price** ” means the price for the Products, the Works or Services which SDI is obliged to pay to the Supplier under a relevant Purchase Order; \n\n\n\n- 1.11.“ **Privacy Laws** ” shall have the meaning set out in Art. 23 of these T&amp;C; \n\n- 1.12.“ **Product** ” means any product which the SDI purchases from the Supplier according to any Purchase Order; \n\n- 1.13.“ **Purchase Order** ” means any document which the SDI and the Supplier enter into which contemplates a transaction under which the Supplier is to deliver certain Products or Works to, or provide certain Services to, the SE; \n\n- 1.14.“ **SE** ” means the relevant Schneider Electric India entity on whose behalf SDI will place the Purchase Order on the Supplier, which shall include any of the following Schneider Electric India entities mentioned below: \n\n   - 1.14.1.Schneider Electric India Private Limited; \n\n   - 1.14.2.Schneider Electric Private Limited; \n\n   - 1.14.3.Schneider Electric IT Business India Private Limited \n\n   - 1.14.4.Schneider Electric President Systems Limited \n\n   - 1.14.5.Schneider Electric Infrastructure Limited \n\n   - 1.14.6.Schneider Electric Systems India Private Limited (formerly known as Invensys India Private Limited) \n\n   - 1.14.7.Eurotherm India Private Limited \n\n   - 1.14.8.Energy Grid Automation Transformers &amp; Switchgear India Private Limited; and \n\n   - 1.14.9.Schneider Electric Solar India Private Limited.', 'This section from the General Terms and Conditions of Purchase covers tax compliance invoice upload TDS deductions payment withholding for shortages or disputes and recovery of tax losses from the supplier\n## 5. TAXES\n\n- 5.7. SDI shall reserve the right of uploading a Valid invoice on the GSTN Portal which has been missed or not uploaded by the Supplier after supplying the goods or services.  In case Supplier do not perform the required action from his end within next two tax periods subsequent to the month in which such invoice details are uploaded by the SDI then interest as applicable on reversal of input tax credit has to be borne by the supplier.\n- 5.8. In case supplier gets black listed/ de-registered during the business relationship then supplier shall indemnify SDI with tax and appropriate interest amount to ensure that no loss is borne by SDI due to default of supplier.\n- 5.9. TDS shall be deducted at the prescribed rate, if any (as the case may be).\n- 5.10. In case where shortages/damages are intimated to the Supplier in writing, the balance payment shall be released only after the cases are settled in accordance with the provision of the Purchase Order. Further, in case of any dispute on the payment to be made to the Supplier, the same shall be settled on or before the month of September following the end of financial year to which the invoice pertains. Additionally, in case the dispute is not settled due to any act of the Supplier and input credit on the said invoice is lost by SDI, the same shall be recovered from the Supplier.', 'This section sets out the pricing rules under the purchase terms including fixed firm prices and what costs taxes duties transportation delivery administration and insurance are included in the price\n## 3. PRICES\n\nUnless otherwise stated in the Purchase Order, all Prices quoted shall remain firm and fixed until the delivery of the Products or Works or the completion of Services under the Purchase Order (in particular, the Prices shall not be escalated for any reason whatsoever); shall include all taxes, duties, levies, and other fees of the same nature arising from the transaction contemplated by the relevant Purchase Order and shall cover all transportation, delivery and administrative costs as well as insurance fees up to the Delivery Point.']</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The document does not specify a currency for invoices. It details required invoice fields, taxes and GST handling, but no currency is stated. The correct response is that this is not specified.</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.99999999998</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.02484480089178914</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>List every distinct deadline or response window the Supplier must observe across the whole contract.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>['This section explains how SDI and SE can change the scope quantities or specifications of a purchase order and how the supplier must respond to any alteration notice including acceptance additional cost or time or refusal and the possibility of termination if no agreement is reached\n## 15. CHANGE ORDER\n\n- 15.1.SDI (in consultation with SE) shall have the right to alter the scope of the Products or Works to be supplied or the Services to be provided at any time before the Products or Works are delivered or the Services are completed (including but not limited to the quantities and specifications of the Products, the Works or the Services) by serving a written notice specifying such alteration (“Alteration Notice”) to the Supplier. The Supplier shall send a response to  SDI within five (5) working days from the date of the Alteration Notice, which response shall: \n\n   - a) set out the additional cost and time (if any) required for performing the Alteration Notice, together with full details supporting the additional cost and time; \n\n   - b) set out the reasons why the Supplier cannot perform the Alteration Notice; or \n\n   - c) set out its agreement to perform the Alteration Notice without additional charges to SE or SDI or additional time for the delivery or performance. \n\n- 15.2.If the Supplier fails to send a response in accordance with the previous paragraph and within the specified time period, it shall be considered to have agreed to perform the Alteration Notice without additional charges or time. \n\n- 15.3.If the Supplier: \n\n   - a) sends a response according to item b) in the first Para. of this Art., or \n\n   - b) sends a response according to item a) in the first Para. of this Art. but SE or SDI do not agree with the additional charges or time, SDI (in consultation with SE) shall have the right to terminate the relevant Purchase Order in accordance with Art. 13 of these T&amp;C', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'This section follows the definitions and sets out the warranty and guarantee remedies for defective products works or services including notice repair replacement collection refund and supplier liability\n## 8. WARRANTY AND GUARANTEE\n\n- 8.4. At any time during the Warranty Period, if SE finds (either by itself or by one of its customers) that any Product, Work, or Service fails to meet (or ceases to meet) any of the warranties stated in the previous paragraphs (“Defective Item”),  SDI (if requested by SE) shall have the right to send a notice (“Compliance Notice”) to the Supplier and the Supplier shall, at  SDI’s election (if requested by SE): \n\n   - a) immediately collect at its own costs, the Defective Items (to the extent applicable) and repay to  SDI (or their designated customer) the Price for the Defective Items with interest at two percent (2%) above the prevailing prime lending rate calculated from the date when SDI paid the Price, and compensate SE and SDI against any losses arising from the purchase, use, or resale of the Defective Items, including the cost of sourcing alternative suppliers and any liabilities owed to the   SDI’s customers (i.e. SE and SE’s customers); or \n\n   - b) repair, rectify, or replace the Defective Items (at its own cost) within the period SDI (in consultation with SE) specifies in the Compliance Notice (or, if the Compliance Notice fails to specify the period, fifteen (15) working days from the date of the Compliance Notice).\n- 8.5. The Supplier shall ensure that its subcontractors and suppliers comply with the obligations set out in this Article as if they were a party to these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>The Supplier must observe these deadlines/response windows:
+- **Alteration Notice:** respond to SDI within **5 working days** of the Alteration Notice.
+- **Delivery/performance:** deliver Products/Works or complete Services within the **agreed time period**.
+- **Reminder Notice for delay:** perform within the period stated in the Reminder Notice, or if none is stated, within **7 days** from the Reminder Notice date.
+- **Export controls:** provide applicable export control rules and required permit/license information within **3 working days** from receipt of the Purchase Order.
+- **Termination at convenience:** upon notice, **immediately** cease performance and cause subcontractors/suppliers to cease.
+- **Warranty defect remedy—collection/refund option:** **immediately** collect Defective Items at its own cost and repay/compensate as required.
+- **Warranty defect remedy—repair/replace option:** repair, rectify, or replace within the period specified in the Compliance Notice, or if none is specified, within **15 working days** from the Compliance Notice date.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Examples spanning the document: 15 days to challenge a debit note (Art. 4); 5 working days to respond to an Alteration Notice (Art. 15.1); 7 days to act after a Reminder Notice if none specified (Art. 6.3); 30 days to rectify a rectifiable breach (Art. 14.1(b)); 15 working days to repair/replace a Defective Item if none specified (Art. 8.4); 3 working days to supply export-control info after PO receipt (Art. 23); 24 hours to notify a Security Incident (Art. 31.3); 45 calendar days to pay set-off amounts (Art. 17). A complete answer requires sweeping the entire document.</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8041666666465626</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4558657451057309</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Summarize every scenario in which SE or SDI may withhold, deduct, or recover money from the Supplier.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>["Section 17 of Schneider Electric General Terms and Conditions of Purchase on set off and withholding rights allowing SDI and SE to deduct or withhold payments for breaches, nonconforming services, and other amounts owed by the supplier\n## 17. SET-OFF\n\nSDI (in consultation with SE) may withhold amounts due under this Agreement on account of:  (a) claims arising out of or related to Supplier's breach or reasonably anticipated breach of this Agreement, (b) any amounts owed by Supplier to SE and/or SDI under this Agreement or otherwise; (c) non-conforming or deficient Services not yet corrected; (d) a reasonable doubt that Supplier can complete the Services for the unpaid portion of the Agreement price; or (e) any amounts owed by Supplier to SE and/or SDI or to an Affiliate under any other contracts, claims, demands, lawsuits or other matters.  If amounts owed by Supplier to SE and/or SDI exceed the unpaid balance of this Agreement, Supplier agrees to pay those amounts within forty-five calendar days after receipt of SDI’s notice identifying the amounts due.", 'Section 12 sets the intellectual property rights rules for the purchase agreement including supplier warranty against infringement indemnity for third party claims and ownership of IP in materials provided by SE and IP created during performance of the agreement\n## 12. INTELLECTUAL PROPERTY RIGHTS\n\n- 12.1.Supplier warrants and declares that he has the unencumbered right to supply Products, to deliver Works, to provide the Services, and to permit SE’s disposal of the Products, Works and Services according to the Purchase Order without infringing any Intellectual Property Right of any third party. If any third party brings or threatens to bring any action or claim against SE or SDI or SE’s customers for infringement of any Intellectual Property Right, whether real or alleged, the Supplier shall indemnify SE and SDI against all and any liability, losses, damages (including legal counsel’s fees, costs of court proceedings, and other costs for resolving the claims) and defend such action or claim at Supplier’s sole expense. In such situation, SE and SDI shall reserve the right to withhold any money due or to be due to Supplier or call upon Supplier to furnish additional security (at an amount which, in the opinion of the SE or SDI, acting reasonably, is necessary). Without prejudice to any remedy available under the Agreement, or otherwise provided by any applicable law, the Supplier shall at its entire expense: a) procure the right for continued use by SE and the  SE’s customers of affected Products, Works or Services; or b) upon the SE’s or SDI’s consent, modify or replace the Products, Works or Services with non-infringing items without changing the quality, specification, performance characteristics or functionality of the relevant Product, Works or Services. \n\n- 12.2.The Parties acknowledge and confirm that: \n\n   - a) all Intellectual Property Rights in the drawings, specifications, documents, and other information which the SE or SDI provides to the Supplier for the manufacture of the Products, the Works, the provision of the Services, or otherwise for the Supplier to perform any obligation under the Agreement shall remain in the SE; and \n\n   - b) any Intellectual Property Rights the Supplier develops (regardless of whether based on the Intellectual Property Rights the SE or SDI provides to it or otherwise) during the course of the performance of the Agreement shall be vested in, or are hereby assigned (and Supplier agrees to assign) to the SE.', 'This section sets out the Suppliers obligations for proper packing shipping documentation customs clearance and liability for related losses or extra costs under the purchase terms\n## 21. PACKING AND SHIPPING\n\nThe Supplier shall adequately pack all Products and Works to protect the Products and Works from hazards during the delivery. Without prejudice to the obligations under Art. 7 and 8 of these T&amp;C, the Supplier shall bear any loss or damage to the Products or Works due to insufficient packing (including any cost, expenses, freight, and tax in relation to the return and redelivery of the damaged Products or Works). The Supplier shall ensure that all shipping marks, instructions and shipping/commercial documents are properly prepared to avoid any delay in customs clearance at destination. All shipping documents shall be dispatched and reach SE and SDI in time for insurance cover and for further processing for customs clearance. Any increased costs (including but not limited to storage, demurrage, tariff charges, etc.) which the SE and/or SDI suffers due to improper preparation of, and/or delay in receipt of, the required shipping documents shall be indemnified by the Supplier.  SE and SDI shall have the right to deduct any amount which the Supplier owes to the SE and SDI from any payment due or to be due to the Supplier.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.']</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SE or SDI may withhold, deduct, set off, or recover money from the Supplier in these scenarios:
+- **Supplier breach or anticipated breach**: SDI may withhold amounts due for claims arising from the Supplier’s breach or reasonably anticipated breach of the Agreement.
+- **Amounts owed by Supplier**: SDI may withhold amounts due for any amounts the Supplier owes to SE and/or SDI under the Agreement or otherwise, including amounts owed under other contracts, claims, demands, lawsuits, or other matters, including to an Affiliate.
+- **Non-conforming or deficient Services**: SDI may withhold amounts for non-conforming or deficient Services not yet corrected.
+- **Doubt about completion**: SDI may withhold amounts if there is reasonable doubt that the Supplier can complete the Services for the unpaid portion of the Agreement price.
+- **Excess amounts owed**: If amounts owed by the Supplier exceed the unpaid balance, the Supplier must pay the excess within 45 calendar days after SDI’s notice identifying the amounts due.
+- **Intellectual property infringement claims**: If a third party brings or threatens an IP infringement claim, the Supplier must indemnify and defend SE and SDI, and SE/SDI may withhold money due or to become due, or require additional security.
+- **Insufficient packing**: The Supplier bears losses or damage to Products or Works caused by insufficient packing, including related return and redelivery costs, expenses, freight, and taxes.
+- **Improper or delayed shipping documents**: The Supplier must indemnify SE and/or SDI for increased costs caused by improper preparation or delayed receipt of required shipping documents, including storage, demurrage, and tariff charges.
+- **Deduction of amounts owed**: SE and SDI may deduct any amount the Supplier owes them from any payment due or to become due to the Supplier.
+- **Termination for default**: If SDI terminates for Supplier default, SDI pays only for Products, Works, or Services that SE has received and elects to keep. The Supplier must repay SDI for any Products or Works already paid for but not received or returned to the Supplier.
+- **Termination for convenience**: If SDI terminates without cause, the Supplier is paid only for manufactured Products, delivered Works, and provided Services existing at the time of notice, and only if they satisfy Agreement requirements. The Supplier cannot recover anticipated or prospective profits or other losses from the termination.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Across the document these include: GST/input-tax-credit non-compliance withholding and recovery (Art. 5); debit notes for volume/quality/price disputes (Art. 4); set-off of amounts owed (Art. 17); liquidated damages for late delivery (Art. 6); repayment plus interest for Defective Items (Art. 8.4); deductions for losses from improper packing/shipping (Art. 21); and withholding money on third-party IP-infringement claims (Art. 12.1). A complete answer requires aggregating many sections.</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9999999999666667</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5424338792922578</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Overall, what are the main categories of obligation this contract places on the Supplier?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>['This section sets the rules for assigning rights and subcontracting obligations under the purchase agreement including SDIs right to transfer its interests and the Suppliers need for prior written consent to subcontract or assign work\n## 20. ASSIGNMENT AND SUBCONTRACTING\n\nSDI shall have the right to assign its rights or obligations under the Agreement in part or in whole to any third party (including its affiliate) by notice to, but without consent of, the Supplier. However, the Supplier shall not assign or subcontract any obligation under the Agreement to any third party without the prior written consent of SDI. Without prejudice to the foregoing, SDI’s consent to the assignment or sub-contracting shall not release the Supplier from the obligations under the Agreement which have been assigned or subcontracted. Supplier assumes full responsibility to SE and SDI for the improper acts and omissions of its subcontractors or others employed or retained by Supplier in connection with the Agreement.', 'This section sets the suppliers obligations to comply with export and re export control laws provide required permits and license information to SE and SDI and indemnify them for any resulting non compliance.\n## 23. EXPORT CONTROLS AND COMPLIANCE\n\nThe Supplier acknowledges that it is fully aware of, and knowledgeable about, the export and re-export controls regulations, ordinances and laws in the jurisdiction from which the Products are exported or the Services are provided and agrees to obtain all necessary export and re-export permits or licenses at the Supplier’s expense to ensure that SE enjoys the full benefit under the relevant Purchase Order and these T&amp;C. Further, the Supplier shall supply SE and/or SDI with the information regarding any applicable export controls rules and required permits or licenses for the Products or Works to be shipped, in writing within three (3) working days from the receipt of Purchase Order. The Supplier shall also notify SE and SDI in writing of any changes to such export and reexport controls regulations and/or permit or licensing requirements which may affect the SE’s benefits under the Agreement. The Supplier undertakes to comply with all export and re-export controls regulations or rules in relation to the delivery of the Products, the Works and the provision of the Services and shall indemnify SE and SDI against all liability, losses, damages, and expenses (including reasonable attorney’s fees) resulting from the Supplier’s non-compliance or violations of such export and re-export controls regulations.', 'Section 8 of the purchase terms sets out warranty and guarantee obligations for the supplier including standards of performance for works and services compliance with specifications and applicable quality standards\n## 8. WARRANTY AND GUARANTEE\n\n- 8.3. With respect to the Works and Services, the Supplier warrants that: a) the Services under the Purchase Order shall be performed by duly competent people and with the commercially highest level of care; \n\n   - b) the Services shall meet the standard set out in the Purchase Order or, if the Purchase Order fails to state the standard, the highest standard in the relevant market; \n\n\n\n   - c) the Works shall comply with the specifications stated in the Purchase Order or, if the Purchase Order fails to state the specification, to conform to the specification which they are normally designed to achieve; \n\n   - d) the Services shall comply with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the provision of the Services; and \n\n   - e) the Services shall satisfy any other requirements set out in the Purchase Order or in these T&amp;C.', 'Section 11 of the purchase terms sets out the suppliers insurance obligations requiring adequate insurance coverage from reputable insurers and allowing SDI to suspend performance if proof of coverage or premium payment is not provided\n## 11. INSURANCE\n\n- 11.1.Unless otherwise provided in the relevant Purchase Order, the Supplier shall, during the term of the relevant Purchase Order until the expiration of the corresponding Warranty Period, at its own costs, maintain the required insurances in respect of all Products, all Services, all Works, and all raw materials used for producing the Products and for providing the Services, to cover its liability under the Agreement. \n\n\n\n- 11.2.The Supplier shall subscribe for insurance from reputable insurers (to the reasonable satisfaction of the SDI (in consultation with SE)). The Supplier shall produce satisfactory evidence of such insurance and of the payment of insurance fees at SDI’s request (in consultation with SE) from time to time.  The Supplier shall comply with all provisions under the relevant insurance policies. \n\n- 11.3.Without prejudice to any remedy available under any law or under the Agreement, SDI (in consultation with SE) shall have the right to order the Supplier to suspend the performance of any relevant Purchase Order unless and until the Supplier produces the proof of insurance coverage, payment of insurance premiums, and the rectification of any breach of the insurance policy (if any). No right to claim any loss, damage, compensation or price escalation shall accrue to the Supplier when performance of any Purchase Order is ordered to be suspended by SDI (in consultation with SE).', 'This section sets out the suppliers warranty and guarantee obligations under the purchase terms including title quality compliance and product performance standards for goods works and services\n## 8. WARRANTY AND GUARANTEE\n\n- 8.1. With respect to the Products, Works and the Services, the Supplier warrants that: a) it has full right to manufacture the Products, to provide the Services, and to deliver the Products and Works pursuant to the Agreement; \n\n   - b) all ownership, title and rights in the Products, Works and in the Services are free from any liens, charges, encumbrances; and \n\n   - c) SE has full right to use, re-sell, or otherwise dispose the Products, the Works and Services.\n- 8.2. With respect to the Products, the Supplier warrants that such Products shall be: a) new at the time when they are delivered to the Delivery Point; \n\n   - b) manufactured with good workmanship by using materials of the commercially best quality; \n\n   - c) free from any defect; \n\n   - d) able to achieve the function stated in the Purchase Order or, if the Purchase Order fails to state the function, to meet the requirements of merchantability and fit for purpose; \n\n   - e) in compliance with ISO9000, ISO26000, ISO14001, ISO 50001 Quality Assessment Standards or any other internationally recognized standards applicable to the manufacture and delivery of the Products or Works, and \n\n   - f) in compliance with any other requirements set out in the Purchase Order or in these T&amp;C.']</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The contract places the main obligations on the Supplier in these categories:
+- **Assignment and subcontracting:** Supplier cannot assign or subcontract obligations without SDI’s prior written consent and remains responsible for assigned/subcontracted work and subcontractors’ acts or omissions.
+- **Export controls and compliance:** Supplier must comply with export/re-export laws, obtain required permits or licenses at its own expense, provide related information to SE/SDI, notify them of changes, and indemnify them for non-compliance.
+- **Warranty and quality obligations:** Supplier warrants title and rights, freedom from liens, product quality, defect-free performance, compliance with specifications, fitness for purpose, and compliance with applicable ISO/international standards.
+- **Services and works standards:** Supplier must perform services with competent personnel, high care, applicable standards, specifications, and Purchase Order requirements.
+- **Insurance:** Supplier must maintain adequate insurance at its own cost, use reputable insurers, provide proof of coverage and premium payment when requested, and comply with insurance policy terms.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>High-level themes spanning the contract: deliver on time and to spec (Arts. 6, 8, 9); provide warranties and remedy defects (Art. 8); carry insurance (Art. 11); indemnify SE/SDI (Art. 10); respect and assign IP rights (Art. 12); maintain confidentiality (Arts. 1.4, 26); comply with tax/GST, export-control and other laws (Arts. 5, 22, 23); protect data and meet cyber-security minimums (Arts. 24, 31); supply documentation (Art. 25); and follow the Business Partner Code of Conduct (Art. 30). This is a whole-document synthesis.</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.9714285714285714</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6709766001464725</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>List all the ways a Purchase Order can be terminated under this contract and the condition for each.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>['This section sets out SDI and SEs right to terminate a purchase order for convenience on 15 days notice and the suppliers obligations to stop work transfer deliverables and subcontractor commitments and accept payment only for completed conforming goods works or services with no claim for lost profits\n## 13. TERMINATION AT CONVENIENCE\n\n- 13.1.  SDI (in consultation with SE) shall have the right to terminate a Purchase Order in part or in whole, without cause, by giving 15 days’ prior notice to the Supplier who shall: \n\n   - a) immediately cease (and cause its subcontractors and suppliers to cease) any performance under the relevant Purchase Order (including manufacturing the Products, providing the Services, and placing orders with its suppliers) without affecting any other Purchase Order, or any part of Purchase Order which is not terminated; \n\n   - b) make its best efforts to protect all Products and Works which are ready for delivery, and hand over the same, together with all relevant documentations set out in Art. 24 of these T&amp;C; and \n\n   - c) use best efforts to terminate existing orders placed with its subcontractor or suppliers or, at the SE and/or SDI’s request, assign all rights and obligations under those existing orders to SDI. \n\n- 13.2.The Supplier shall be paid (and only be paid) for the Products which have been manufactured, Works which have been delivered, and Services which have been provided at the time when  SDI serves the termination notice, provided that such Products, Works and Services satisfy all requirements under the Agreement. Such payment by SDI shall be final and forms the exclusive remedy available to the Supplier for the termination of the Purchase Order, in part or in whole, by SE or SDI. The Supplier shall NOT be entitled to any anticipated or prospective profits or any other loss arising from such a termination.', 'Section 6 on delivery and performance under the purchase terms covering liquidated damages for late delivery and SDI and SE rights to require continued performance or terminate the purchase order after reminder notice and continued delay\n## 6. DELIVERY AND PERFORMANCE\n\n- 6.2. For the avoidance of doubt, the Supplier acknowledges and agrees that liquidated damages referred to above are a reasonable and genuine pre-estimate of the losses that would be caused to SE and/or SDI due to Supplier’s failure to deliver the Products or Works or complete the Services within the agreed time period. Notwithstanding the liquidated damages set out in the previous paragraph or other remedies available at law or in equity, the Supplier shall still fulfill its obligations under the Agreement and does not absolve Supplier of its obligations and liabilities under the Agreement. All extra costs and expenses incurred as a result of the late delivery or late provision (including the costs to airship the delayed Products, and the increased costs in relation to manpower) shall be borne by the Supplier.\n- 6.3. If the Supplier fails to deliver the Products or Works or to provide the Services within the period specified in the Reminder Notice or, if the Reminder Notice does not specify a period, seven (7) days from the date of the Reminder Notice,  SDI (in consultation with SE) shall have sole discretion to terminate the Purchase Order in accordance with Art. 14 of these T&amp;C.', 'Section 26 of the Schneider Electric General Terms and Conditions of Purchase sets out the suppliers confidentiality obligations including permitted disclosure on a need to know basis return or destruction of confidential materials and survival of the duty after completion or termination\n## 26. CONFIDENTIALITY\n\nThe Supplier shall keep all Confidential Information secret and shall not use any of it for any purpose other than the performance of the Agreement, except that, for the purpose of performance of the Agreement, the Supplier is allowed to disclose any Confidential Information, on a need-to-know basis, to his employees, subcontractors, or suppliers who undertake in writing not to disclose or otherwise misuse the Confidential Information. Upon the request by SDI, the Supplier shall execute a separate non-disclosure agreement in the form reasonably satisfactory to the SDI, undertaking not to disclose or misuse the Confidential Information.  If any Purchase Order is completed or otherwise terminated, the Supplier shall return or destroy (at the SDI’s request), at its own costs, all documents or other media which contain any Confidential Information.  The obligation set out in this Article or in any non-disclosure agreement shall survive the termination or completion of any Purchase Order or the Agreement.', 'This section sets out SDI and SE rights to terminate a purchase order immediately for supplier default breach nonperformance insolvency and explains payment return and surviving obligations after termination\n## 14. TERMINATION FOR DEFAULT\n\n- 14.1. SDI (in consultation with SE) shall have the right to terminate at SE or SDI’s discretion (in consultation with SE), wholly or partially, the Order by notice with immediate effect and without any compensation to the Supplier, should the Supplier: a) commit a breach of any material provision under the Agreement; \n\n   - b) commit any breach of any provision of the Agreement and fail to rectify such breach (if such breach is capable of rectification) within thirty (30) days after the notice from SDI (issued in consultation with SE) of such breach; c) fail to deliver the Products or the Works, or to complete the Services as set out in Art. 6.3 of these T&amp;C; d) refuse to proceed with the performance of the relevant Purchase Order; or \n\n   - e) become insolvent or bankrupt, file a petition for voluntary winding up except for reorganization, appoint a receiver or under judicial management under a court order, assign his substantial assets for his creditors and/or perform an act which in  SDI’s view (in consultation with SE), may deprive the SE or SDI from any substantial benefit under the Purchase Order or the Agreement. \n\n- 14.2.If SDI (in consultation with SE) exercises its termination right under this Article, it shall pay (and only pay) to the Supplier the Price for the Products, the Works or the Services which SE has received and elects to keep. SE has the sole discretion to return to the Supplier any Products, or Works which it has received. For the avoidance of any doubt, the Supplier shall repay \n\n\n\nto   SDI the price for any Products or Works which   SDI has paid for but has either not received or has elected to return to the Supplier. The exercise of the termination right according to this Article shall not prejudice any right or remedy SE and/or SDI may have at law or in equity. \n\n- 14.3.The termination of any Purchase Order under Art. 13 of these T&amp;C or under this Article shall not affect any obligation of the Supplier (including the obligations under Art. 8 of these T&amp;C) with respect to those Products, Works or Services which SE has received and SDI has paid for.', 'Section 2 sets out how the purchase terms are interpreted and establishes that these general terms apply to all purchase orders and override any conflicting supplier terms unless a separately negotiated services agreement prevails\n## 2. INTERPRETATION\n\n- 2.1. These T&amp;C shall be incorporated into any Purchase Order by reference and be interpreted as an integrated part of the Purchase Order. The supply of all Products, Works or Services by the Supplier to the SE shall be governed by these T&amp;C and any other term proposed or submitted by the Supplier in this regard is expressly rejected. Where there is any inconsistency between any provision in the Purchase Order and any provision in these T&amp;C, these T&amp;C prevail. Notwithstanding the foregoing, in the event the Parties specifically negotiate and execute a services agreement, then the terms and conditions of the said services agreement shall prevail over these T&amp;C to the extent of any discrepancy or conflict.']</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>A Purchase Order can be terminated in the following ways:
+1. **Termination for convenience (Article 13)**
+   - **Who may terminate:** SDI, in consultation with SE.
+   - **Condition:** Without cause, in whole or in part.
+   - **Notice required:** 15 days’ prior notice to the Supplier.
+2. **Termination for default — material breach (Article 14.1(a))**
+   - **Who may terminate:** SDI, in consultation with SE.
+   - **Condition:** Supplier commits a breach of any material provision of the Agreement.
+   - **Effect:** Immediate termination by notice, without compensation.
+3. **Termination for default — unremedied breach (Article 14.1(b))**
+   - **Condition:** Supplier breaches any provision of the Agreement and fails to rectify it within 30 days after notice from SDI, if the breach is capable of rectification.
+4. **Termination for late delivery or late performance (Articles 6.3 and 14.1(c))**
+   - **Condition:** Supplier fails to deliver Products or Works, or provide Services, within the period stated in a Reminder Notice, or if no period is stated, within 7 days from the Reminder Notice.
+5. **Termination for refusal to perform (Article 14.1(d))**
+   - **Condition:** Supplier refuses to proceed with performance of the relevant Purchase Order.
+6. **Termination for insolvency or similar financial events (Article 14.1(e))**
+   - **Condition:** Supplier becomes insolvent or bankrupt, files for voluntary winding up except for reorganization, has a receiver appointed, comes under judicial management, assigns substantial assets for creditors, or performs an act that SDI views as depriving SE or SDI of substantial benefit under the Purchase Order or Agreement.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Termination at convenience: by SDI without cause on 15 days' notice (Art. 13). Termination for default: immediately, on a material breach, an unrectified breach (30 days), failure to deliver after a Reminder Notice, refusal to perform, or insolvency/bankruptcy (Art. 14). Via change order: if the parties cannot agree on a rejected/extra-cost Alteration Notice, SDI may terminate under Art. 13 (Art. 15.3). Delivery failure: termination after an unmet Reminder Notice period (Art. 6.3). Requires gathering distant sections.</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.249999999975</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6296003872473307</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>